--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -566,6 +566,16 @@
           <t>acquolinaristorante</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -643,6 +653,11 @@
           <t>al_madrigale</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -705,6 +720,16 @@
           <t>ristorantealloro</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -767,6 +792,16 @@
           <t>dieci_ristorante</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -829,6 +864,16 @@
           <t>enotecalatorreavillalaetitia</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -891,6 +936,16 @@
           <t>glasshostaria</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -954,6 +1009,16 @@
 idyliobyapreda</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1016,6 +1081,16 @@
           <t>ilconviviotroiani</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1078,6 +1153,16 @@
           <t>ristoranteilpagliaccio</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1140,8 +1225,16 @@
           <t>iltino_restaurant</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr"/>
-      <c r="H11" s="1" t="inlineStr"/>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1196,8 +1289,16 @@
           <t>laparolina.ristorante</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr"/>
-      <c r="H12" s="1" t="inlineStr"/>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1304,8 +1405,16 @@
           <t>latrotadal63</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr"/>
-      <c r="H14" s="1" t="inlineStr"/>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1360,8 +1469,16 @@
           <t>osteriadellorologio</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr"/>
-      <c r="H15" s="1" t="inlineStr"/>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1416,8 +1533,16 @@
           <t>materiaprimaosteriacontemporanea</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr"/>
-      <c r="H16" s="1" t="inlineStr"/>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1472,6 +1597,16 @@
           <t>ristorante_moma</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1531,7 +1666,11 @@
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr"/>
-      <c r="H18" s="1" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1586,6 +1725,16 @@
           <t>ormaromaristorante</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1649,8 +1798,16 @@
 pascucci_al_porticciolo</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1705,6 +1862,16 @@
           <t>permegiulioterrinoni</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1767,6 +1934,16 @@
           <t>pipero_ristorante</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1829,6 +2006,16 @@
           <t>pulejoristorante</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1891,8 +2078,16 @@
           <t>ristorante_riso_amaro</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr"/>
-      <c r="H24" s="1" t="inlineStr"/>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1947,8 +2142,16 @@
           <t>satricvm</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2003,6 +2206,16 @@
           <t>ziarestaurant</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -2065,6 +2278,16 @@
           <t>acciuga_roma</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -2147,8 +2370,16 @@
           <t>atlas_vita_cultura_cibo_vino</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2247,8 +2478,16 @@
           <t>barred.roma</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr"/>
-      <c r="H30" s="1" t="inlineStr"/>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2303,6 +2542,16 @@
           <t>bistrot64roma</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -2409,8 +2658,16 @@
           <t>bottegatrediciofficial</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2509,8 +2766,16 @@
           <t>carteroblio</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2561,8 +2826,16 @@
           <t>casamalgarini</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2617,8 +2890,16 @@
           <t>contatto.ristorante</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2717,8 +2998,16 @@
           <t>cuocoecamicia</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2773,8 +3062,16 @@
           <t>dogmaristorante</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2829,8 +3126,16 @@
           <t>dlr_frascati</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2885,8 +3190,16 @@
           <t>ego_ristorante</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2941,8 +3254,16 @@
           <t>cavour313roma</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2994,7 +3315,11 @@
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3181,8 +3506,16 @@
           <t>ilmarcheseroma</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3234,7 +3567,11 @@
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3289,8 +3626,16 @@
           <t>laciambellabaravin</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3389,8 +3734,16 @@
           <t>latanadeicarbonari</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr"/>
-      <c r="H52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3445,8 +3798,16 @@
           <t>locanda_altobelli</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr"/>
-      <c r="H53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3494,7 +3855,11 @@
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr"/>
-      <c r="H54" s="1" t="inlineStr"/>
+      <c r="H54" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3549,8 +3914,16 @@
           <t>mare_fiumicino</t>
         </is>
       </c>
-      <c r="G55" s="1" t="inlineStr"/>
-      <c r="H55" s="1" t="inlineStr"/>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3602,7 +3975,11 @@
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr"/>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3653,8 +4030,16 @@
           <t>misticanza.osteria</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3709,8 +4094,16 @@
           <t>moganoxritual_lab</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3765,8 +4158,16 @@
           <t>nuhosteriacontemporanea</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3817,8 +4218,16 @@
           <t>osterialandi</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3917,8 +4326,16 @@
           <t>retro_bottega</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr"/>
-      <c r="H62" s="1" t="inlineStr"/>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3973,8 +4390,16 @@
           <t>ristorantericciolidoro</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" s="1" t="inlineStr"/>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4029,8 +4454,16 @@
           <t>rimessaroscioli</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -1254,7 +1254,7 @@
       </c>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="R14" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="R15" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="R18" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="R20" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="R24" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="R25" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="R28" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="R33" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="R34" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="R35" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="R36" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="R37" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2963,71 +2963,64 @@
       </c>
       <c r="R38" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Cuoco e Camicia</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Via di Monte Polacco, 2/4</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>06/88922987</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>www.cuocoecamicia.it</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>cuocoecamicia</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>cuocoecamicia</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I39" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr"/>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R39" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3084,7 @@
       </c>
       <c r="R40" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3148,7 @@
       </c>
       <c r="R41" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3212,7 @@
       </c>
       <c r="R42" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3276,7 @@
       </c>
       <c r="R43" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3332,7 @@
       </c>
       <c r="R44" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3376,7 @@
       </c>
       <c r="R45" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3420,7 @@
       </c>
       <c r="R46" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3464,7 @@
       </c>
       <c r="R47" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3528,7 @@
       </c>
       <c r="R48" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3584,7 @@
       </c>
       <c r="R49" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3648,7 @@
       </c>
       <c r="R50" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3692,7 @@
       </c>
       <c r="R51" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3756,7 @@
       </c>
       <c r="R52" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3820,7 @@
       </c>
       <c r="R53" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3879,71 +3872,64 @@
       </c>
       <c r="R54" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Mare Bistrot</t>
         </is>
       </c>
-      <c r="B55" s="1" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Via della Torre Clementina, 126</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>334/7978290</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>www.marebistrot.com</t>
         </is>
       </c>
-      <c r="E55" s="1" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>profile.php?id=61556563215380</t>
         </is>
       </c>
-      <c r="F55" s="1" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>mare_fiumicino</t>
         </is>
       </c>
-      <c r="G55" s="1" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="H55" s="1" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr"/>
-      <c r="L55" s="1" t="inlineStr"/>
-      <c r="M55" s="1" t="inlineStr"/>
-      <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr"/>
-      <c r="P55" s="1" t="inlineStr"/>
-      <c r="Q55" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R55" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 16/04/2026</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3985,7 @@
       </c>
       <c r="R56" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4045,7 @@
       </c>
       <c r="R57" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4109,7 @@
       </c>
       <c r="R58" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4173,7 @@
       </c>
       <c r="R59" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4233,7 @@
       </c>
       <c r="R60" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4277,7 @@
       </c>
       <c r="R61" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4355,135 +4341,121 @@
       </c>
       <c r="R62" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Riccioli d'Oro</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Via Conca d'Oro, 38</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>06/83797040</t>
         </is>
       </c>
-      <c r="D63" s="1" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>www.ristorantericciolidoro.it</t>
         </is>
       </c>
-      <c r="E63" s="1" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>profile.php?id=61551090176976</t>
         </is>
       </c>
-      <c r="F63" s="1" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>ristorantericciolidoro</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="H63" s="1" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr"/>
-      <c r="L63" s="1" t="inlineStr"/>
-      <c r="M63" s="1" t="inlineStr"/>
-      <c r="N63" s="1" t="inlineStr"/>
-      <c r="O63" s="1" t="inlineStr"/>
-      <c r="P63" s="1" t="inlineStr"/>
-      <c r="Q63" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R63" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 16/04/2026</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Rimessa Roscioli</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Via del Conservatorio, 58</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>06/68803914</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>www.rimessaroscioli.com</t>
         </is>
       </c>
-      <c r="E64" s="1" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>RimessaRoscioli</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>rimessaroscioli</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H64" s="1" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr"/>
-      <c r="L64" s="1" t="inlineStr"/>
-      <c r="M64" s="1" t="inlineStr"/>
-      <c r="N64" s="1" t="inlineStr"/>
-      <c r="O64" s="1" t="inlineStr"/>
-      <c r="P64" s="1" t="inlineStr"/>
-      <c r="Q64" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R64" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 31/03/2026</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4486,11 @@
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr"/>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
@@ -4535,7 +4511,7 @@
       </c>
       <c r="R65" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4570,8 +4546,16 @@
           <t>moiristorante</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4591,7 +4575,7 @@
       </c>
       <c r="R66" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4626,8 +4610,16 @@
           <t>sintesi_ristorante</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4647,7 +4639,7 @@
       </c>
       <c r="R67" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4683,7 @@
       </c>
       <c r="R68" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4727,7 @@
       </c>
       <c r="R69" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4771,7 @@
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4814,8 +4806,16 @@
           <t>tinello_bistrot</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4870,8 +4870,16 @@
           <t>toma52trattoriagourmet</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4891,7 +4899,7 @@
       </c>
       <c r="R72" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4926,8 +4934,16 @@
           <t>umaroma_restaurant</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4947,7 +4963,7 @@
       </c>
       <c r="R73" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4991,7 +5007,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5026,8 +5042,16 @@
           <t>266labarraca</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5047,7 +5071,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5115,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5126,6 +5150,16 @@
           <t>ristoranteaidueotri</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -5206,6 +5240,16 @@
       <c r="F78" t="inlineStr">
         <is>
           <t>alceppo</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5299,7 +5343,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5387,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5378,8 +5422,16 @@
           <t>arcangelodandini</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5399,7 +5451,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5434,8 +5486,16 @@
           <t>armandoalpantheon</t>
         </is>
       </c>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5455,7 +5515,7 @@
       </c>
       <c r="R82" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5490,8 +5550,16 @@
           <t>aventina.roma</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5511,7 +5579,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5546,8 +5614,16 @@
           <t>baccanoroma</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5567,7 +5643,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5671,11 @@
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
+      <c r="H85" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I85" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5615,7 +5695,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5646,8 +5726,16 @@
           <t>buccia_trattoria</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I86" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5667,7 +5755,7 @@
       </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5702,8 +5790,16 @@
           <t>casaleverdeluna</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H87" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I87" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5723,7 +5819,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5758,8 +5854,16 @@
           <t>chaletdellago</t>
         </is>
       </c>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H88" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I88" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5779,7 +5883,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5814,8 +5918,16 @@
           <t>chinappi_roma</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I89" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5835,7 +5947,7 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5870,8 +5982,16 @@
           <t>contradarapello</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I90" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5891,7 +6011,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5922,8 +6042,16 @@
           <t>contrasto_viterbo</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I91" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5943,7 +6071,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5978,8 +6106,16 @@
           <t>fausto_ferrante_</t>
         </is>
       </c>
-      <c r="G92" s="1" t="inlineStr"/>
-      <c r="H92" s="1" t="inlineStr"/>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I92" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5999,7 +6135,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6034,8 +6170,16 @@
           <t>ristorantedamicheleroma</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I93" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6055,7 +6199,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6090,8 +6234,16 @@
           <t>denovo_e_dantico_lalocanda</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr"/>
-      <c r="H94" s="1" t="inlineStr"/>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H94" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I94" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6111,7 +6263,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6294,11 @@
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr"/>
-      <c r="G95" s="1" t="inlineStr"/>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
@@ -6163,7 +6319,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6198,8 +6354,16 @@
           <t>friccico_roma</t>
         </is>
       </c>
-      <c r="G96" s="1" t="inlineStr"/>
-      <c r="H96" s="1" t="inlineStr"/>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H96" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I96" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6219,7 +6383,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6250,8 +6414,16 @@
           <t>gallo_ristorante</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I97" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6271,7 +6443,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6306,8 +6478,16 @@
           <t>ristorante_garibaldidal1970</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I98" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6327,7 +6507,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6362,8 +6542,16 @@
           <t>ilcaliceelastella</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I99" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6383,7 +6571,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6418,8 +6606,16 @@
           <t>Agristorante_ilcasaletto</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr"/>
-      <c r="H100" s="1" t="inlineStr"/>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6439,7 +6635,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6679,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6518,8 +6714,16 @@
           <t>ristoranteilgrecale</t>
         </is>
       </c>
-      <c r="G102" s="1" t="inlineStr"/>
-      <c r="H102" s="1" t="inlineStr"/>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H102" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I102" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6539,7 +6743,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6570,8 +6774,16 @@
           <t>ilpacchero.solitario</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr"/>
-      <c r="H103" s="1" t="inlineStr"/>
+      <c r="G103" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H103" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I103" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6591,7 +6803,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6626,8 +6838,16 @@
           <t>iltorchiofrascati</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr"/>
-      <c r="H104" s="1" t="inlineStr"/>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I104" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6647,7 +6867,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6678,8 +6898,16 @@
           <t>iodio_roma</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" s="1" t="inlineStr"/>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I105" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6699,7 +6927,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6734,8 +6962,16 @@
           <t>la_baia_fregene_</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr"/>
-      <c r="H106" s="1" t="inlineStr"/>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6755,7 +6991,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6799,63 +7035,64 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>La Galleria di Sopra</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Via Leonardo Murialdo, 9</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>06/9322791</t>
         </is>
       </c>
-      <c r="D108" s="1" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>www.lagalleriadisopra.it</t>
         </is>
       </c>
-      <c r="E108" s="1" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>LaGalleriaDiSopra</t>
         </is>
       </c>
-      <c r="F108" s="1" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>lagalleriadisopra</t>
         </is>
       </c>
-      <c r="G108" s="1" t="inlineStr"/>
-      <c r="H108" s="1" t="inlineStr"/>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J108" s="1" t="inlineStr"/>
-      <c r="K108" s="1" t="inlineStr"/>
-      <c r="L108" s="1" t="inlineStr"/>
-      <c r="M108" s="1" t="inlineStr"/>
-      <c r="N108" s="1" t="inlineStr"/>
-      <c r="O108" s="1" t="inlineStr"/>
-      <c r="P108" s="1" t="inlineStr"/>
-      <c r="Q108" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R108" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 11/04/2026</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6890,8 +7127,16 @@
           <t>lalampara_passoscuro</t>
         </is>
       </c>
-      <c r="G109" s="1" t="inlineStr"/>
-      <c r="H109" s="1" t="inlineStr"/>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H109" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I109" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6911,7 +7156,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6946,8 +7191,16 @@
           <t>locandadelbere</t>
         </is>
       </c>
-      <c r="G110" s="1" t="inlineStr"/>
-      <c r="H110" s="1" t="inlineStr"/>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I110" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6967,7 +7220,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6998,7 +7251,11 @@
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr"/>
-      <c r="G111" s="1" t="inlineStr"/>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
@@ -7019,7 +7276,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7054,8 +7311,16 @@
           <t>la_palazzina_ristorante</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr"/>
-      <c r="H112" s="1" t="inlineStr"/>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H112" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7075,63 +7340,64 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>La Quercia</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Piazza della Quercia, 23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>06/68300932</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>www.osterialaquercia.com</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>profile.php?id=100063755283530</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>laquerciaosteria</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t>La Quercia</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>Piazza della Quercia, 23</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>06/68300932</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>www.osterialaquercia.com</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>profile.php?id=100063755283530</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>laquerciaosteria</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr"/>
-      <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J113" s="1" t="inlineStr"/>
-      <c r="K113" s="1" t="inlineStr"/>
-      <c r="L113" s="1" t="inlineStr"/>
-      <c r="M113" s="1" t="inlineStr"/>
-      <c r="N113" s="1" t="inlineStr"/>
-      <c r="O113" s="1" t="inlineStr"/>
-      <c r="P113" s="1" t="inlineStr"/>
-      <c r="Q113" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R113" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7162,8 +7428,16 @@
           <t>la_tavernadeicorsari</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr"/>
-      <c r="H114" s="1" t="inlineStr"/>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I114" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7183,7 +7457,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7218,8 +7492,16 @@
           <t>ristorantelavillettaformia</t>
         </is>
       </c>
-      <c r="G115" s="1" t="inlineStr"/>
-      <c r="H115" s="1" t="inlineStr"/>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H115" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I115" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7239,7 +7521,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7274,8 +7556,16 @@
           <t>lisomariofficial</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr"/>
-      <c r="H116" s="1" t="inlineStr"/>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7295,7 +7585,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7616,11 @@
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr"/>
-      <c r="G117" s="1" t="inlineStr"/>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
@@ -7347,7 +7641,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7382,8 +7676,16 @@
           <t>locanda.dorica</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr"/>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7403,63 +7705,64 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>Locanda Nocera</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Via Viggiano, 155</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>351/7590202</t>
         </is>
       </c>
-      <c r="D119" s="1" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>locandanocera.eatbu.com</t>
         </is>
       </c>
-      <c r="E119" s="1" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>locandanocera</t>
         </is>
       </c>
-      <c r="F119" s="1" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>locanda_nocera</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr"/>
-      <c r="H119" s="1" t="inlineStr"/>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J119" s="1" t="inlineStr"/>
-      <c r="K119" s="1" t="inlineStr"/>
-      <c r="L119" s="1" t="inlineStr"/>
-      <c r="M119" s="1" t="inlineStr"/>
-      <c r="N119" s="1" t="inlineStr"/>
-      <c r="O119" s="1" t="inlineStr"/>
-      <c r="P119" s="1" t="inlineStr"/>
-      <c r="Q119" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R119" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 03/04/2026</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7494,8 +7797,16 @@
           <t>locandaruggieri</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr"/>
-      <c r="H120" s="1" t="inlineStr"/>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I120" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7515,7 +7826,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7546,8 +7857,16 @@
           <t>losteria_di_ianus</t>
         </is>
       </c>
-      <c r="G121" s="1" t="inlineStr"/>
-      <c r="H121" s="1" t="inlineStr"/>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H121" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I121" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7567,7 +7886,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7602,8 +7921,16 @@
           <t>maksymovych_ristorante</t>
         </is>
       </c>
-      <c r="G122" s="1" t="inlineStr"/>
-      <c r="H122" s="1" t="inlineStr"/>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I122" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7623,7 +7950,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7654,8 +7981,16 @@
           <t>Mamma-Angelina</t>
         </is>
       </c>
-      <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" s="1" t="inlineStr"/>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I123" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7675,7 +8010,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7706,8 +8041,16 @@
           <t>ristorantemammaorso</t>
         </is>
       </c>
-      <c r="G124" s="1" t="inlineStr"/>
-      <c r="H124" s="1" t="inlineStr"/>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I124" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7727,7 +8070,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7771,7 +8114,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7815,7 +8158,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7850,8 +8193,16 @@
           <t>mazzo_roma</t>
         </is>
       </c>
-      <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr"/>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7871,7 +8222,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7906,7 +8257,11 @@
           <t>menabo_vino_e_cucina</t>
         </is>
       </c>
-      <c r="G128" s="1" t="inlineStr"/>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
@@ -7927,7 +8282,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7983,7 +8338,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8394,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8095,7 +8450,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8494,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8538,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8590,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8291,7 +8646,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8694,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8750,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8798,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8854,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8910,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8966,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8667,7 +9022,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8723,7 +9078,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8767,7 +9122,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8811,7 +9166,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8867,7 +9222,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8923,7 +9278,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8975,7 +9330,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9386,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9430,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9486,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9530,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9574,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9630,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9686,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9742,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9786,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9842,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9898,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9950,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9998,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9695,7 +10050,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9751,7 +10106,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9807,7 +10162,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9859,7 +10214,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9915,7 +10270,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9959,7 +10314,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10370,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10414,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10470,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10526,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10582,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10638,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10682,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10734,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10778,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10834,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10886,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10942,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10986,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10683,7 +11038,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10739,7 +11094,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10783,7 +11138,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10839,7 +11194,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10891,7 +11246,7 @@
       </c>
       <c r="R185" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10935,7 +11290,7 @@
       </c>
       <c r="R186" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10991,7 +11346,7 @@
       </c>
       <c r="R187" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11402,7 @@
       </c>
       <c r="R188" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11458,7 @@
       </c>
       <c r="R189" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11147,7 +11502,7 @@
       </c>
       <c r="R190" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11203,7 +11558,7 @@
       </c>
       <c r="R191" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11610,7 @@
       </c>
       <c r="R192" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11666,7 @@
       </c>
       <c r="R193" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11722,7 @@
       </c>
       <c r="R194" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11778,7 @@
       </c>
       <c r="R195" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11834,7 @@
       </c>
       <c r="R196" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11886,7 @@
       </c>
       <c r="R197" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11942,7 @@
       </c>
       <c r="R198" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11998,7 @@
       </c>
       <c r="R199" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11687,7 +12042,7 @@
       </c>
       <c r="R200" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11743,7 +12098,7 @@
       </c>
       <c r="R201" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11799,7 +12154,7 @@
       </c>
       <c r="R202" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11855,7 +12210,7 @@
       </c>
       <c r="R203" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11911,7 +12266,7 @@
       </c>
       <c r="R204" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -11967,7 +12322,7 @@
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12370,7 @@
       </c>
       <c r="R206" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12071,7 +12426,7 @@
       </c>
       <c r="R207" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12482,7 @@
       </c>
       <c r="R208" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12526,7 @@
       </c>
       <c r="R209" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12570,7 @@
       </c>
       <c r="R210" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12626,7 @@
       </c>
       <c r="R211" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12327,7 +12682,7 @@
       </c>
       <c r="R212" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12738,7 @@
       </c>
       <c r="R213" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12439,7 +12794,7 @@
       </c>
       <c r="R214" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12850,7 @@
       </c>
       <c r="R215" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12902,7 @@
       </c>
       <c r="R216" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12958,7 @@
       </c>
       <c r="R217" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12806,7 +13161,7 @@
       </c>
       <c r="R220" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12850,7 +13205,7 @@
       </c>
       <c r="R221" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12906,7 +13261,7 @@
       </c>
       <c r="R222" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -12962,7 +13317,7 @@
       </c>
       <c r="R223" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13373,7 @@
       </c>
       <c r="R224" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13429,7 @@
       </c>
       <c r="R225" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13130,7 +13485,7 @@
       </c>
       <c r="R226" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13174,7 +13529,7 @@
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13230,7 +13585,7 @@
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13629,7 @@
       </c>
       <c r="R229" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13685,7 @@
       </c>
       <c r="R230" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13729,7 @@
       </c>
       <c r="R231" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13781,7 @@
       </c>
       <c r="R232" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13837,7 @@
       </c>
       <c r="R233" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13893,7 @@
       </c>
       <c r="R234" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13594,7 +13949,7 @@
       </c>
       <c r="R235" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13638,7 +13993,7 @@
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13690,7 +14045,7 @@
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13742,7 +14097,7 @@
       </c>
       <c r="R238" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13798,7 +14153,7 @@
       </c>
       <c r="R239" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13854,7 +14209,7 @@
       </c>
       <c r="R240" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13910,7 +14265,7 @@
       </c>
       <c r="R241" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -13966,7 +14321,7 @@
       </c>
       <c r="R242" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14377,7 @@
       </c>
       <c r="R243" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14433,7 @@
       </c>
       <c r="R244" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14489,7 @@
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14533,7 @@
       </c>
       <c r="R246" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14234,7 +14589,7 @@
       </c>
       <c r="R247" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14278,7 +14633,7 @@
       </c>
       <c r="R248" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14677,7 @@
       </c>
       <c r="R249" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14733,7 @@
       </c>
       <c r="R250" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14789,7 @@
       </c>
       <c r="R251" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14490,7 +14845,7 @@
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14897,7 @@
       </c>
       <c r="R253" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14953,7 @@
       </c>
       <c r="R254" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14654,7 +15009,7 @@
       </c>
       <c r="R255" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14710,7 +15065,7 @@
       </c>
       <c r="R256" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14766,7 +15121,7 @@
       </c>
       <c r="R257" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14822,7 +15177,7 @@
       </c>
       <c r="R258" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14878,7 +15233,7 @@
       </c>
       <c r="R259" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14934,7 +15289,7 @@
       </c>
       <c r="R260" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -14982,7 +15337,7 @@
       </c>
       <c r="R261" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15389,7 @@
       </c>
       <c r="R262" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15445,7 @@
       </c>
       <c r="R263" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15501,7 @@
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15557,7 @@
       </c>
       <c r="R265" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15254,7 +15609,7 @@
       </c>
       <c r="R266" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15306,7 +15661,7 @@
       </c>
       <c r="R267" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15705,7 @@
       </c>
       <c r="R268" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15402,7 +15757,7 @@
       </c>
       <c r="R269" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15454,7 +15809,7 @@
       </c>
       <c r="R270" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15498,7 +15853,7 @@
       </c>
       <c r="R271" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15542,7 +15897,7 @@
       </c>
       <c r="R272" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15598,7 +15953,7 @@
       </c>
       <c r="R273" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15650,7 +16005,7 @@
       </c>
       <c r="R274" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15706,7 +16061,7 @@
       </c>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15762,7 +16117,7 @@
       </c>
       <c r="R276" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15818,7 +16173,7 @@
       </c>
       <c r="R277" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15870,7 +16225,7 @@
       </c>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15926,7 +16281,7 @@
       </c>
       <c r="R279" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -15982,7 +16337,7 @@
       </c>
       <c r="R280" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16385,7 @@
       </c>
       <c r="R281" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16441,7 @@
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16497,7 @@
       </c>
       <c r="R283" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16194,7 +16549,7 @@
       </c>
       <c r="R284" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16234,7 +16589,7 @@
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16645,7 @@
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16697,7 @@
       </c>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16749,7 @@
       </c>
       <c r="R288" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16805,7 @@
       </c>
       <c r="R289" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16857,7 @@
       </c>
       <c r="R290" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16546,7 +16901,7 @@
       </c>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16945,7 @@
       </c>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16646,7 +17001,7 @@
       </c>
       <c r="R293" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16698,7 +17053,7 @@
       </c>
       <c r="R294" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16742,7 +17097,7 @@
       </c>
       <c r="R295" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16798,7 +17153,7 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16854,7 +17209,7 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16906,7 +17261,7 @@
       </c>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -16958,7 +17313,7 @@
       </c>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17014,7 +17369,7 @@
       </c>
       <c r="R300" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17058,7 +17413,7 @@
       </c>
       <c r="R301" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17106,7 +17461,7 @@
       </c>
       <c r="R302" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17517,7 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17218,7 +17573,7 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17266,7 +17621,7 @@
       </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17322,7 +17677,7 @@
       </c>
       <c r="R306" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17378,7 +17733,7 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17789,7 @@
       </c>
       <c r="R308" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17490,7 +17845,7 @@
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17546,7 +17901,7 @@
       </c>
       <c r="R310" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17602,7 +17957,7 @@
       </c>
       <c r="R311" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17658,7 +18013,7 @@
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17710,7 +18065,7 @@
       </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17766,7 +18121,7 @@
       </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17822,7 +18177,7 @@
       </c>
       <c r="R315" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17878,7 +18233,7 @@
       </c>
       <c r="R316" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17934,7 +18289,7 @@
       </c>
       <c r="R317" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -17978,7 +18333,7 @@
       </c>
       <c r="R318" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18022,7 +18377,7 @@
       </c>
       <c r="R319" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18066,7 +18421,7 @@
       </c>
       <c r="R320" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18477,7 @@
       </c>
       <c r="R321" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18533,7 @@
       </c>
       <c r="R322" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18589,7 @@
       </c>
       <c r="R323" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18286,7 +18641,7 @@
       </c>
       <c r="R324" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18342,7 +18697,7 @@
       </c>
       <c r="R325" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18753,7 @@
       </c>
       <c r="R326" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18442,7 +18797,7 @@
       </c>
       <c r="R327" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18853,7 @@
       </c>
       <c r="R328" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18554,7 +18909,7 @@
       </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18610,7 +18965,7 @@
       </c>
       <c r="R330" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18658,7 +19013,7 @@
       </c>
       <c r="R331" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18878,7 +19233,7 @@
       </c>
       <c r="R334" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18934,7 +19289,7 @@
       </c>
       <c r="R335" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -18986,7 +19341,7 @@
       </c>
       <c r="R336" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19030,7 +19385,7 @@
       </c>
       <c r="R337" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19086,7 +19441,7 @@
       </c>
       <c r="R338" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19138,7 +19493,7 @@
       </c>
       <c r="R339" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19194,7 +19549,7 @@
       </c>
       <c r="R340" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19238,7 +19593,7 @@
       </c>
       <c r="R341" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19282,7 +19637,7 @@
       </c>
       <c r="R342" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19685,7 @@
       </c>
       <c r="R343" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19386,7 +19741,7 @@
       </c>
       <c r="R344" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19434,7 +19789,7 @@
       </c>
       <c r="R345" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19478,7 +19833,7 @@
       </c>
       <c r="R346" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19534,7 +19889,7 @@
       </c>
       <c r="R347" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19586,7 +19941,7 @@
       </c>
       <c r="R348" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19638,7 +19993,7 @@
       </c>
       <c r="R349" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19694,7 +20049,7 @@
       </c>
       <c r="R350" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19738,7 +20093,7 @@
       </c>
       <c r="R351" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19794,7 +20149,7 @@
       </c>
       <c r="R352" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19846,7 +20201,7 @@
       </c>
       <c r="R353" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19902,7 +20257,7 @@
       </c>
       <c r="R354" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -19958,7 +20313,7 @@
       </c>
       <c r="R355" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20014,7 +20369,7 @@
       </c>
       <c r="R356" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20070,7 +20425,7 @@
       </c>
       <c r="R357" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20122,7 +20477,7 @@
       </c>
       <c r="R358" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20178,7 +20533,7 @@
       </c>
       <c r="R359" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20749,7 @@
       </c>
       <c r="R362" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20450,7 +20805,7 @@
       </c>
       <c r="R363" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20861,7 @@
       </c>
       <c r="R364" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20558,7 +20913,7 @@
       </c>
       <c r="R365" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20606,7 +20961,7 @@
       </c>
       <c r="R366" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20662,7 +21017,7 @@
       </c>
       <c r="R367" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20718,7 +21073,7 @@
       </c>
       <c r="R368" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20774,7 +21129,7 @@
       </c>
       <c r="R369" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20826,7 +21181,7 @@
       </c>
       <c r="R370" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20882,7 +21237,7 @@
       </c>
       <c r="R371" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20926,7 +21281,7 @@
       </c>
       <c r="R372" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -20982,7 +21337,7 @@
       </c>
       <c r="R373" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21393,7 @@
       </c>
       <c r="R374" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21094,7 +21449,7 @@
       </c>
       <c r="R375" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21150,7 +21505,7 @@
       </c>
       <c r="R376" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21206,7 +21561,7 @@
       </c>
       <c r="R377" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21258,7 +21613,7 @@
       </c>
       <c r="R378" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21302,7 +21657,7 @@
       </c>
       <c r="R379" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21358,7 +21713,7 @@
       </c>
       <c r="R380" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21410,7 +21765,7 @@
       </c>
       <c r="R381" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21466,7 +21821,7 @@
       </c>
       <c r="R382" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21518,7 +21873,7 @@
       </c>
       <c r="R383" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21570,7 +21925,7 @@
       </c>
       <c r="R384" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21626,7 +21981,7 @@
       </c>
       <c r="R385" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21682,7 +22037,7 @@
       </c>
       <c r="R386" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21734,7 +22089,7 @@
       </c>
       <c r="R387" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21790,7 +22145,7 @@
       </c>
       <c r="R388" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21846,7 +22201,7 @@
       </c>
       <c r="R389" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21898,7 +22253,7 @@
       </c>
       <c r="R390" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21942,7 +22297,7 @@
       </c>
       <c r="R391" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -21998,7 +22353,7 @@
       </c>
       <c r="R392" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22054,7 +22409,7 @@
       </c>
       <c r="R393" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22106,7 +22461,7 @@
       </c>
       <c r="R394" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22162,7 +22517,7 @@
       </c>
       <c r="R395" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22214,7 +22569,7 @@
       </c>
       <c r="R396" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22266,7 +22621,7 @@
       </c>
       <c r="R397" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22322,7 +22677,7 @@
       </c>
       <c r="R398" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22729,7 @@
       </c>
       <c r="R399" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22430,7 +22785,7 @@
       </c>
       <c r="R400" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22478,7 +22833,7 @@
       </c>
       <c r="R401" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22885,7 @@
       </c>
       <c r="R402" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22937,7 @@
       </c>
       <c r="R403" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22638,7 +22993,7 @@
       </c>
       <c r="R404" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22694,7 +23049,7 @@
       </c>
       <c r="R405" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22746,7 +23101,7 @@
       </c>
       <c r="R406" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22786,7 +23141,7 @@
       </c>
       <c r="R407" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22838,7 +23193,7 @@
       </c>
       <c r="R408" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22894,7 +23249,7 @@
       </c>
       <c r="R409" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22946,7 +23301,7 @@
       </c>
       <c r="R410" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -22990,7 +23345,7 @@
       </c>
       <c r="R411" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -23038,7 +23393,7 @@
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -23090,7 +23445,7 @@
       </c>
       <c r="R413" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23501,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -23202,7 +23557,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -23258,7 +23613,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -23314,7 +23669,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -23370,7 +23725,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -23426,7 +23781,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -23482,7 +23837,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -938,7 +938,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1195,130 +1195,126 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Il Tino</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Via Monte Cadria, 125</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>06/5522778</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>www.ristoranteiltino.com</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>ristoranteiltino</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>iltino_restaurant</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr"/>
-      <c r="L11" s="1" t="inlineStr"/>
-      <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
-      <c r="O11" s="1" t="inlineStr"/>
-      <c r="P11" s="1" t="inlineStr"/>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R11" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GBP aperto, 1 stella Michelin 2026, TheFork prenotazioni attive</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>La Parolina</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Via Giacomo Leopardi, 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0763/717130</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>www.laparolina.it</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>LaParolina</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>laparolina.ristorante</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr"/>
-      <c r="L12" s="1" t="inlineStr"/>
-      <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
-      <c r="O12" s="1" t="inlineStr"/>
-      <c r="P12" s="1" t="inlineStr"/>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R12" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, menu speciale 20 anni fino mar 2026</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1375,194 +1371,188 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>La Trota</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Via Santa Susanna, 33</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>0746/685078</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>www.latrota.com</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>LaTrotadal1963</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>latrotadal63</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr"/>
-      <c r="L14" s="1" t="inlineStr"/>
-      <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
-      <c r="O14" s="1" t="inlineStr"/>
-      <c r="P14" s="1" t="inlineStr"/>
-      <c r="Q14" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R14" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GBP aperto, 1 stella Michelin 2026, TheFork attivo, sito latrota.com</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>L'Osteria dell'Orologio</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Via della Torre Clementina, 114</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>06/6505251</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>www.osteriadellorologio.net</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>osteriadellorologio.orologio</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>osteriadellorologio</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr"/>
-      <c r="L15" s="1" t="inlineStr"/>
-      <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="1" t="inlineStr"/>
-      <c r="O15" s="1" t="inlineStr"/>
-      <c r="P15" s="1" t="inlineStr"/>
-      <c r="Q15" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R15" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, sito osteriadellorologio.net attivo</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Materia Prima</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Via Sardegna, 8</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>0773/86391</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>www.materiaprimapontinia.it</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>materiaprimaosteriacontemporanea</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>materiaprimaosteriacontemporanea</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr"/>
-      <c r="L16" s="1" t="inlineStr"/>
-      <c r="M16" s="1" t="inlineStr"/>
-      <c r="N16" s="1" t="inlineStr"/>
-      <c r="O16" s="1" t="inlineStr"/>
-      <c r="P16" s="1" t="inlineStr"/>
-      <c r="Q16" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R16" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GBP aperto, sito materiaprimaroma.it attivo, prenotazioni 2026</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1639,58 +1629,54 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Nomos Ante</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Via di San Paolo alla Regola, 3</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>06/84102388</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>www.nomoshotel.com/nomos-ante</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr"/>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>nomoshotel</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr"/>
-      <c r="H18" s="1" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr"/>
-      <c r="L18" s="1" t="inlineStr"/>
-      <c r="M18" s="1" t="inlineStr"/>
-      <c r="N18" s="1" t="inlineStr"/>
-      <c r="O18" s="1" t="inlineStr"/>
-      <c r="P18" s="1" t="inlineStr"/>
-      <c r="Q18" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R18" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GBP aperto, aperto set 2025 al Nomos Hotel, citato tra le novità Roma 2026</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1767,67 +1753,65 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Pascucci al Porticciolo</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Viale Traiano, 85</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>06/65029204</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>www.pascuccialporticciolo.com</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>pascucciaporticciolo</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>pascucci_al_porticciolo_x000d_
 pascucci_al_porticciolo</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr"/>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R20" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GBP aperto, 1 stella Michelin 2026, sito pascuccialporticciolo.it attivo</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2048,130 +2032,126 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Riso Amaro</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Viale Regina Margherita, 22</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>0771/523655</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>www.ristoranterisoamaro.it</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>defilippismaurizio83</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>ristorante_riso_amaro</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr"/>
-      <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="1" t="inlineStr"/>
-      <c r="N24" s="1" t="inlineStr"/>
-      <c r="O24" s="1" t="inlineStr"/>
-      <c r="P24" s="1" t="inlineStr"/>
-      <c r="Q24" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R24" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, Wheree mar 2026, TheFork attivo</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Satricvm</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Strada Nettuno-Cisterna, 1227 - Loc. Le Ferriere</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>349/1923153</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>www.maxcotilli.com</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Satricvm-109800836034879</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>satricvm</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H25" s="1" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr"/>
-      <c r="L25" s="1" t="inlineStr"/>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr"/>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R25" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, TheFork attivo, sito blog.maxcotilli.com</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2340,174 +2320,163 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Atlas</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Via Ciro Menotti, 16/18</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>06/35072243</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>www.atlascoelestis.it</t>
         </is>
       </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>atlascoelestis.it</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>atlas_vita_cultura_cibo_vino</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr"/>
-      <c r="L28" s="1" t="inlineStr"/>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
-      <c r="O28" s="1" t="inlineStr"/>
-      <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R28" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GBP aperto, sito atlascoelestis.it attivo, recensioni 2026 positive</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Avus</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Via Cavour, 117</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>06/30324564</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr"/>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr"/>
-      <c r="G29" s="1" t="inlineStr"/>
-      <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr"/>
-      <c r="L29" s="1" t="inlineStr"/>
-      <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr"/>
-      <c r="O29" s="1" t="inlineStr"/>
-      <c r="P29" s="1" t="inlineStr"/>
-      <c r="Q29" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R29" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GBP aperto, cucina vegetale a Marino RM, info aggiornate mar 2026</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Barred</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Via Cesena, 30</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>06/97273382</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>www.barred.it</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>barredroma</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>barred.roma</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr"/>
-      <c r="L30" s="1" t="inlineStr"/>
-      <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr"/>
-      <c r="O30" s="1" t="inlineStr"/>
-      <c r="P30" s="1" t="inlineStr"/>
-      <c r="Q30" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R30" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GBP aperto, Yelp feb 2026, TheFork attivo, Turismo Roma presente</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2578,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr"/>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
       <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
@@ -2628,342 +2601,319 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Bottega Tredici</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Via dei Falegnami, 14</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>06/92118504</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>www.bottegatredici.it</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>bottegaTrediciOfficial</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>bottegatrediciofficial</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H33" s="1" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr"/>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr"/>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R33" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GBP aperto, TheFork disponibile, Turismo Roma, Yelp dic 2025</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Brado</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Viale Amelia, 42</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>375/5140851</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr"/>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr"/>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr"/>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GBP aperto, TheFork menù 2026, sito bradoroma.it attivo</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Carter Oblio</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Via Giuseppe Gioachino Belli, 21</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>06/39728547</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>www.carteroblio.com</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>ristorantecarteroblio</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>carteroblio</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H35" s="1" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I35" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr"/>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R35" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>GBP aperto, partecipante Taste of Roma apr 2026, Michelin 2026</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Casa Malgarini</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Via della Giustiniana, 670/B</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>06/87772889</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>paesaggioalimentare</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>casamalgarini</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H36" s="1" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr"/>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr"/>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R36" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>GBP aperto, Puntarella Rossa 'dieci ristoranti da provare Roma 2026' mar 2026</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Contatto</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Via Gioberti, 11</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>06/21700957</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>www.contattoristorante.it</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>contattoristorante</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>contatto.ristorante</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H37" s="1" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I37" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr"/>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R37" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>GBP aperto (Frascati VIA Gioberti 11), sito contattoristorante.it attivo</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Controluce</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Via della Luce, 44</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>06/5814839</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr"/>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R38" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>GBP aperto, TheFork attivo, recensione mar 2026 su nomadogclub</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3000,879 +2950,827 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>GBP aperto, Yelp apr 2026, sito cuocoecamicia.it attivo</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dogma</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Piazza Zama, 34</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>06/86679819</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>www.ristorantedogma.com</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>dogmaristorante</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>dogmaristorante</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Dogma</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>Piazza Zama, 34</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>06/86679819</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>www.ristorantedogma.com</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>dogmaristorante</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>dogmaristorante</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>GBP aperto; Michelin 2026; sito attivo</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dopo Lavoro Ricreativo</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Via Nino Bixio, 1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>06/630640</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>www.dlrfrascati.it</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dlrfrascati</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>dlr_frascati</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr"/>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R40" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>Dopo Lavoro Ricreativo</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>Via Nino Bixio, 1</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>06/630640</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>www.dlrfrascati.it</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>Dlrfrascati</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>dlr_frascati</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>GBP aperto; Instagram attivo; TheFork 9.8/10</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EGO</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Etruria, 35</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>342/5470485</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>www.egorestaurant.it</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ego.ristorante</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ego_ristorante</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H41" s="1" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr"/>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R41" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>EGO</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>Via Etruria, 35</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>342/5470485</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>www.egorestaurant.it</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>ego.ristorante</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>ego_ristorante</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>GBP aperto; Passione Gourmet 10 aprile 2026</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Enoteca Cavour 313</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Via Cavour, 313</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>06/6785496</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>www.cavour313.it</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>EnotecaCavour313</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>cavour313roma</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H42" s="1" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I42" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr"/>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R42" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>Enoteca Cavour 313</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>Via Cavour, 313</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>06/6785496</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>www.cavour313.it</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>EnotecaCavour313</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>cavour313roma</t>
-        </is>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated October 2025; sito attivo</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Fase - cucina spontanea</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Via Muggia, 14</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>331/1264351</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>www.faserestaurant.it</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>faseroma</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H43" s="1" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>GBP aperto; sito attivo; 50 Top Italy 2025-26</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Forma</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Via Trieste, 9</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0766/672647</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>GBP aperto; TheFork Recensioni Verificate 2026 (sede Civitavecchia)</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Giù Upside Down Restaurant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Via Paolo Stoppa, 40</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>375/5475445</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>GBP aperto; 124 rec. TripAdvisor; aperto nov 2024</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hand Made</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Viale della Pineta di Fregene, 52/C</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>06/66562063</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>GBP aperto; TripAdvisor lista aprile 2026 Fregene</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Il Marchese</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Via di Ripetta, 162</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>06/90218872</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>www.ilmarcheseroma.it</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ilmarcheseroma</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ilmarcheseroma</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I43" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr"/>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R43" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Fase - cucina spontanea</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>Via Muggia, 14</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>331/1264351</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>www.faserestaurant.it</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>faseroma</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr"/>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R44" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>Forma</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>Via Trieste, 9</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>0766/672647</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr"/>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R45" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>Giù Upside Down Restaurant</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>Via Paolo Stoppa, 40</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>375/5475445</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr"/>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R46" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>Hand Made</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>Viale della Pineta di Fregene, 52/C</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>06/66562063</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr"/>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R47" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>Il Marchese</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>Via di Ripetta, 162</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>06/90218872</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>www.ilmarcheseroma.it</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>ilmarcheseroma</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>ilmarcheseroma</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>GBP aperto; TheFork 8.9/10 attivo</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Isotta - Trattoria Cortese</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Via Carlo Livi, 10/16</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>06/23209132</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>www.isottatrattoria.it</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>isottatrattoria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H48" s="1" t="inlineStr">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>GBP aperto; Instagram attivo; TripAdvisor attivo</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>La Ciambella bar à vin</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Via dell'Arco della Ciambella, 20</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>06/6832930</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>www.la-ciambella.it</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RistoranteLaCiambella</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>laciambellabaravin</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr"/>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R48" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>Isotta - Trattoria Cortese</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>Via Carlo Livi, 10/16</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>06/23209132</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>www.isottatrattoria.it</t>
-        </is>
-      </c>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>isottatrattoria</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I49" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr"/>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R49" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>La Ciambella bar à vin</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>Via dell'Arco della Ciambella, 20</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>06/6832930</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>www.la-ciambella.it</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>RistoranteLaCiambella</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>laciambellabaravin</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated April 2026; Michelin</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>La Perla</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Via Collebianco, 11</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>339/8876306</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>GBP aperto; Gambero Rosso 2026 (sede Arpino FR); sito attivo</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>La Tana dei Carbonari</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Via XX Settembre, 35</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>351/7434838</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>www.latanadeicarbonari.it</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>La-Tana-Dei-Carbonari-100067152780921/</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>latanadeicarbonari</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H50" s="1" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I50" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr"/>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R50" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>La Perla</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>Via Collebianco, 11</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>339/8876306</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr"/>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr"/>
-      <c r="L51" s="1" t="inlineStr"/>
-      <c r="M51" s="1" t="inlineStr"/>
-      <c r="N51" s="1" t="inlineStr"/>
-      <c r="O51" s="1" t="inlineStr"/>
-      <c r="P51" s="1" t="inlineStr"/>
-      <c r="Q51" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R51" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>La Tana dei Carbonari</t>
-        </is>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>Via XX Settembre, 35</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>351/7434838</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>www.latanadeicarbonari.it</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>La-Tana-Dei-Carbonari-100067152780921/</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>latanadeicarbonari</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>GBP aperto; sito attivo; Gambero Rosso (sede Roccagorga LT)</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Locanda Altobelli</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Via Annunziata, 121</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>346/8256622</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>locanda-altobelli.business.site</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Locanda-Altobelli-100083226037628</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>locanda_altobelli</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H52" s="1" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr"/>
-      <c r="L52" s="1" t="inlineStr"/>
-      <c r="M52" s="1" t="inlineStr"/>
-      <c r="N52" s="1" t="inlineStr"/>
-      <c r="O52" s="1" t="inlineStr"/>
-      <c r="P52" s="1" t="inlineStr"/>
-      <c r="Q52" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R52" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>Locanda Altobelli</t>
-        </is>
-      </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>Via Annunziata, 121</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>346/8256622</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>locanda-altobelli.business.site</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>Locanda-Altobelli-100083226037628</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>locanda_altobelli</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>GBP aperto; Michelin 2026; 138 rec. Google (sede Terracina LT)</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Mafè - osteria moderna</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Via Valsavaranche, 29/31</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>06/86299221</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>osteria_mafe</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H53" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I53" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr"/>
-      <c r="L53" s="1" t="inlineStr"/>
-      <c r="M53" s="1" t="inlineStr"/>
-      <c r="N53" s="1" t="inlineStr"/>
-      <c r="O53" s="1" t="inlineStr"/>
-      <c r="P53" s="1" t="inlineStr"/>
-      <c r="Q53" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R53" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>Mafè - osteria moderna</t>
-        </is>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>Via Valsavaranche, 29/31</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>06/86299221</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr"/>
-      <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>osteria_mafe</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr"/>
-      <c r="H54" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I54" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr"/>
-      <c r="L54" s="1" t="inlineStr"/>
-      <c r="M54" s="1" t="inlineStr"/>
-      <c r="N54" s="1" t="inlineStr"/>
-      <c r="O54" s="1" t="inlineStr"/>
-      <c r="P54" s="1" t="inlineStr"/>
-      <c r="Q54" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R54" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>GBP aperto; Instagram attivo; aperto ott 2024</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -3922,258 +3820,252 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Promosso ad APERTO: post Facebook del 16/04/2026</t>
+          <t>GBP aperto; recensione TheFork 5 gen 2026 (sede Fiumicino)</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Metis</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Piazza Enrico Martini, 24/25</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>06/40066729</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>www.rismetis.com</t>
         </is>
       </c>
-      <c r="E56" s="1" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>metis.ristorante</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr"/>
-      <c r="L56" s="1" t="inlineStr"/>
-      <c r="M56" s="1" t="inlineStr"/>
-      <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr"/>
-      <c r="P56" s="1" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R56" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated July 2025; RestaurantGuru 4.9/5</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Misticanza - Osteria della Terra</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Via Cesare Baronio, 179</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>06/69306952</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>MisticanzaOsteria</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>misticanza.osteria</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H57" s="1" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr"/>
-      <c r="L57" s="1" t="inlineStr"/>
-      <c r="M57" s="1" t="inlineStr"/>
-      <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr"/>
-      <c r="P57" s="1" t="inlineStr"/>
-      <c r="Q57" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R57" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>GBP aperto; recensione 1 febbraio 2026; Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Mogano</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Via del Praticello Alto, 5</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>327/2312156</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>www.moganorestaurant.it</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>profile.php?id=100068956915811</t>
         </is>
       </c>
-      <c r="F58" s="1" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>moganoxritual_lab</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H58" s="1" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I58" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr"/>
-      <c r="L58" s="1" t="inlineStr"/>
-      <c r="M58" s="1" t="inlineStr"/>
-      <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr"/>
-      <c r="P58" s="1" t="inlineStr"/>
-      <c r="Q58" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R58" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>GBP aperto; Puntarella Rossa 17 marzo 2026 (sede Formello RM)</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>NUH Osteria Contemporanea</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Via della Missione, 56</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>0774/282912</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>www.nuhosteriacontemporanea.com</t>
         </is>
       </c>
-      <c r="E59" s="1" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>nuhosteriacontemporanea</t>
         </is>
       </c>
-      <c r="F59" s="1" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>nuhosteriacontemporanea</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="H59" s="1" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I59" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr"/>
-      <c r="L59" s="1" t="inlineStr"/>
-      <c r="M59" s="1" t="inlineStr"/>
-      <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr"/>
-      <c r="P59" s="1" t="inlineStr"/>
-      <c r="Q59" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R59" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>GBP aperto; TheFork 9.9/10; La Pecora Nera 2026 (sede Tivoli)</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -4346,114 +4238,128 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="1" t="inlineStr">
         <is>
           <t>Riccioli d'Oro</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="1" t="inlineStr">
         <is>
           <t>Via Conca d'Oro, 38</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>06/83797040</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="1" t="inlineStr">
         <is>
           <t>www.ristorantericciolidoro.it</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="1" t="inlineStr">
         <is>
           <t>profile.php?id=61551090176976</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="1" t="inlineStr">
         <is>
           <t>ristorantericciolidoro</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 16/04/2026</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="inlineStr"/>
+      <c r="K63" s="1" t="inlineStr"/>
+      <c r="L63" s="1" t="inlineStr"/>
+      <c r="M63" s="1" t="inlineStr"/>
+      <c r="N63" s="1" t="inlineStr"/>
+      <c r="O63" s="1" t="inlineStr"/>
+      <c r="P63" s="1" t="inlineStr"/>
+      <c r="Q63" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R63" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>Rimessa Roscioli</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="1" t="inlineStr">
         <is>
           <t>Via del Conservatorio, 58</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>06/68803914</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="1" t="inlineStr">
         <is>
           <t>www.rimessaroscioli.com</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="1" t="inlineStr">
         <is>
           <t>RimessaRoscioli</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="1" t="inlineStr">
         <is>
           <t>rimessaroscioli</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="G64" s="1" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 31/03/2026</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
+      <c r="H64" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J64" s="1" t="inlineStr"/>
+      <c r="K64" s="1" t="inlineStr"/>
+      <c r="L64" s="1" t="inlineStr"/>
+      <c r="M64" s="1" t="inlineStr"/>
+      <c r="N64" s="1" t="inlineStr"/>
+      <c r="O64" s="1" t="inlineStr"/>
+      <c r="P64" s="1" t="inlineStr"/>
+      <c r="Q64" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R64" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -4486,11 +4392,7 @@
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G65" s="1" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
@@ -4546,16 +4448,8 @@
           <t>moiristorante</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H66" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G66" s="1" t="inlineStr"/>
+      <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4610,16 +4504,8 @@
           <t>sintesi_ristorante</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H67" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G67" s="1" t="inlineStr"/>
+      <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4806,16 +4692,8 @@
           <t>tinello_bistrot</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H71" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G71" s="1" t="inlineStr"/>
+      <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4870,16 +4748,8 @@
           <t>toma52trattoriagourmet</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H72" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G72" s="1" t="inlineStr"/>
+      <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4934,16 +4804,8 @@
           <t>umaroma_restaurant</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H73" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G73" s="1" t="inlineStr"/>
+      <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5042,16 +4904,8 @@
           <t>266labarraca</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H75" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G75" s="1" t="inlineStr"/>
+      <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5150,16 +5004,6 @@
           <t>ristoranteaidueotri</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -5240,16 +5084,6 @@
       <c r="F78" t="inlineStr">
         <is>
           <t>alceppo</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>14/10/2025</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>N/D</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5422,16 +5256,8 @@
           <t>arcangelodandini</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H81" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G81" s="1" t="inlineStr"/>
+      <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5486,16 +5312,8 @@
           <t>armandoalpantheon</t>
         </is>
       </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H82" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G82" s="1" t="inlineStr"/>
+      <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5550,16 +5368,8 @@
           <t>aventina.roma</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G83" s="1" t="inlineStr"/>
+      <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5614,16 +5424,8 @@
           <t>baccanoroma</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H84" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G84" s="1" t="inlineStr"/>
+      <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5671,11 +5473,7 @@
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5726,16 +5524,8 @@
           <t>buccia_trattoria</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H86" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G86" s="1" t="inlineStr"/>
+      <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5790,16 +5580,8 @@
           <t>casaleverdeluna</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H87" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G87" s="1" t="inlineStr"/>
+      <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5854,16 +5636,8 @@
           <t>chaletdellago</t>
         </is>
       </c>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H88" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G88" s="1" t="inlineStr"/>
+      <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5918,16 +5692,8 @@
           <t>chinappi_roma</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H89" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G89" s="1" t="inlineStr"/>
+      <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5982,16 +5748,8 @@
           <t>contradarapello</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H90" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G90" s="1" t="inlineStr"/>
+      <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6042,16 +5800,8 @@
           <t>contrasto_viterbo</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H91" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G91" s="1" t="inlineStr"/>
+      <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6106,16 +5856,8 @@
           <t>fausto_ferrante_</t>
         </is>
       </c>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H92" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G92" s="1" t="inlineStr"/>
+      <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6170,16 +5912,8 @@
           <t>ristorantedamicheleroma</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H93" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G93" s="1" t="inlineStr"/>
+      <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6234,16 +5968,8 @@
           <t>denovo_e_dantico_lalocanda</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H94" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G94" s="1" t="inlineStr"/>
+      <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6294,11 +6020,7 @@
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr"/>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
@@ -6354,16 +6076,8 @@
           <t>friccico_roma</t>
         </is>
       </c>
-      <c r="G96" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H96" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G96" s="1" t="inlineStr"/>
+      <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6414,16 +6128,8 @@
           <t>gallo_ristorante</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H97" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G97" s="1" t="inlineStr"/>
+      <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6478,16 +6184,8 @@
           <t>ristorante_garibaldidal1970</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H98" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G98" s="1" t="inlineStr"/>
+      <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6542,16 +6240,8 @@
           <t>ilcaliceelastella</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G99" s="1" t="inlineStr"/>
+      <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6606,16 +6296,8 @@
           <t>Agristorante_ilcasaletto</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G100" s="1" t="inlineStr"/>
+      <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6714,16 +6396,8 @@
           <t>ristoranteilgrecale</t>
         </is>
       </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H102" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G102" s="1" t="inlineStr"/>
+      <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6774,16 +6448,8 @@
           <t>ilpacchero.solitario</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H103" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G103" s="1" t="inlineStr"/>
+      <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6838,16 +6504,8 @@
           <t>iltorchiofrascati</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H104" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G104" s="1" t="inlineStr"/>
+      <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6898,16 +6556,8 @@
           <t>iodio_roma</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H105" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G105" s="1" t="inlineStr"/>
+      <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6962,16 +6612,8 @@
           <t>la_baia_fregene_</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G106" s="1" t="inlineStr"/>
+      <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7040,57 +6682,56 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="1" t="inlineStr">
         <is>
           <t>La Galleria di Sopra</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="1" t="inlineStr">
         <is>
           <t>Via Leonardo Murialdo, 9</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>06/9322791</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="1" t="inlineStr">
         <is>
           <t>www.lagalleriadisopra.it</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E108" s="1" t="inlineStr">
         <is>
           <t>LaGalleriaDiSopra</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="1" t="inlineStr">
         <is>
           <t>lagalleriadisopra</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 11/04/2026</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr">
+      <c r="G108" s="1" t="inlineStr"/>
+      <c r="H108" s="1" t="inlineStr"/>
+      <c r="I108" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J108" s="1" t="inlineStr"/>
+      <c r="K108" s="1" t="inlineStr"/>
+      <c r="L108" s="1" t="inlineStr"/>
+      <c r="M108" s="1" t="inlineStr"/>
+      <c r="N108" s="1" t="inlineStr"/>
+      <c r="O108" s="1" t="inlineStr"/>
+      <c r="P108" s="1" t="inlineStr"/>
+      <c r="Q108" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R108" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -7127,16 +6768,8 @@
           <t>lalampara_passoscuro</t>
         </is>
       </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H109" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G109" s="1" t="inlineStr"/>
+      <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7191,16 +6824,8 @@
           <t>locandadelbere</t>
         </is>
       </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H110" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G110" s="1" t="inlineStr"/>
+      <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7251,11 +6876,7 @@
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr"/>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
@@ -7311,16 +6932,8 @@
           <t>la_palazzina_ristorante</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H112" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G112" s="1" t="inlineStr"/>
+      <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7345,57 +6958,56 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="1" t="inlineStr">
         <is>
           <t>La Quercia</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="1" t="inlineStr">
         <is>
           <t>Piazza della Quercia, 23</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>06/68300932</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" s="1" t="inlineStr">
         <is>
           <t>www.osterialaquercia.com</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="1" t="inlineStr">
         <is>
           <t>profile.php?id=100063755283530</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="1" t="inlineStr">
         <is>
           <t>laquerciaosteria</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
+      <c r="G113" s="1" t="inlineStr"/>
+      <c r="H113" s="1" t="inlineStr"/>
+      <c r="I113" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J113" s="1" t="inlineStr"/>
+      <c r="K113" s="1" t="inlineStr"/>
+      <c r="L113" s="1" t="inlineStr"/>
+      <c r="M113" s="1" t="inlineStr"/>
+      <c r="N113" s="1" t="inlineStr"/>
+      <c r="O113" s="1" t="inlineStr"/>
+      <c r="P113" s="1" t="inlineStr"/>
+      <c r="Q113" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R113" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -7428,16 +7040,8 @@
           <t>la_tavernadeicorsari</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H114" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G114" s="1" t="inlineStr"/>
+      <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7492,16 +7096,8 @@
           <t>ristorantelavillettaformia</t>
         </is>
       </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H115" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G115" s="1" t="inlineStr"/>
+      <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7556,16 +7152,8 @@
           <t>lisomariofficial</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H116" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G116" s="1" t="inlineStr"/>
+      <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7616,11 +7204,7 @@
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr"/>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G117" s="1" t="inlineStr"/>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
@@ -7676,16 +7260,8 @@
           <t>locanda.dorica</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H118" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G118" s="1" t="inlineStr"/>
+      <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7710,57 +7286,56 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="1" t="inlineStr">
         <is>
           <t>Locanda Nocera</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="1" t="inlineStr">
         <is>
           <t>Via Viggiano, 155</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>351/7590202</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="1" t="inlineStr">
         <is>
           <t>locandanocera.eatbu.com</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E119" s="1" t="inlineStr">
         <is>
           <t>locandanocera</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" s="1" t="inlineStr">
         <is>
           <t>locanda_nocera</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 03/04/2026</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr">
+      <c r="G119" s="1" t="inlineStr"/>
+      <c r="H119" s="1" t="inlineStr"/>
+      <c r="I119" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J119" s="1" t="inlineStr"/>
+      <c r="K119" s="1" t="inlineStr"/>
+      <c r="L119" s="1" t="inlineStr"/>
+      <c r="M119" s="1" t="inlineStr"/>
+      <c r="N119" s="1" t="inlineStr"/>
+      <c r="O119" s="1" t="inlineStr"/>
+      <c r="P119" s="1" t="inlineStr"/>
+      <c r="Q119" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R119" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
@@ -7797,16 +7372,8 @@
           <t>locandaruggieri</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G120" s="1" t="inlineStr"/>
+      <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7857,16 +7424,8 @@
           <t>losteria_di_ianus</t>
         </is>
       </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G121" s="1" t="inlineStr"/>
+      <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7921,16 +7480,8 @@
           <t>maksymovych_ristorante</t>
         </is>
       </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H122" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G122" s="1" t="inlineStr"/>
+      <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7981,16 +7532,8 @@
           <t>Mamma-Angelina</t>
         </is>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G123" s="1" t="inlineStr"/>
+      <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8041,16 +7584,8 @@
           <t>ristorantemammaorso</t>
         </is>
       </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G124" s="1" t="inlineStr"/>
+      <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8193,16 +7728,8 @@
           <t>mazzo_roma</t>
         </is>
       </c>
-      <c r="G127" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H127" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G127" s="1" t="inlineStr"/>
+      <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8257,11 +7784,7 @@
           <t>menabo_vino_e_cucina</t>
         </is>
       </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G128" s="1" t="inlineStr"/>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -2596,7 +2596,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="R60" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="R61" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="R62" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="R63" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4361,59 +4361,54 @@
       </c>
       <c r="R64" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Ristorante Delicato</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Via Umberto I, 2</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>0746/249202</t>
         </is>
       </c>
-      <c r="D65" s="1" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>www.ristorantedelicato.com</t>
         </is>
       </c>
-      <c r="E65" s="1" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>ristorantedelicato</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr"/>
-      <c r="I65" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr"/>
-      <c r="L65" s="1" t="inlineStr"/>
-      <c r="M65" s="1" t="inlineStr"/>
-      <c r="N65" s="1" t="inlineStr"/>
-      <c r="O65" s="1" t="inlineStr"/>
-      <c r="P65" s="1" t="inlineStr"/>
-      <c r="Q65" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R65" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 21/04/2026</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4448,8 +4443,16 @@
           <t>moiristorante</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4469,7 +4472,7 @@
       </c>
       <c r="R66" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4504,8 +4507,16 @@
           <t>sintesi_ristorante</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4525,7 +4536,7 @@
       </c>
       <c r="R67" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4580,7 @@
       </c>
       <c r="R68" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4624,7 @@
       </c>
       <c r="R69" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4668,7 @@
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4692,8 +4703,16 @@
           <t>tinello_bistrot</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4713,7 +4732,7 @@
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4748,8 +4767,16 @@
           <t>toma52trattoriagourmet</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4769,7 +4796,7 @@
       </c>
       <c r="R72" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4804,8 +4831,16 @@
           <t>umaroma_restaurant</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4825,7 +4860,7 @@
       </c>
       <c r="R73" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4904,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4904,8 +4939,16 @@
           <t>266labarraca</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4925,7 +4968,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4969,7 +5012,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5004,6 +5047,16 @@
           <t>ristoranteaidueotri</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -5084,6 +5137,16 @@
       <c r="F78" t="inlineStr">
         <is>
           <t>alceppo</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5177,7 +5240,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5284,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5256,8 +5319,16 @@
           <t>arcangelodandini</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5277,63 +5348,64 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Armando al Pantheon</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Salita dei Crescenzi, 31</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>06/68803034</t>
         </is>
       </c>
-      <c r="D82" s="1" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>www.armandoalpantheon.it</t>
         </is>
       </c>
-      <c r="E82" s="1" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>armandoalpantheon</t>
         </is>
       </c>
-      <c r="F82" s="1" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>armandoalpantheon</t>
         </is>
       </c>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr"/>
-      <c r="L82" s="1" t="inlineStr"/>
-      <c r="M82" s="1" t="inlineStr"/>
-      <c r="N82" s="1" t="inlineStr"/>
-      <c r="O82" s="1" t="inlineStr"/>
-      <c r="P82" s="1" t="inlineStr"/>
-      <c r="Q82" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R82" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 22/04/2026</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5368,8 +5440,16 @@
           <t>aventina.roma</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5389,7 +5469,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5424,8 +5504,16 @@
           <t>baccanoroma</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5445,7 +5533,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5561,11 @@
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
+      <c r="H85" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I85" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5493,7 +5585,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5524,8 +5616,16 @@
           <t>buccia_trattoria</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I86" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5545,7 +5645,7 @@
       </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5580,8 +5680,16 @@
           <t>casaleverdeluna</t>
         </is>
       </c>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H87" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I87" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5601,7 +5709,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5636,8 +5744,16 @@
           <t>chaletdellago</t>
         </is>
       </c>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H88" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I88" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5657,63 +5773,64 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Chinappi</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Via Augusto Valenziani, 19</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>06/4819005</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>www.chinappi.it</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>chinappiroma</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>chinappi_roma</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr">
-        <is>
-          <t>Chinappi</t>
-        </is>
-      </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>Via Augusto Valenziani, 19</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>06/4819005</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>www.chinappi.it</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>chinappiroma</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>chinappi_roma</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr"/>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
-      <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R89" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 20/04/2026</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5748,8 +5865,16 @@
           <t>contradarapello</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I90" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5769,7 +5894,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5800,8 +5925,16 @@
           <t>contrasto_viterbo</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I91" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5821,7 +5954,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5856,8 +5989,16 @@
           <t>fausto_ferrante_</t>
         </is>
       </c>
-      <c r="G92" s="1" t="inlineStr"/>
-      <c r="H92" s="1" t="inlineStr"/>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I92" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5877,7 +6018,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5912,8 +6053,16 @@
           <t>ristorantedamicheleroma</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I93" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5933,7 +6082,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5968,8 +6117,16 @@
           <t>denovo_e_dantico_lalocanda</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr"/>
-      <c r="H94" s="1" t="inlineStr"/>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H94" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I94" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5989,7 +6146,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6177,11 @@
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr"/>
-      <c r="G95" s="1" t="inlineStr"/>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
@@ -6041,7 +6202,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6076,8 +6237,16 @@
           <t>friccico_roma</t>
         </is>
       </c>
-      <c r="G96" s="1" t="inlineStr"/>
-      <c r="H96" s="1" t="inlineStr"/>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="H96" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I96" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6097,7 +6266,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6128,8 +6297,16 @@
           <t>gallo_ristorante</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I97" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6149,7 +6326,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6184,8 +6361,16 @@
           <t>ristorante_garibaldidal1970</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I98" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6205,63 +6390,64 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Il Calice e la Stella</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Piazza Garibaldi, 9</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>328/9024761</t>
         </is>
       </c>
-      <c r="D99" s="1" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>www.ilcalicelastella.it</t>
         </is>
       </c>
-      <c r="E99" s="1" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>ilcaliceelastella</t>
         </is>
       </c>
-      <c r="F99" s="1" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>ilcaliceelastella</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J99" s="1" t="inlineStr"/>
-      <c r="K99" s="1" t="inlineStr"/>
-      <c r="L99" s="1" t="inlineStr"/>
-      <c r="M99" s="1" t="inlineStr"/>
-      <c r="N99" s="1" t="inlineStr"/>
-      <c r="O99" s="1" t="inlineStr"/>
-      <c r="P99" s="1" t="inlineStr"/>
-      <c r="Q99" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R99" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 22/04/2026</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6296,8 +6482,16 @@
           <t>Agristorante_ilcasaletto</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr"/>
-      <c r="H100" s="1" t="inlineStr"/>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6317,7 +6511,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6555,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6396,8 +6590,16 @@
           <t>ristoranteilgrecale</t>
         </is>
       </c>
-      <c r="G102" s="1" t="inlineStr"/>
-      <c r="H102" s="1" t="inlineStr"/>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H102" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I102" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6417,7 +6619,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6448,8 +6650,16 @@
           <t>ilpacchero.solitario</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr"/>
-      <c r="H103" s="1" t="inlineStr"/>
+      <c r="G103" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H103" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I103" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6469,7 +6679,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6504,8 +6714,16 @@
           <t>iltorchiofrascati</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr"/>
-      <c r="H104" s="1" t="inlineStr"/>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I104" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6525,7 +6743,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6556,8 +6774,16 @@
           <t>iodio_roma</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" s="1" t="inlineStr"/>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I105" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6577,7 +6803,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6612,8 +6838,16 @@
           <t>la_baia_fregene_</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr"/>
-      <c r="H106" s="1" t="inlineStr"/>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6633,7 +6867,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6677,63 +6911,64 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>La Galleria di Sopra</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Via Leonardo Murialdo, 9</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>06/9322791</t>
         </is>
       </c>
-      <c r="D108" s="1" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>www.lagalleriadisopra.it</t>
         </is>
       </c>
-      <c r="E108" s="1" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>LaGalleriaDiSopra</t>
         </is>
       </c>
-      <c r="F108" s="1" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>lagalleriadisopra</t>
         </is>
       </c>
-      <c r="G108" s="1" t="inlineStr"/>
-      <c r="H108" s="1" t="inlineStr"/>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J108" s="1" t="inlineStr"/>
-      <c r="K108" s="1" t="inlineStr"/>
-      <c r="L108" s="1" t="inlineStr"/>
-      <c r="M108" s="1" t="inlineStr"/>
-      <c r="N108" s="1" t="inlineStr"/>
-      <c r="O108" s="1" t="inlineStr"/>
-      <c r="P108" s="1" t="inlineStr"/>
-      <c r="Q108" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R108" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 21/04/2026</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6768,8 +7003,16 @@
           <t>lalampara_passoscuro</t>
         </is>
       </c>
-      <c r="G109" s="1" t="inlineStr"/>
-      <c r="H109" s="1" t="inlineStr"/>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H109" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I109" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6789,7 +7032,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6824,8 +7067,16 @@
           <t>locandadelbere</t>
         </is>
       </c>
-      <c r="G110" s="1" t="inlineStr"/>
-      <c r="H110" s="1" t="inlineStr"/>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I110" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6845,7 +7096,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6876,7 +7127,11 @@
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr"/>
-      <c r="G111" s="1" t="inlineStr"/>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
@@ -6897,7 +7152,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6932,8 +7187,16 @@
           <t>la_palazzina_ristorante</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr"/>
-      <c r="H112" s="1" t="inlineStr"/>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H112" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6953,63 +7216,64 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>La Quercia</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>Piazza della Quercia, 23</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>06/68300932</t>
         </is>
       </c>
-      <c r="D113" s="1" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>www.osterialaquercia.com</t>
         </is>
       </c>
-      <c r="E113" s="1" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>profile.php?id=100063755283530</t>
         </is>
       </c>
-      <c r="F113" s="1" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>laquerciaosteria</t>
         </is>
       </c>
-      <c r="G113" s="1" t="inlineStr"/>
-      <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J113" s="1" t="inlineStr"/>
-      <c r="K113" s="1" t="inlineStr"/>
-      <c r="L113" s="1" t="inlineStr"/>
-      <c r="M113" s="1" t="inlineStr"/>
-      <c r="N113" s="1" t="inlineStr"/>
-      <c r="O113" s="1" t="inlineStr"/>
-      <c r="P113" s="1" t="inlineStr"/>
-      <c r="Q113" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R113" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7040,8 +7304,16 @@
           <t>la_tavernadeicorsari</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr"/>
-      <c r="H114" s="1" t="inlineStr"/>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I114" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7061,7 +7333,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7096,8 +7368,16 @@
           <t>ristorantelavillettaformia</t>
         </is>
       </c>
-      <c r="G115" s="1" t="inlineStr"/>
-      <c r="H115" s="1" t="inlineStr"/>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H115" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I115" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7117,7 +7397,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7152,8 +7432,16 @@
           <t>lisomariofficial</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr"/>
-      <c r="H116" s="1" t="inlineStr"/>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7173,7 +7461,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7492,11 @@
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr"/>
-      <c r="G117" s="1" t="inlineStr"/>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
@@ -7225,7 +7517,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7260,8 +7552,16 @@
           <t>locanda.dorica</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr"/>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7281,63 +7581,64 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>Locanda Nocera</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Via Viggiano, 155</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>351/7590202</t>
         </is>
       </c>
-      <c r="D119" s="1" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>locandanocera.eatbu.com</t>
         </is>
       </c>
-      <c r="E119" s="1" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>locandanocera</t>
         </is>
       </c>
-      <c r="F119" s="1" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>locanda_nocera</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr"/>
-      <c r="H119" s="1" t="inlineStr"/>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J119" s="1" t="inlineStr"/>
-      <c r="K119" s="1" t="inlineStr"/>
-      <c r="L119" s="1" t="inlineStr"/>
-      <c r="M119" s="1" t="inlineStr"/>
-      <c r="N119" s="1" t="inlineStr"/>
-      <c r="O119" s="1" t="inlineStr"/>
-      <c r="P119" s="1" t="inlineStr"/>
-      <c r="Q119" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R119" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 03/04/2026</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7372,8 +7673,16 @@
           <t>locandaruggieri</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr"/>
-      <c r="H120" s="1" t="inlineStr"/>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I120" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7393,7 +7702,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7424,8 +7733,16 @@
           <t>losteria_di_ianus</t>
         </is>
       </c>
-      <c r="G121" s="1" t="inlineStr"/>
-      <c r="H121" s="1" t="inlineStr"/>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H121" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I121" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7445,7 +7762,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7480,8 +7797,16 @@
           <t>maksymovych_ristorante</t>
         </is>
       </c>
-      <c r="G122" s="1" t="inlineStr"/>
-      <c r="H122" s="1" t="inlineStr"/>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I122" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7501,7 +7826,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7532,8 +7857,16 @@
           <t>Mamma-Angelina</t>
         </is>
       </c>
-      <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" s="1" t="inlineStr"/>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I123" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7553,7 +7886,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7584,8 +7917,16 @@
           <t>ristorantemammaorso</t>
         </is>
       </c>
-      <c r="G124" s="1" t="inlineStr"/>
-      <c r="H124" s="1" t="inlineStr"/>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I124" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7605,7 +7946,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7990,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7693,7 +8034,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7728,8 +8069,16 @@
           <t>mazzo_roma</t>
         </is>
       </c>
-      <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr"/>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7749,7 +8098,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7784,7 +8133,11 @@
           <t>menabo_vino_e_cucina</t>
         </is>
       </c>
-      <c r="G128" s="1" t="inlineStr"/>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
@@ -7805,7 +8158,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7861,7 +8214,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7917,7 +8270,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7973,7 +8326,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8370,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8414,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8466,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8522,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8570,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8626,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8674,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8377,7 +8730,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8786,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8842,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8898,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8954,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8998,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8689,7 +9042,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8745,7 +9098,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8801,7 +9154,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8853,7 +9206,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8909,7 +9262,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8953,7 +9306,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9362,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9406,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9097,7 +9450,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9506,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9562,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9618,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9309,7 +9662,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9718,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9774,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9826,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9874,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9926,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9982,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9685,7 +10038,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9737,7 +10090,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9793,7 +10146,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9837,7 +10190,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9893,7 +10246,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9937,7 +10290,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9993,7 +10346,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10402,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10458,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10514,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10558,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10257,7 +10610,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10654,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10710,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10762,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10465,7 +10818,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10862,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10914,7 @@
       </c>
       <c r="R181" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10970,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10661,7 +11014,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10717,7 +11070,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10769,7 +11122,7 @@
       </c>
       <c r="R185" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10813,7 +11166,7 @@
       </c>
       <c r="R186" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10869,7 +11222,7 @@
       </c>
       <c r="R187" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10925,7 +11278,7 @@
       </c>
       <c r="R188" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10981,7 +11334,7 @@
       </c>
       <c r="R189" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11378,7 @@
       </c>
       <c r="R190" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11434,7 @@
       </c>
       <c r="R191" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11486,7 @@
       </c>
       <c r="R192" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11542,7 @@
       </c>
       <c r="R193" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11598,7 @@
       </c>
       <c r="R194" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11654,7 @@
       </c>
       <c r="R195" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11357,7 +11710,7 @@
       </c>
       <c r="R196" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11762,7 @@
       </c>
       <c r="R197" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11818,7 @@
       </c>
       <c r="R198" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11521,7 +11874,7 @@
       </c>
       <c r="R199" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11918,7 @@
       </c>
       <c r="R200" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11974,7 @@
       </c>
       <c r="R201" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11677,7 +12030,7 @@
       </c>
       <c r="R202" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11733,7 +12086,7 @@
       </c>
       <c r="R203" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11789,7 +12142,7 @@
       </c>
       <c r="R204" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11845,7 +12198,7 @@
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11893,7 +12246,7 @@
       </c>
       <c r="R206" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -11949,7 +12302,7 @@
       </c>
       <c r="R207" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12358,7 @@
       </c>
       <c r="R208" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12402,7 @@
       </c>
       <c r="R209" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12446,7 @@
       </c>
       <c r="R210" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12149,7 +12502,7 @@
       </c>
       <c r="R211" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12205,7 +12558,7 @@
       </c>
       <c r="R212" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12261,7 +12614,7 @@
       </c>
       <c r="R213" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12670,7 @@
       </c>
       <c r="R214" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12373,7 +12726,7 @@
       </c>
       <c r="R215" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12778,7 @@
       </c>
       <c r="R216" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12834,7 @@
       </c>
       <c r="R217" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12684,7 +13037,7 @@
       </c>
       <c r="R220" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12728,7 +13081,7 @@
       </c>
       <c r="R221" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12784,7 +13137,7 @@
       </c>
       <c r="R222" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12840,7 +13193,7 @@
       </c>
       <c r="R223" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12896,7 +13249,7 @@
       </c>
       <c r="R224" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -12952,7 +13305,7 @@
       </c>
       <c r="R225" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13361,7 @@
       </c>
       <c r="R226" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13405,7 @@
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13461,7 @@
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13505,7 @@
       </c>
       <c r="R229" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13561,7 @@
       </c>
       <c r="R230" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13605,7 @@
       </c>
       <c r="R231" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13657,7 @@
       </c>
       <c r="R232" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13360,7 +13713,7 @@
       </c>
       <c r="R233" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13769,7 @@
       </c>
       <c r="R234" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13472,7 +13825,7 @@
       </c>
       <c r="R235" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13516,7 +13869,7 @@
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13568,7 +13921,7 @@
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13973,7 @@
       </c>
       <c r="R238" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13676,7 +14029,7 @@
       </c>
       <c r="R239" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13732,7 +14085,7 @@
       </c>
       <c r="R240" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13788,7 +14141,7 @@
       </c>
       <c r="R241" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13844,7 +14197,7 @@
       </c>
       <c r="R242" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13900,7 +14253,7 @@
       </c>
       <c r="R243" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -13956,7 +14309,7 @@
       </c>
       <c r="R244" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14365,7 @@
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14409,7 @@
       </c>
       <c r="R246" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14465,7 @@
       </c>
       <c r="R247" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14156,7 +14509,7 @@
       </c>
       <c r="R248" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14553,7 @@
       </c>
       <c r="R249" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14256,7 +14609,7 @@
       </c>
       <c r="R250" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14312,7 +14665,7 @@
       </c>
       <c r="R251" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14368,7 +14721,7 @@
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14773,7 @@
       </c>
       <c r="R253" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14829,7 @@
       </c>
       <c r="R254" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14532,7 +14885,7 @@
       </c>
       <c r="R255" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14941,7 @@
       </c>
       <c r="R256" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14644,7 +14997,7 @@
       </c>
       <c r="R257" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14700,7 +15053,7 @@
       </c>
       <c r="R258" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14756,7 +15109,7 @@
       </c>
       <c r="R259" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14812,7 +15165,7 @@
       </c>
       <c r="R260" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14860,7 +15213,7 @@
       </c>
       <c r="R261" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14912,7 +15265,7 @@
       </c>
       <c r="R262" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -14968,7 +15321,7 @@
       </c>
       <c r="R263" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15377,7 @@
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15433,7 @@
       </c>
       <c r="R265" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15485,7 @@
       </c>
       <c r="R266" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15537,7 @@
       </c>
       <c r="R267" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15228,7 +15581,7 @@
       </c>
       <c r="R268" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15633,7 @@
       </c>
       <c r="R269" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15685,7 @@
       </c>
       <c r="R270" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15729,7 @@
       </c>
       <c r="R271" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15773,7 @@
       </c>
       <c r="R272" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15476,7 +15829,7 @@
       </c>
       <c r="R273" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15881,7 @@
       </c>
       <c r="R274" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15584,7 +15937,7 @@
       </c>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15640,7 +15993,7 @@
       </c>
       <c r="R276" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15696,7 +16049,7 @@
       </c>
       <c r="R277" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15748,7 +16101,7 @@
       </c>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15804,7 +16157,7 @@
       </c>
       <c r="R279" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15860,7 +16213,7 @@
       </c>
       <c r="R280" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15908,7 +16261,7 @@
       </c>
       <c r="R281" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -15964,7 +16317,7 @@
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16020,7 +16373,7 @@
       </c>
       <c r="R283" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16072,7 +16425,7 @@
       </c>
       <c r="R284" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16465,7 @@
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16521,7 @@
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16573,7 @@
       </c>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16625,7 @@
       </c>
       <c r="R288" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16681,7 @@
       </c>
       <c r="R289" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16733,7 @@
       </c>
       <c r="R290" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16424,7 +16777,7 @@
       </c>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16821,7 @@
       </c>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16877,7 @@
       </c>
       <c r="R293" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16929,7 @@
       </c>
       <c r="R294" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16973,7 @@
       </c>
       <c r="R295" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16676,7 +17029,7 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16732,7 +17085,7 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16784,7 +17137,7 @@
       </c>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16836,7 +17189,7 @@
       </c>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16892,7 +17245,7 @@
       </c>
       <c r="R300" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16936,7 +17289,7 @@
       </c>
       <c r="R301" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -16984,7 +17337,7 @@
       </c>
       <c r="R302" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17040,7 +17393,7 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17096,7 +17449,7 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17144,7 +17497,7 @@
       </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17200,7 +17553,7 @@
       </c>
       <c r="R306" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17256,7 +17609,7 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17665,7 @@
       </c>
       <c r="R308" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17368,7 +17721,7 @@
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17777,7 @@
       </c>
       <c r="R310" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17833,7 @@
       </c>
       <c r="R311" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17889,7 @@
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17588,7 +17941,7 @@
       </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17644,7 +17997,7 @@
       </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17700,7 +18053,7 @@
       </c>
       <c r="R315" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17756,7 +18109,7 @@
       </c>
       <c r="R316" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17812,7 +18165,7 @@
       </c>
       <c r="R317" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17856,7 +18209,7 @@
       </c>
       <c r="R318" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17900,7 +18253,7 @@
       </c>
       <c r="R319" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -17944,7 +18297,7 @@
       </c>
       <c r="R320" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18353,7 @@
       </c>
       <c r="R321" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18056,7 +18409,7 @@
       </c>
       <c r="R322" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18112,7 +18465,7 @@
       </c>
       <c r="R323" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18164,7 +18517,7 @@
       </c>
       <c r="R324" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18220,7 +18573,7 @@
       </c>
       <c r="R325" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18276,7 +18629,7 @@
       </c>
       <c r="R326" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18320,7 +18673,7 @@
       </c>
       <c r="R327" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18376,7 +18729,7 @@
       </c>
       <c r="R328" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18432,7 +18785,7 @@
       </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18841,7 @@
       </c>
       <c r="R330" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18536,7 +18889,7 @@
       </c>
       <c r="R331" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18756,7 +19109,7 @@
       </c>
       <c r="R334" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18812,7 +19165,7 @@
       </c>
       <c r="R335" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18864,7 +19217,7 @@
       </c>
       <c r="R336" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18908,7 +19261,7 @@
       </c>
       <c r="R337" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -18964,7 +19317,7 @@
       </c>
       <c r="R338" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19016,7 +19369,7 @@
       </c>
       <c r="R339" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19072,7 +19425,7 @@
       </c>
       <c r="R340" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19116,7 +19469,7 @@
       </c>
       <c r="R341" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19160,7 +19513,7 @@
       </c>
       <c r="R342" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19208,7 +19561,7 @@
       </c>
       <c r="R343" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19264,7 +19617,7 @@
       </c>
       <c r="R344" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19312,7 +19665,7 @@
       </c>
       <c r="R345" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19356,7 +19709,7 @@
       </c>
       <c r="R346" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19412,7 +19765,7 @@
       </c>
       <c r="R347" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19464,7 +19817,7 @@
       </c>
       <c r="R348" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19869,7 @@
       </c>
       <c r="R349" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19572,7 +19925,7 @@
       </c>
       <c r="R350" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19616,7 +19969,7 @@
       </c>
       <c r="R351" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19672,7 +20025,7 @@
       </c>
       <c r="R352" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19724,7 +20077,7 @@
       </c>
       <c r="R353" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19780,7 +20133,7 @@
       </c>
       <c r="R354" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19836,7 +20189,7 @@
       </c>
       <c r="R355" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19892,7 +20245,7 @@
       </c>
       <c r="R356" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -19948,7 +20301,7 @@
       </c>
       <c r="R357" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20000,7 +20353,7 @@
       </c>
       <c r="R358" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20056,7 +20409,7 @@
       </c>
       <c r="R359" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20272,7 +20625,7 @@
       </c>
       <c r="R362" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20328,7 +20681,7 @@
       </c>
       <c r="R363" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20737,7 @@
       </c>
       <c r="R364" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20436,7 +20789,7 @@
       </c>
       <c r="R365" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20837,7 @@
       </c>
       <c r="R366" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20540,7 +20893,7 @@
       </c>
       <c r="R367" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20949,7 @@
       </c>
       <c r="R368" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20652,7 +21005,7 @@
       </c>
       <c r="R369" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20704,7 +21057,7 @@
       </c>
       <c r="R370" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20760,7 +21113,7 @@
       </c>
       <c r="R371" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20804,7 +21157,7 @@
       </c>
       <c r="R372" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20860,7 +21213,7 @@
       </c>
       <c r="R373" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20916,7 +21269,7 @@
       </c>
       <c r="R374" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -20972,7 +21325,7 @@
       </c>
       <c r="R375" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21381,7 @@
       </c>
       <c r="R376" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21084,7 +21437,7 @@
       </c>
       <c r="R377" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21136,7 +21489,7 @@
       </c>
       <c r="R378" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21533,7 @@
       </c>
       <c r="R379" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21236,7 +21589,7 @@
       </c>
       <c r="R380" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21288,7 +21641,7 @@
       </c>
       <c r="R381" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21697,7 @@
       </c>
       <c r="R382" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21396,7 +21749,7 @@
       </c>
       <c r="R383" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21448,7 +21801,7 @@
       </c>
       <c r="R384" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21857,7 @@
       </c>
       <c r="R385" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21560,7 +21913,7 @@
       </c>
       <c r="R386" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21965,7 @@
       </c>
       <c r="R387" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21668,7 +22021,7 @@
       </c>
       <c r="R388" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21724,7 +22077,7 @@
       </c>
       <c r="R389" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21776,7 +22129,7 @@
       </c>
       <c r="R390" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21820,7 +22173,7 @@
       </c>
       <c r="R391" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21876,7 +22229,7 @@
       </c>
       <c r="R392" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21932,7 +22285,7 @@
       </c>
       <c r="R393" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -21984,7 +22337,7 @@
       </c>
       <c r="R394" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22393,7 @@
       </c>
       <c r="R395" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22445,7 @@
       </c>
       <c r="R396" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22144,7 +22497,7 @@
       </c>
       <c r="R397" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22200,7 +22553,7 @@
       </c>
       <c r="R398" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22252,7 +22605,7 @@
       </c>
       <c r="R399" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22308,7 +22661,7 @@
       </c>
       <c r="R400" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22709,7 @@
       </c>
       <c r="R401" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22408,7 +22761,7 @@
       </c>
       <c r="R402" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22460,7 +22813,7 @@
       </c>
       <c r="R403" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22516,7 +22869,7 @@
       </c>
       <c r="R404" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22572,7 +22925,7 @@
       </c>
       <c r="R405" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22624,7 +22977,7 @@
       </c>
       <c r="R406" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22664,7 +23017,7 @@
       </c>
       <c r="R407" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22716,7 +23069,7 @@
       </c>
       <c r="R408" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22772,7 +23125,7 @@
       </c>
       <c r="R409" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22824,7 +23177,7 @@
       </c>
       <c r="R410" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22868,7 +23221,7 @@
       </c>
       <c r="R411" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22916,7 +23269,7 @@
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -22968,7 +23321,7 @@
       </c>
       <c r="R413" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -23024,7 +23377,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -23080,7 +23433,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -23136,7 +23489,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -23192,7 +23545,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -23248,7 +23601,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -23304,7 +23657,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -23360,7 +23713,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -2596,7 +2596,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="R60" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="R61" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="R62" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="R63" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="R64" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="R66" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="R67" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="R68" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="R69" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="R72" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="R73" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,11 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H128" s="1" t="inlineStr"/>
+      <c r="H128" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I128" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8158,7 +8162,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8193,8 +8197,16 @@
           <t>istorantemichelechinappi</t>
         </is>
       </c>
-      <c r="G129" s="1" t="inlineStr"/>
-      <c r="H129" s="1" t="inlineStr"/>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8214,7 +8226,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8249,8 +8261,16 @@
           <t>mile_pigneto</t>
         </is>
       </c>
-      <c r="G130" s="1" t="inlineStr"/>
-      <c r="H130" s="1" t="inlineStr"/>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H130" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I130" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8270,7 +8290,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8305,8 +8325,16 @@
           <t>_molo21</t>
         </is>
       </c>
-      <c r="G131" s="1" t="inlineStr"/>
-      <c r="H131" s="1" t="inlineStr"/>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8326,7 +8354,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8398,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8442,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8445,8 +8473,16 @@
           <t>mudejar_spiriti_e_cucina</t>
         </is>
       </c>
-      <c r="G134" s="1" t="inlineStr"/>
-      <c r="H134" s="1" t="inlineStr"/>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H134" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8466,63 +8502,64 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>Namo Ristobottega</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Via Giovan Battista Marzi, 1</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>0766/731637</t>
         </is>
       </c>
-      <c r="D135" s="1" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>www.namoristobottega.it</t>
         </is>
       </c>
-      <c r="E135" s="1" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>namoristobottegatarquinia</t>
         </is>
       </c>
-      <c r="F135" s="1" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>namo_ristobottega_tarquinia</t>
         </is>
       </c>
-      <c r="G135" s="1" t="inlineStr"/>
-      <c r="H135" s="1" t="inlineStr"/>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr"/>
-      <c r="K135" s="1" t="inlineStr"/>
-      <c r="L135" s="1" t="inlineStr"/>
-      <c r="M135" s="1" t="inlineStr"/>
-      <c r="N135" s="1" t="inlineStr"/>
-      <c r="O135" s="1" t="inlineStr"/>
-      <c r="P135" s="1" t="inlineStr"/>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R135" s="1" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 25/04/2026</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8587,11 @@
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr"/>
-      <c r="H136" s="1" t="inlineStr"/>
+      <c r="H136" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I136" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8570,7 +8611,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8605,8 +8646,16 @@
           <t>nuancucina</t>
         </is>
       </c>
-      <c r="G137" s="1" t="inlineStr"/>
-      <c r="H137" s="1" t="inlineStr"/>
+      <c r="G137" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H137" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8626,7 +8675,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8702,11 @@
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr"/>
-      <c r="G138" s="1" t="inlineStr"/>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
@@ -8674,7 +8727,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8709,8 +8762,16 @@
           <t>osteria_anna</t>
         </is>
       </c>
-      <c r="G139" s="1" t="inlineStr"/>
-      <c r="H139" s="1" t="inlineStr"/>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H139" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8730,7 +8791,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8765,8 +8826,16 @@
           <t>osteriadelborgocesano</t>
         </is>
       </c>
-      <c r="G140" s="1" t="inlineStr"/>
-      <c r="H140" s="1" t="inlineStr"/>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H140" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I140" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8786,7 +8855,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8821,8 +8890,16 @@
           <t>osteria_del_tempoperso</t>
         </is>
       </c>
-      <c r="G141" s="1" t="inlineStr"/>
-      <c r="H141" s="1" t="inlineStr"/>
+      <c r="G141" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H141" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I141" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8842,7 +8919,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8877,8 +8954,16 @@
           <t>osteriadimaccarese</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr"/>
-      <c r="H142" s="1" t="inlineStr"/>
+      <c r="G142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8898,7 +8983,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8933,8 +9018,16 @@
           <t>osterialabriciola</t>
         </is>
       </c>
-      <c r="G143" s="1" t="inlineStr"/>
-      <c r="H143" s="1" t="inlineStr"/>
+      <c r="G143" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H143" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I143" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8954,7 +9047,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8998,7 +9091,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9135,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9077,8 +9170,16 @@
           <t>ristorantepastorieroma</t>
         </is>
       </c>
-      <c r="G146" s="1" t="inlineStr"/>
-      <c r="H146" s="1" t="inlineStr"/>
+      <c r="G146" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H146" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I146" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9098,7 +9199,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9133,8 +9234,16 @@
           <t>trattoriapopina</t>
         </is>
       </c>
-      <c r="G147" s="1" t="inlineStr"/>
-      <c r="H147" s="1" t="inlineStr"/>
+      <c r="G147" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H147" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I147" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9154,7 +9263,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9185,8 +9294,16 @@
           <t>portoquadro_ristorante</t>
         </is>
       </c>
-      <c r="G148" s="1" t="inlineStr"/>
-      <c r="H148" s="1" t="inlineStr"/>
+      <c r="G148" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H148" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I148" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9206,7 +9323,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9241,8 +9358,16 @@
           <t>pratodisopra</t>
         </is>
       </c>
-      <c r="G149" s="1" t="inlineStr"/>
-      <c r="H149" s="1" t="inlineStr"/>
+      <c r="G149" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H149" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I149" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9262,7 +9387,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9431,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9341,8 +9466,16 @@
           <t>gli_angeli_gourmet</t>
         </is>
       </c>
-      <c r="G151" s="1" t="inlineStr"/>
-      <c r="H151" s="1" t="inlineStr"/>
+      <c r="G151" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H151" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I151" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9362,7 +9495,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9539,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9583,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9485,8 +9618,16 @@
           <t>scottadito_ristorante</t>
         </is>
       </c>
-      <c r="G154" s="1" t="inlineStr"/>
-      <c r="H154" s="1" t="inlineStr"/>
+      <c r="G154" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H154" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I154" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9506,7 +9647,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9541,8 +9682,16 @@
           <t>soramariaarcangelo</t>
         </is>
       </c>
-      <c r="G155" s="1" t="inlineStr"/>
-      <c r="H155" s="1" t="inlineStr"/>
+      <c r="G155" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H155" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I155" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9562,7 +9711,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9597,8 +9746,16 @@
           <t>fabiolissimasultram</t>
         </is>
       </c>
-      <c r="G156" s="1" t="inlineStr"/>
-      <c r="H156" s="1" t="inlineStr"/>
+      <c r="G156" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H156" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I156" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9618,7 +9775,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9819,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9697,8 +9854,16 @@
           <t>trattoria-del-pesce</t>
         </is>
       </c>
-      <c r="G158" s="1" t="inlineStr"/>
-      <c r="H158" s="1" t="inlineStr"/>
+      <c r="G158" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H158" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I158" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9718,7 +9883,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9753,8 +9918,16 @@
           <t>trattoriadellafortuna</t>
         </is>
       </c>
-      <c r="G159" s="1" t="inlineStr"/>
-      <c r="H159" s="1" t="inlineStr"/>
+      <c r="G159" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H159" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I159" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9774,7 +9947,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9805,8 +9978,16 @@
           <t>trattoriaenotecaassunta</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr"/>
-      <c r="H160" s="1" t="inlineStr"/>
+      <c r="G160" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H160" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I160" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9826,7 +10007,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9853,7 +10034,11 @@
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr"/>
-      <c r="G161" s="1" t="inlineStr"/>
+      <c r="G161" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H161" s="1" t="inlineStr"/>
       <c r="I161" s="1" t="inlineStr">
         <is>
@@ -9874,7 +10059,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9905,8 +10090,16 @@
           <t>vineria_cesare</t>
         </is>
       </c>
-      <c r="G162" s="1" t="inlineStr"/>
-      <c r="H162" s="1" t="inlineStr"/>
+      <c r="G162" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H162" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9926,7 +10119,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9961,8 +10154,16 @@
           <t>ristorantezeromiglia</t>
         </is>
       </c>
-      <c r="G163" s="1" t="inlineStr"/>
-      <c r="H163" s="1" t="inlineStr"/>
+      <c r="G163" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H163" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I163" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9982,7 +10183,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10017,8 +10218,16 @@
           <t>labarriquemonti</t>
         </is>
       </c>
-      <c r="G164" s="1" t="inlineStr"/>
-      <c r="H164" s="1" t="inlineStr"/>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H164" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I164" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10038,7 +10247,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10069,8 +10278,16 @@
           <t>latteria_trastevere</t>
         </is>
       </c>
-      <c r="G165" s="1" t="inlineStr"/>
-      <c r="H165" s="1" t="inlineStr"/>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I165" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10090,7 +10307,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10125,8 +10342,16 @@
           <t>roscioliroma</t>
         </is>
       </c>
-      <c r="G166" s="1" t="inlineStr"/>
-      <c r="H166" s="1" t="inlineStr"/>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H166" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I166" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10146,7 +10371,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10415,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10225,8 +10450,16 @@
           <t>trattoriadacesare</t>
         </is>
       </c>
-      <c r="G168" s="1" t="inlineStr"/>
-      <c r="H168" s="1" t="inlineStr"/>
+      <c r="G168" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H168" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I168" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10246,7 +10479,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10523,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10325,8 +10558,16 @@
           <t>daenzoal29</t>
         </is>
       </c>
-      <c r="G170" s="1" t="inlineStr"/>
-      <c r="H170" s="1" t="inlineStr"/>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I170" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10346,7 +10587,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10381,8 +10622,16 @@
           <t>feliceatestaccio</t>
         </is>
       </c>
-      <c r="G171" s="1" t="inlineStr"/>
-      <c r="H171" s="1" t="inlineStr"/>
+      <c r="G171" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I171" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10402,7 +10651,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10437,8 +10686,16 @@
           <t>velavevodetto</t>
         </is>
       </c>
-      <c r="G172" s="1" t="inlineStr"/>
-      <c r="H172" s="1" t="inlineStr"/>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I172" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10458,7 +10715,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10493,8 +10750,16 @@
           <t>Grappolo_d_Oro-Rome_Lazio</t>
         </is>
       </c>
-      <c r="G173" s="1" t="inlineStr"/>
-      <c r="H173" s="1" t="inlineStr"/>
+      <c r="G173" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H173" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I173" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10514,7 +10779,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10823,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10589,8 +10854,16 @@
           <t>osteria.iotto</t>
         </is>
       </c>
-      <c r="G175" s="1" t="inlineStr"/>
-      <c r="H175" s="1" t="inlineStr"/>
+      <c r="G175" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H175" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I175" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10610,7 +10883,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10927,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10689,8 +10962,16 @@
           <t>latavernacciaroma</t>
         </is>
       </c>
-      <c r="G177" s="1" t="inlineStr"/>
-      <c r="H177" s="1" t="inlineStr"/>
+      <c r="G177" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H177" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I177" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10710,7 +10991,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10741,8 +11022,16 @@
           <t>mangiadischi_roma</t>
         </is>
       </c>
-      <c r="G178" s="1" t="inlineStr"/>
-      <c r="H178" s="1" t="inlineStr"/>
+      <c r="G178" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H178" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I178" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10762,7 +11051,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10797,8 +11086,16 @@
           <t>nantrocalicietaglieri</t>
         </is>
       </c>
-      <c r="G179" s="1" t="inlineStr"/>
-      <c r="H179" s="1" t="inlineStr"/>
+      <c r="G179" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H179" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I179" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10818,7 +11115,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10862,59 +11159,59 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="inlineStr">
+      <c r="A181" t="inlineStr">
         <is>
           <t>Osteria Bonelli</t>
         </is>
       </c>
-      <c r="B181" s="1" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Viale dell'Acquedotto Alessandrino, 172/174</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>329/8633077</t>
         </is>
       </c>
-      <c r="D181" s="1" t="inlineStr"/>
-      <c r="E181" s="1" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>Osteria-Bonelli</t>
         </is>
       </c>
-      <c r="F181" s="1" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>osteriabonelli</t>
         </is>
       </c>
-      <c r="G181" s="1" t="inlineStr"/>
-      <c r="H181" s="1" t="inlineStr"/>
-      <c r="I181" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J181" s="1" t="inlineStr"/>
-      <c r="K181" s="1" t="inlineStr"/>
-      <c r="L181" s="1" t="inlineStr"/>
-      <c r="M181" s="1" t="inlineStr"/>
-      <c r="N181" s="1" t="inlineStr"/>
-      <c r="O181" s="1" t="inlineStr"/>
-      <c r="P181" s="1" t="inlineStr"/>
-      <c r="Q181" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R181" s="1" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 27/04/2026</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10949,8 +11246,16 @@
           <t>osteria_del_velodromo_vecchio</t>
         </is>
       </c>
-      <c r="G182" s="1" t="inlineStr"/>
-      <c r="H182" s="1" t="inlineStr"/>
+      <c r="G182" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H182" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I182" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10970,7 +11275,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11319,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11049,8 +11354,16 @@
           <t>osteriafratellimori</t>
         </is>
       </c>
-      <c r="G184" s="1" t="inlineStr"/>
-      <c r="H184" s="1" t="inlineStr"/>
+      <c r="G184" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H184" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I184" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11070,7 +11383,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11415,11 @@
         </is>
       </c>
       <c r="G185" s="1" t="inlineStr"/>
-      <c r="H185" s="1" t="inlineStr"/>
+      <c r="H185" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I185" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11122,7 +11439,7 @@
       </c>
       <c r="R185" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11483,7 @@
       </c>
       <c r="R186" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11201,8 +11518,16 @@
           <t>prolocotrastevere</t>
         </is>
       </c>
-      <c r="G187" s="1" t="inlineStr"/>
-      <c r="H187" s="1" t="inlineStr"/>
+      <c r="G187" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H187" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I187" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11222,63 +11547,64 @@
       </c>
       <c r="R187" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="inlineStr">
+      <c r="A188" t="inlineStr">
         <is>
           <t>Rosina - cucina di casa</t>
         </is>
       </c>
-      <c r="B188" s="1" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Vicolo delle Grotte, 27</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>06/69374499</t>
         </is>
       </c>
-      <c r="D188" s="1" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>www.rosinacucinadicasa.com</t>
         </is>
       </c>
-      <c r="E188" s="1" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>profile.php?id=100090475848922</t>
         </is>
       </c>
-      <c r="F188" s="1" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>rosina_cucina_di_casa</t>
         </is>
       </c>
-      <c r="G188" s="1" t="inlineStr"/>
-      <c r="H188" s="1" t="inlineStr"/>
-      <c r="I188" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J188" s="1" t="inlineStr"/>
-      <c r="K188" s="1" t="inlineStr"/>
-      <c r="L188" s="1" t="inlineStr"/>
-      <c r="M188" s="1" t="inlineStr"/>
-      <c r="N188" s="1" t="inlineStr"/>
-      <c r="O188" s="1" t="inlineStr"/>
-      <c r="P188" s="1" t="inlineStr"/>
-      <c r="Q188" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R188" s="1" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 27/04/2026</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11313,8 +11639,16 @@
           <t>santopalatoroma</t>
         </is>
       </c>
-      <c r="G189" s="1" t="inlineStr"/>
-      <c r="H189" s="1" t="inlineStr"/>
+      <c r="G189" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H189" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I189" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11334,7 +11668,7 @@
       </c>
       <c r="R189" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11712,7 @@
       </c>
       <c r="R190" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11413,8 +11747,16 @@
           <t>trattoriadelcimino</t>
         </is>
       </c>
-      <c r="G191" s="1" t="inlineStr"/>
-      <c r="H191" s="1" t="inlineStr"/>
+      <c r="G191" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H191" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I191" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11434,7 +11776,7 @@
       </c>
       <c r="R191" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11465,8 +11807,16 @@
           <t>trecca_roma</t>
         </is>
       </c>
-      <c r="G192" s="1" t="inlineStr"/>
-      <c r="H192" s="1" t="inlineStr"/>
+      <c r="G192" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H192" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I192" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11486,7 +11836,7 @@
       </c>
       <c r="R192" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11521,8 +11871,16 @@
           <t>aiki.pub</t>
         </is>
       </c>
-      <c r="G193" s="1" t="inlineStr"/>
-      <c r="H193" s="1" t="inlineStr"/>
+      <c r="G193" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H193" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I193" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11542,7 +11900,7 @@
       </c>
       <c r="R193" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11577,8 +11935,16 @@
           <t>casalocaroma</t>
         </is>
       </c>
-      <c r="G194" s="1" t="inlineStr"/>
-      <c r="H194" s="1" t="inlineStr"/>
+      <c r="G194" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H194" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I194" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11598,7 +11964,7 @@
       </c>
       <c r="R194" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11633,8 +11999,16 @@
           <t>darbasharistorante</t>
         </is>
       </c>
-      <c r="G195" s="1" t="inlineStr"/>
-      <c r="H195" s="1" t="inlineStr"/>
+      <c r="G195" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H195" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I195" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11654,7 +12028,7 @@
       </c>
       <c r="R195" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11689,8 +12063,16 @@
           <t>galbiroma</t>
         </is>
       </c>
-      <c r="G196" s="1" t="inlineStr"/>
-      <c r="H196" s="1" t="inlineStr"/>
+      <c r="G196" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H196" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I196" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11710,7 +12092,7 @@
       </c>
       <c r="R196" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11741,7 +12123,11 @@
         </is>
       </c>
       <c r="F197" s="1" t="inlineStr"/>
-      <c r="G197" s="1" t="inlineStr"/>
+      <c r="G197" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H197" s="1" t="inlineStr"/>
       <c r="I197" s="1" t="inlineStr">
         <is>
@@ -11762,7 +12148,7 @@
       </c>
       <c r="R197" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11797,8 +12183,16 @@
           <t>hasekuraroma</t>
         </is>
       </c>
-      <c r="G198" s="1" t="inlineStr"/>
-      <c r="H198" s="1" t="inlineStr"/>
+      <c r="G198" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H198" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I198" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11818,7 +12212,7 @@
       </c>
       <c r="R198" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11853,8 +12247,16 @@
           <t>hiromimaison</t>
         </is>
       </c>
-      <c r="G199" s="1" t="inlineStr"/>
-      <c r="H199" s="1" t="inlineStr"/>
+      <c r="G199" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H199" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I199" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11874,7 +12276,7 @@
       </c>
       <c r="R199" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11918,7 +12320,7 @@
       </c>
       <c r="R200" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -11953,8 +12355,16 @@
           <t>kohakurome</t>
         </is>
       </c>
-      <c r="G201" s="1" t="inlineStr"/>
-      <c r="H201" s="1" t="inlineStr"/>
+      <c r="G201" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H201" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I201" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -11974,7 +12384,7 @@
       </c>
       <c r="R201" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12009,8 +12419,16 @@
           <t>expendiodeagave</t>
         </is>
       </c>
-      <c r="G202" s="1" t="inlineStr"/>
-      <c r="H202" s="1" t="inlineStr"/>
+      <c r="G202" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H202" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I202" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12030,7 +12448,7 @@
       </c>
       <c r="R202" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12065,8 +12483,16 @@
           <t>larenardiereaventino</t>
         </is>
       </c>
-      <c r="G203" s="1" t="inlineStr"/>
-      <c r="H203" s="1" t="inlineStr"/>
+      <c r="G203" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H203" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I203" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12086,7 +12512,7 @@
       </c>
       <c r="R203" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12121,8 +12547,16 @@
           <t>ristorante.lin</t>
         </is>
       </c>
-      <c r="G204" s="1" t="inlineStr"/>
-      <c r="H204" s="1" t="inlineStr"/>
+      <c r="G204" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H204" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I204" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12142,7 +12576,7 @@
       </c>
       <c r="R204" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12177,8 +12611,16 @@
           <t>mamayaramen</t>
         </is>
       </c>
-      <c r="G205" s="1" t="inlineStr"/>
-      <c r="H205" s="1" t="inlineStr"/>
+      <c r="G205" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H205" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I205" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12198,7 +12640,7 @@
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12668,11 @@
         </is>
       </c>
       <c r="G206" s="1" t="inlineStr"/>
-      <c r="H206" s="1" t="inlineStr"/>
+      <c r="H206" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I206" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12246,7 +12692,7 @@
       </c>
       <c r="R206" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12281,8 +12727,16 @@
           <t>mifang_roma</t>
         </is>
       </c>
-      <c r="G207" s="1" t="inlineStr"/>
-      <c r="H207" s="1" t="inlineStr"/>
+      <c r="G207" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H207" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I207" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12302,7 +12756,7 @@
       </c>
       <c r="R207" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12337,8 +12791,16 @@
           <t>mikachan_ristorante_giapponese</t>
         </is>
       </c>
-      <c r="G208" s="1" t="inlineStr"/>
-      <c r="H208" s="1" t="inlineStr"/>
+      <c r="G208" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H208" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I208" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12358,7 +12820,7 @@
       </c>
       <c r="R208" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12864,7 @@
       </c>
       <c r="R209" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12908,7 @@
       </c>
       <c r="R210" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12481,8 +12943,16 @@
           <t>oolong_roma</t>
         </is>
       </c>
-      <c r="G211" s="1" t="inlineStr"/>
-      <c r="H211" s="1" t="inlineStr"/>
+      <c r="G211" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H211" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I211" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12502,7 +12972,7 @@
       </c>
       <c r="R211" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12537,8 +13007,16 @@
           <t>sakanasushiroma</t>
         </is>
       </c>
-      <c r="G212" s="1" t="inlineStr"/>
-      <c r="H212" s="1" t="inlineStr"/>
+      <c r="G212" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H212" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I212" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12558,7 +13036,7 @@
       </c>
       <c r="R212" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12593,8 +13071,16 @@
           <t>sinosteria</t>
         </is>
       </c>
-      <c r="G213" s="1" t="inlineStr"/>
-      <c r="H213" s="1" t="inlineStr"/>
+      <c r="G213" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H213" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I213" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12614,7 +13100,7 @@
       </c>
       <c r="R213" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12649,8 +13135,16 @@
           <t>song_dimsum</t>
         </is>
       </c>
-      <c r="G214" s="1" t="inlineStr"/>
-      <c r="H214" s="1" t="inlineStr"/>
+      <c r="G214" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H214" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I214" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12670,7 +13164,7 @@
       </c>
       <c r="R214" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12705,8 +13199,16 @@
           <t>sushisen_roma</t>
         </is>
       </c>
-      <c r="G215" s="1" t="inlineStr"/>
-      <c r="H215" s="1" t="inlineStr"/>
+      <c r="G215" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H215" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I215" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12726,7 +13228,7 @@
       </c>
       <c r="R215" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12757,8 +13259,16 @@
           <t>umami_roma</t>
         </is>
       </c>
-      <c r="G216" s="1" t="inlineStr"/>
-      <c r="H216" s="1" t="inlineStr"/>
+      <c r="G216" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H216" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I216" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12778,7 +13288,7 @@
       </c>
       <c r="R216" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12813,8 +13323,16 @@
           <t>Waraku</t>
         </is>
       </c>
-      <c r="G217" s="1" t="inlineStr"/>
-      <c r="H217" s="1" t="inlineStr"/>
+      <c r="G217" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H217" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I217" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -12834,7 +13352,7 @@
       </c>
       <c r="R217" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -12869,6 +13387,16 @@
           <t>180grammipizzeriaromana</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I218" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -12944,6 +13472,16 @@
       <c r="F219" t="inlineStr">
         <is>
           <t>arotapizzeria</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13037,7 +13575,7 @@
       </c>
       <c r="R220" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13081,7 +13619,7 @@
       </c>
       <c r="R221" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13116,8 +13654,16 @@
           <t>avenidacalo</t>
         </is>
       </c>
-      <c r="G222" s="1" t="inlineStr"/>
-      <c r="H222" s="1" t="inlineStr"/>
+      <c r="G222" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H222" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I222" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13137,7 +13683,7 @@
       </c>
       <c r="R222" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13172,8 +13718,16 @@
           <t>baccioeigradini</t>
         </is>
       </c>
-      <c r="G223" s="1" t="inlineStr"/>
-      <c r="H223" s="1" t="inlineStr"/>
+      <c r="G223" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H223" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I223" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13193,7 +13747,7 @@
       </c>
       <c r="R223" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13228,8 +13782,16 @@
           <t>berbereroma</t>
         </is>
       </c>
-      <c r="G224" s="1" t="inlineStr"/>
-      <c r="H224" s="1" t="inlineStr"/>
+      <c r="G224" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H224" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I224" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13249,7 +13811,7 @@
       </c>
       <c r="R224" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13284,8 +13846,16 @@
           <t>brucio_lacontemporanea</t>
         </is>
       </c>
-      <c r="G225" s="1" t="inlineStr"/>
-      <c r="H225" s="1" t="inlineStr"/>
+      <c r="G225" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H225" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I225" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13305,7 +13875,7 @@
       </c>
       <c r="R225" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13340,8 +13910,16 @@
           <t>brucio_roma</t>
         </is>
       </c>
-      <c r="G226" s="1" t="inlineStr"/>
-      <c r="H226" s="1" t="inlineStr"/>
+      <c r="G226" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H226" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I226" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13361,7 +13939,7 @@
       </c>
       <c r="R226" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13983,7 @@
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13440,8 +14018,16 @@
           <t>crunch_roma</t>
         </is>
       </c>
-      <c r="G228" s="1" t="inlineStr"/>
-      <c r="H228" s="1" t="inlineStr"/>
+      <c r="G228" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H228" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I228" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13461,7 +14047,7 @@
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13505,7 +14091,7 @@
       </c>
       <c r="R229" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13540,8 +14126,16 @@
           <t>dazio_roma</t>
         </is>
       </c>
-      <c r="G230" s="1" t="inlineStr"/>
-      <c r="H230" s="1" t="inlineStr"/>
+      <c r="G230" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H230" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I230" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13561,7 +14155,7 @@
       </c>
       <c r="R230" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13605,7 +14199,7 @@
       </c>
       <c r="R231" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13636,8 +14230,16 @@
           <t>extremis_rome</t>
         </is>
       </c>
-      <c r="G232" s="1" t="inlineStr"/>
-      <c r="H232" s="1" t="inlineStr"/>
+      <c r="G232" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H232" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I232" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13657,7 +14259,7 @@
       </c>
       <c r="R232" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13692,8 +14294,16 @@
           <t>farine_la_pizza</t>
         </is>
       </c>
-      <c r="G233" s="1" t="inlineStr"/>
-      <c r="H233" s="1" t="inlineStr"/>
+      <c r="G233" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H233" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I233" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13713,7 +14323,7 @@
       </c>
       <c r="R233" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13748,8 +14358,16 @@
           <t>fermentum_roma</t>
         </is>
       </c>
-      <c r="G234" s="1" t="inlineStr"/>
-      <c r="H234" s="1" t="inlineStr"/>
+      <c r="G234" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H234" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I234" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13769,7 +14387,7 @@
       </c>
       <c r="R234" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13804,8 +14422,16 @@
           <t>gianpapizzeria</t>
         </is>
       </c>
-      <c r="G235" s="1" t="inlineStr"/>
-      <c r="H235" s="1" t="inlineStr"/>
+      <c r="G235" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H235" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I235" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13825,7 +14451,7 @@
       </c>
       <c r="R235" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13869,7 +14495,7 @@
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13900,8 +14526,16 @@
           <t>iquintiliroma</t>
         </is>
       </c>
-      <c r="G237" s="1" t="inlineStr"/>
-      <c r="H237" s="1" t="inlineStr"/>
+      <c r="G237" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H237" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I237" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13921,7 +14555,7 @@
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -13952,8 +14586,16 @@
           <t>ilmaratoneta_roma</t>
         </is>
       </c>
-      <c r="G238" s="1" t="inlineStr"/>
-      <c r="H238" s="1" t="inlineStr"/>
+      <c r="G238" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H238" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I238" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -13973,7 +14615,7 @@
       </c>
       <c r="R238" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14008,8 +14650,16 @@
           <t>infucina_edoardopapa</t>
         </is>
       </c>
-      <c r="G239" s="1" t="inlineStr"/>
-      <c r="H239" s="1" t="inlineStr"/>
+      <c r="G239" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H239" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I239" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14029,7 +14679,7 @@
       </c>
       <c r="R239" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14064,8 +14714,16 @@
           <t>lagattamangiona</t>
         </is>
       </c>
-      <c r="G240" s="1" t="inlineStr"/>
-      <c r="H240" s="1" t="inlineStr"/>
+      <c r="G240" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H240" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I240" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14085,7 +14743,7 @@
       </c>
       <c r="R240" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14120,8 +14778,16 @@
           <t>elementaretrastevere</t>
         </is>
       </c>
-      <c r="G241" s="1" t="inlineStr"/>
-      <c r="H241" s="1" t="inlineStr"/>
+      <c r="G241" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H241" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I241" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14141,7 +14807,7 @@
       </c>
       <c r="R241" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14176,8 +14842,16 @@
           <t>pizzeria_magnifica</t>
         </is>
       </c>
-      <c r="G242" s="1" t="inlineStr"/>
-      <c r="H242" s="1" t="inlineStr"/>
+      <c r="G242" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H242" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I242" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14197,7 +14871,7 @@
       </c>
       <c r="R242" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14232,8 +14906,16 @@
           <t>pizzamater</t>
         </is>
       </c>
-      <c r="G243" s="1" t="inlineStr"/>
-      <c r="H243" s="1" t="inlineStr"/>
+      <c r="G243" s="1" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="H243" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I243" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14253,7 +14935,7 @@
       </c>
       <c r="R243" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14288,8 +14970,16 @@
           <t>mia.pizzeria.creativa</t>
         </is>
       </c>
-      <c r="G244" s="1" t="inlineStr"/>
-      <c r="H244" s="1" t="inlineStr"/>
+      <c r="G244" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H244" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I244" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14309,7 +14999,7 @@
       </c>
       <c r="R244" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14344,8 +15034,16 @@
           <t>piccolobucoroma</t>
         </is>
       </c>
-      <c r="G245" s="1" t="inlineStr"/>
-      <c r="H245" s="1" t="inlineStr"/>
+      <c r="G245" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H245" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I245" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14365,7 +15063,7 @@
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14409,63 +15107,64 @@
       </c>
       <c r="R246" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="inlineStr">
+      <c r="A247" t="inlineStr">
         <is>
           <t>Santa Pizza</t>
         </is>
       </c>
-      <c r="B247" s="1" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>Via di Villa Faonte, 94</t>
         </is>
       </c>
-      <c r="C247" s="1" t="inlineStr">
+      <c r="C247" t="inlineStr">
         <is>
           <t>06/85951563</t>
         </is>
       </c>
-      <c r="D247" s="1" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>www.santapizzaroma.it</t>
         </is>
       </c>
-      <c r="E247" s="1" t="inlineStr">
+      <c r="E247" t="inlineStr">
         <is>
           <t>profile.php?id=100087051387864</t>
         </is>
       </c>
-      <c r="F247" s="1" t="inlineStr">
+      <c r="F247" t="inlineStr">
         <is>
           <t>santapizzaroma</t>
         </is>
       </c>
-      <c r="G247" s="1" t="inlineStr"/>
-      <c r="H247" s="1" t="inlineStr"/>
-      <c r="I247" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J247" s="1" t="inlineStr"/>
-      <c r="K247" s="1" t="inlineStr"/>
-      <c r="L247" s="1" t="inlineStr"/>
-      <c r="M247" s="1" t="inlineStr"/>
-      <c r="N247" s="1" t="inlineStr"/>
-      <c r="O247" s="1" t="inlineStr"/>
-      <c r="P247" s="1" t="inlineStr"/>
-      <c r="Q247" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R247" s="1" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 22/04/2026</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14509,7 +15208,7 @@
       </c>
       <c r="R248" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14553,7 +15252,7 @@
       </c>
       <c r="R249" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14588,8 +15287,16 @@
           <t>spiazzoroma</t>
         </is>
       </c>
-      <c r="G250" s="1" t="inlineStr"/>
-      <c r="H250" s="1" t="inlineStr"/>
+      <c r="G250" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H250" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I250" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14609,7 +15316,7 @@
       </c>
       <c r="R250" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14644,8 +15351,16 @@
           <t>svario_pizzabar</t>
         </is>
       </c>
-      <c r="G251" s="1" t="inlineStr"/>
-      <c r="H251" s="1" t="inlineStr"/>
+      <c r="G251" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H251" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I251" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14665,7 +15380,7 @@
       </c>
       <c r="R251" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14700,8 +15415,16 @@
           <t>tacthinandcrunchy</t>
         </is>
       </c>
-      <c r="G252" s="1" t="inlineStr"/>
-      <c r="H252" s="1" t="inlineStr"/>
+      <c r="G252" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H252" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I252" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14721,7 +15444,7 @@
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14752,8 +15475,16 @@
           <t>tondapizzeria</t>
         </is>
       </c>
-      <c r="G253" s="1" t="inlineStr"/>
-      <c r="H253" s="1" t="inlineStr"/>
+      <c r="G253" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H253" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I253" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14773,7 +15504,7 @@
       </c>
       <c r="R253" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14808,8 +15539,16 @@
           <t>artigianodelcaffe</t>
         </is>
       </c>
-      <c r="G254" s="1" t="inlineStr"/>
-      <c r="H254" s="1" t="inlineStr"/>
+      <c r="G254" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H254" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I254" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14829,7 +15568,7 @@
       </c>
       <c r="R254" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14864,8 +15603,16 @@
           <t>bap__roma</t>
         </is>
       </c>
-      <c r="G255" s="1" t="inlineStr"/>
-      <c r="H255" s="1" t="inlineStr"/>
+      <c r="G255" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H255" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I255" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14885,7 +15632,7 @@
       </c>
       <c r="R255" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14920,8 +15667,16 @@
           <t>barnumroma</t>
         </is>
       </c>
-      <c r="G256" s="1" t="inlineStr"/>
-      <c r="H256" s="1" t="inlineStr"/>
+      <c r="G256" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H256" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I256" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14941,7 +15696,7 @@
       </c>
       <c r="R256" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -14976,8 +15731,16 @@
           <t>cafemerenda_roma</t>
         </is>
       </c>
-      <c r="G257" s="1" t="inlineStr"/>
-      <c r="H257" s="1" t="inlineStr"/>
+      <c r="G257" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H257" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I257" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -14997,7 +15760,7 @@
       </c>
       <c r="R257" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15032,8 +15795,16 @@
           <t>caffe_conti</t>
         </is>
       </c>
-      <c r="G258" s="1" t="inlineStr"/>
-      <c r="H258" s="1" t="inlineStr"/>
+      <c r="G258" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H258" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I258" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15053,63 +15824,64 @@
       </c>
       <c r="R258" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="inlineStr">
+      <c r="A259" t="inlineStr">
         <is>
           <t>Caffè Fleming</t>
         </is>
       </c>
-      <c r="B259" s="1" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Via Flaminia, 677/A</t>
         </is>
       </c>
-      <c r="C259" s="1" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>06/3333960</t>
         </is>
       </c>
-      <c r="D259" s="1" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>www.caffefleming.it</t>
         </is>
       </c>
-      <c r="E259" s="1" t="inlineStr">
+      <c r="E259" t="inlineStr">
         <is>
           <t>caffefleming</t>
         </is>
       </c>
-      <c r="F259" s="1" t="inlineStr">
+      <c r="F259" t="inlineStr">
         <is>
           <t>caffefleming</t>
         </is>
       </c>
-      <c r="G259" s="1" t="inlineStr"/>
-      <c r="H259" s="1" t="inlineStr"/>
-      <c r="I259" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J259" s="1" t="inlineStr"/>
-      <c r="K259" s="1" t="inlineStr"/>
-      <c r="L259" s="1" t="inlineStr"/>
-      <c r="M259" s="1" t="inlineStr"/>
-      <c r="N259" s="1" t="inlineStr"/>
-      <c r="O259" s="1" t="inlineStr"/>
-      <c r="P259" s="1" t="inlineStr"/>
-      <c r="Q259" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R259" s="1" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 27/04/2026</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15144,8 +15916,16 @@
           <t>casamanfredi</t>
         </is>
       </c>
-      <c r="G260" s="1" t="inlineStr"/>
-      <c r="H260" s="1" t="inlineStr"/>
+      <c r="G260" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H260" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I260" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15165,7 +15945,7 @@
       </c>
       <c r="R260" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15973,11 @@
         </is>
       </c>
       <c r="G261" s="1" t="inlineStr"/>
-      <c r="H261" s="1" t="inlineStr"/>
+      <c r="H261" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I261" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15213,7 +15997,7 @@
       </c>
       <c r="R261" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15244,8 +16028,16 @@
           <t>cristalli.di.zucchero</t>
         </is>
       </c>
-      <c r="G262" s="1" t="inlineStr"/>
-      <c r="H262" s="1" t="inlineStr"/>
+      <c r="G262" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H262" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I262" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15265,7 +16057,7 @@
       </c>
       <c r="R262" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15300,8 +16092,16 @@
           <t>dantoni1974</t>
         </is>
       </c>
-      <c r="G263" s="1" t="inlineStr"/>
-      <c r="H263" s="1" t="inlineStr"/>
+      <c r="G263" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H263" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I263" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15321,7 +16121,7 @@
       </c>
       <c r="R263" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15356,8 +16156,16 @@
           <t>farorome</t>
         </is>
       </c>
-      <c r="G264" s="1" t="inlineStr"/>
-      <c r="H264" s="1" t="inlineStr"/>
+      <c r="G264" s="1" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="H264" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I264" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15377,7 +16185,7 @@
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15412,8 +16220,16 @@
           <t>faxfactory</t>
         </is>
       </c>
-      <c r="G265" s="1" t="inlineStr"/>
-      <c r="H265" s="1" t="inlineStr"/>
+      <c r="G265" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H265" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I265" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15433,7 +16249,7 @@
       </c>
       <c r="R265" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15464,8 +16280,16 @@
           <t>federicoprodon</t>
         </is>
       </c>
-      <c r="G266" s="1" t="inlineStr"/>
-      <c r="H266" s="1" t="inlineStr"/>
+      <c r="G266" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H266" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I266" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15485,7 +16309,7 @@
       </c>
       <c r="R266" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15517,7 +16341,11 @@
         </is>
       </c>
       <c r="G267" s="1" t="inlineStr"/>
-      <c r="H267" s="1" t="inlineStr"/>
+      <c r="H267" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I267" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15537,7 +16365,7 @@
       </c>
       <c r="R267" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15581,7 +16409,7 @@
       </c>
       <c r="R268" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15612,8 +16440,16 @@
           <t>gastromario.it</t>
         </is>
       </c>
-      <c r="G269" s="1" t="inlineStr"/>
-      <c r="H269" s="1" t="inlineStr"/>
+      <c r="G269" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H269" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I269" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15633,7 +16469,7 @@
       </c>
       <c r="R269" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15665,7 +16501,11 @@
         </is>
       </c>
       <c r="G270" s="1" t="inlineStr"/>
-      <c r="H270" s="1" t="inlineStr"/>
+      <c r="H270" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I270" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15685,7 +16525,7 @@
       </c>
       <c r="R270" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15729,7 +16569,7 @@
       </c>
       <c r="R271" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15773,7 +16613,7 @@
       </c>
       <c r="R272" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15808,8 +16648,16 @@
           <t>lelevainroma</t>
         </is>
       </c>
-      <c r="G273" s="1" t="inlineStr"/>
-      <c r="H273" s="1" t="inlineStr"/>
+      <c r="G273" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H273" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I273" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15829,7 +16677,7 @@
       </c>
       <c r="R273" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15860,8 +16708,16 @@
           <t>lievitopizzapane</t>
         </is>
       </c>
-      <c r="G274" s="1" t="inlineStr"/>
-      <c r="H274" s="1" t="inlineStr"/>
+      <c r="G274" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H274" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I274" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15881,7 +16737,7 @@
       </c>
       <c r="R274" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15916,8 +16772,16 @@
           <t>love.roma_</t>
         </is>
       </c>
-      <c r="G275" s="1" t="inlineStr"/>
-      <c r="H275" s="1" t="inlineStr"/>
+      <c r="G275" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H275" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I275" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15937,7 +16801,7 @@
       </c>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -15972,8 +16836,16 @@
           <t>marzapaneroma</t>
         </is>
       </c>
-      <c r="G276" s="1" t="inlineStr"/>
-      <c r="H276" s="1" t="inlineStr"/>
+      <c r="G276" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H276" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I276" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -15993,63 +16865,64 @@
       </c>
       <c r="R276" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="inlineStr">
+      <c r="A277" t="inlineStr">
         <is>
           <t>Nero Vaniglia</t>
         </is>
       </c>
-      <c r="B277" s="1" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>Circonvallazione Ostiense, 201</t>
         </is>
       </c>
-      <c r="C277" s="1" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>06/5780306</t>
         </is>
       </c>
-      <c r="D277" s="1" t="inlineStr">
+      <c r="D277" t="inlineStr">
         <is>
           <t>www.nerovaniglia.it</t>
         </is>
       </c>
-      <c r="E277" s="1" t="inlineStr">
+      <c r="E277" t="inlineStr">
         <is>
           <t>nerovanigliagiorgiagrillo</t>
         </is>
       </c>
-      <c r="F277" s="1" t="inlineStr">
+      <c r="F277" t="inlineStr">
         <is>
           <t>nerovaniglia</t>
         </is>
       </c>
-      <c r="G277" s="1" t="inlineStr"/>
-      <c r="H277" s="1" t="inlineStr"/>
-      <c r="I277" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J277" s="1" t="inlineStr"/>
-      <c r="K277" s="1" t="inlineStr"/>
-      <c r="L277" s="1" t="inlineStr"/>
-      <c r="M277" s="1" t="inlineStr"/>
-      <c r="N277" s="1" t="inlineStr"/>
-      <c r="O277" s="1" t="inlineStr"/>
-      <c r="P277" s="1" t="inlineStr"/>
-      <c r="Q277" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R277" s="1" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 27/04/2026</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16954,11 @@
         </is>
       </c>
       <c r="G278" s="1" t="inlineStr"/>
-      <c r="H278" s="1" t="inlineStr"/>
+      <c r="H278" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I278" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -16101,7 +16978,7 @@
       </c>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16136,8 +17013,16 @@
           <t>pasticceria_barberini</t>
         </is>
       </c>
-      <c r="G279" s="1" t="inlineStr"/>
-      <c r="H279" s="1" t="inlineStr"/>
+      <c r="G279" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H279" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I279" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -16157,7 +17042,7 @@
       </c>
       <c r="R279" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16192,7 +17077,11 @@
           <t>pasticceriawaltermuscobompiani</t>
         </is>
       </c>
-      <c r="G280" s="1" t="inlineStr"/>
+      <c r="G280" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H280" s="1" t="inlineStr"/>
       <c r="I280" s="1" t="inlineStr">
         <is>
@@ -16213,7 +17102,7 @@
       </c>
       <c r="R280" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16261,7 +17150,7 @@
       </c>
       <c r="R281" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16317,7 +17206,7 @@
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16373,7 +17262,7 @@
       </c>
       <c r="R283" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16425,7 +17314,7 @@
       </c>
       <c r="R284" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16465,7 +17354,7 @@
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16521,7 +17410,7 @@
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16573,7 +17462,7 @@
       </c>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16625,7 +17514,7 @@
       </c>
       <c r="R288" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16681,7 +17570,7 @@
       </c>
       <c r="R289" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16733,7 +17622,7 @@
       </c>
       <c r="R290" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16777,7 +17666,7 @@
       </c>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16821,7 +17710,7 @@
       </c>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16877,7 +17766,7 @@
       </c>
       <c r="R293" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16929,7 +17818,7 @@
       </c>
       <c r="R294" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -16973,7 +17862,7 @@
       </c>
       <c r="R295" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17029,7 +17918,7 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17085,7 +17974,7 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17137,7 +18026,7 @@
       </c>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17189,7 +18078,7 @@
       </c>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17245,7 +18134,7 @@
       </c>
       <c r="R300" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17289,7 +18178,7 @@
       </c>
       <c r="R301" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17337,7 +18226,7 @@
       </c>
       <c r="R302" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17393,7 +18282,7 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17449,7 +18338,7 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17497,7 +18386,7 @@
       </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17553,7 +18442,7 @@
       </c>
       <c r="R306" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17609,7 +18498,7 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17665,7 +18554,7 @@
       </c>
       <c r="R308" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17721,7 +18610,7 @@
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17777,7 +18666,7 @@
       </c>
       <c r="R310" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17833,7 +18722,7 @@
       </c>
       <c r="R311" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17889,7 +18778,7 @@
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17941,7 +18830,7 @@
       </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -17997,7 +18886,7 @@
       </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18053,7 +18942,7 @@
       </c>
       <c r="R315" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18109,7 +18998,7 @@
       </c>
       <c r="R316" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18165,7 +19054,7 @@
       </c>
       <c r="R317" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18209,7 +19098,7 @@
       </c>
       <c r="R318" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18253,7 +19142,7 @@
       </c>
       <c r="R319" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18297,7 +19186,7 @@
       </c>
       <c r="R320" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18353,7 +19242,7 @@
       </c>
       <c r="R321" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18409,7 +19298,7 @@
       </c>
       <c r="R322" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18465,7 +19354,7 @@
       </c>
       <c r="R323" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18517,7 +19406,7 @@
       </c>
       <c r="R324" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18573,7 +19462,7 @@
       </c>
       <c r="R325" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18629,7 +19518,7 @@
       </c>
       <c r="R326" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18673,7 +19562,7 @@
       </c>
       <c r="R327" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18729,7 +19618,7 @@
       </c>
       <c r="R328" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18785,7 +19674,7 @@
       </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18841,7 +19730,7 @@
       </c>
       <c r="R330" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -18889,7 +19778,7 @@
       </c>
       <c r="R331" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19109,7 +19998,7 @@
       </c>
       <c r="R334" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19165,7 +20054,7 @@
       </c>
       <c r="R335" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19217,7 +20106,7 @@
       </c>
       <c r="R336" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19261,7 +20150,7 @@
       </c>
       <c r="R337" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19317,7 +20206,7 @@
       </c>
       <c r="R338" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19369,7 +20258,7 @@
       </c>
       <c r="R339" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19425,7 +20314,7 @@
       </c>
       <c r="R340" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19469,7 +20358,7 @@
       </c>
       <c r="R341" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19513,7 +20402,7 @@
       </c>
       <c r="R342" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19561,7 +20450,7 @@
       </c>
       <c r="R343" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19617,7 +20506,7 @@
       </c>
       <c r="R344" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19665,7 +20554,7 @@
       </c>
       <c r="R345" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19709,7 +20598,7 @@
       </c>
       <c r="R346" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19765,7 +20654,7 @@
       </c>
       <c r="R347" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19817,7 +20706,7 @@
       </c>
       <c r="R348" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19869,7 +20758,7 @@
       </c>
       <c r="R349" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19925,7 +20814,7 @@
       </c>
       <c r="R350" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -19969,7 +20858,7 @@
       </c>
       <c r="R351" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20025,7 +20914,7 @@
       </c>
       <c r="R352" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20966,7 @@
       </c>
       <c r="R353" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20133,7 +21022,7 @@
       </c>
       <c r="R354" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20189,7 +21078,7 @@
       </c>
       <c r="R355" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20245,7 +21134,7 @@
       </c>
       <c r="R356" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20301,7 +21190,7 @@
       </c>
       <c r="R357" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20353,7 +21242,7 @@
       </c>
       <c r="R358" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20409,7 +21298,7 @@
       </c>
       <c r="R359" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20625,7 +21514,7 @@
       </c>
       <c r="R362" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20681,7 +21570,7 @@
       </c>
       <c r="R363" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20737,7 +21626,7 @@
       </c>
       <c r="R364" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20789,7 +21678,7 @@
       </c>
       <c r="R365" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20837,7 +21726,7 @@
       </c>
       <c r="R366" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20893,7 +21782,7 @@
       </c>
       <c r="R367" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -20949,7 +21838,7 @@
       </c>
       <c r="R368" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21005,7 +21894,7 @@
       </c>
       <c r="R369" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21057,7 +21946,7 @@
       </c>
       <c r="R370" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21113,7 +22002,7 @@
       </c>
       <c r="R371" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21157,7 +22046,7 @@
       </c>
       <c r="R372" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21213,7 +22102,7 @@
       </c>
       <c r="R373" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21269,7 +22158,7 @@
       </c>
       <c r="R374" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21325,7 +22214,7 @@
       </c>
       <c r="R375" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21381,7 +22270,7 @@
       </c>
       <c r="R376" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21437,7 +22326,7 @@
       </c>
       <c r="R377" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21489,7 +22378,7 @@
       </c>
       <c r="R378" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21533,7 +22422,7 @@
       </c>
       <c r="R379" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21589,7 +22478,7 @@
       </c>
       <c r="R380" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21641,7 +22530,7 @@
       </c>
       <c r="R381" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21697,7 +22586,7 @@
       </c>
       <c r="R382" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21749,7 +22638,7 @@
       </c>
       <c r="R383" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21801,7 +22690,7 @@
       </c>
       <c r="R384" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21857,7 +22746,7 @@
       </c>
       <c r="R385" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21913,7 +22802,7 @@
       </c>
       <c r="R386" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -21965,7 +22854,7 @@
       </c>
       <c r="R387" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22021,7 +22910,7 @@
       </c>
       <c r="R388" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22077,7 +22966,7 @@
       </c>
       <c r="R389" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22129,7 +23018,7 @@
       </c>
       <c r="R390" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22173,7 +23062,7 @@
       </c>
       <c r="R391" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22229,7 +23118,7 @@
       </c>
       <c r="R392" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22285,7 +23174,7 @@
       </c>
       <c r="R393" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22337,7 +23226,7 @@
       </c>
       <c r="R394" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22393,7 +23282,7 @@
       </c>
       <c r="R395" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22445,7 +23334,7 @@
       </c>
       <c r="R396" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22497,7 +23386,7 @@
       </c>
       <c r="R397" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22553,7 +23442,7 @@
       </c>
       <c r="R398" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22605,7 +23494,7 @@
       </c>
       <c r="R399" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22661,7 +23550,7 @@
       </c>
       <c r="R400" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22709,7 +23598,7 @@
       </c>
       <c r="R401" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22761,7 +23650,7 @@
       </c>
       <c r="R402" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22813,7 +23702,7 @@
       </c>
       <c r="R403" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22869,7 +23758,7 @@
       </c>
       <c r="R404" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22925,7 +23814,7 @@
       </c>
       <c r="R405" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -22977,7 +23866,7 @@
       </c>
       <c r="R406" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23017,7 +23906,7 @@
       </c>
       <c r="R407" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23069,7 +23958,7 @@
       </c>
       <c r="R408" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23125,7 +24014,7 @@
       </c>
       <c r="R409" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23177,7 +24066,7 @@
       </c>
       <c r="R410" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23221,7 +24110,7 @@
       </c>
       <c r="R411" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23269,7 +24158,7 @@
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23321,7 +24210,7 @@
       </c>
       <c r="R413" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23377,7 +24266,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23433,7 +24322,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23489,7 +24378,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23545,7 +24434,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23601,7 +24490,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23657,7 +24546,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -23713,7 +24602,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -2596,7 +2596,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4070,296 +4070,280 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Osteria Landi</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Via Claudio, 28</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>06/56305565</t>
         </is>
       </c>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>osterialandi</t>
         </is>
       </c>
-      <c r="F60" s="1" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>osterialandi</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H60" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr"/>
-      <c r="L60" s="1" t="inlineStr"/>
-      <c r="M60" s="1" t="inlineStr"/>
-      <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr"/>
-      <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R60" s="1" t="inlineStr">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, TheFork 9.4/10, recensione Foodzilla 24/04/2026, Google 4.7</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Portale 21 - Opificio di cucina</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Via Rodolfo Morandi, 32</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>06/94837668</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr"/>
-      <c r="E61" s="1" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr"/>
-      <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr"/>
-      <c r="L61" s="1" t="inlineStr"/>
-      <c r="M61" s="1" t="inlineStr"/>
-      <c r="N61" s="1" t="inlineStr"/>
-      <c r="O61" s="1" t="inlineStr"/>
-      <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R61" s="1" t="inlineStr">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto (Marino), sito attivo, Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Retrobottega</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Via D’Ascanio, 26/A</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>06/68136310</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>www.retro-bottega.com</t>
         </is>
       </c>
-      <c r="E62" s="1" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>retrobottega4</t>
         </is>
       </c>
-      <c r="F62" s="1" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>retro_bottega</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H62" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr"/>
-      <c r="L62" s="1" t="inlineStr"/>
-      <c r="M62" s="1" t="inlineStr"/>
-      <c r="N62" s="1" t="inlineStr"/>
-      <c r="O62" s="1" t="inlineStr"/>
-      <c r="P62" s="1" t="inlineStr"/>
-      <c r="Q62" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R62" s="1" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, OpenTable 'Updated 2026', Michelin Star, Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Riccioli d'Oro</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Via Conca d'Oro, 38</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>06/83797040</t>
         </is>
       </c>
-      <c r="D63" s="1" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>www.ristorantericciolidoro.it</t>
         </is>
       </c>
-      <c r="E63" s="1" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>profile.php?id=61551090176976</t>
         </is>
       </c>
-      <c r="F63" s="1" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>ristorantericciolidoro</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H63" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr"/>
-      <c r="L63" s="1" t="inlineStr"/>
-      <c r="M63" s="1" t="inlineStr"/>
-      <c r="N63" s="1" t="inlineStr"/>
-      <c r="O63" s="1" t="inlineStr"/>
-      <c r="P63" s="1" t="inlineStr"/>
-      <c r="Q63" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R63" s="1" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, TheFork menu 2026 attivo, sito attivo</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Rimessa Roscioli</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Via del Conservatorio, 58</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>06/68803914</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>www.rimessaroscioli.com</t>
         </is>
       </c>
-      <c r="E64" s="1" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>RimessaRoscioli</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>rimessaroscioli</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H64" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr"/>
-      <c r="L64" s="1" t="inlineStr"/>
-      <c r="M64" s="1" t="inlineStr"/>
-      <c r="N64" s="1" t="inlineStr"/>
-      <c r="O64" s="1" t="inlineStr"/>
-      <c r="P64" s="1" t="inlineStr"/>
-      <c r="Q64" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R64" s="1" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated April 2026', Wheree 'Updated February 2026'</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -4413,604 +4397,557 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Ristorante Moi</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Via Antonio Serra, 15</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>06/87600399</t>
         </is>
       </c>
-      <c r="D66" s="1" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>www.ristorantemoi.com</t>
         </is>
       </c>
-      <c r="E66" s="1" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>ristorantemoi</t>
         </is>
       </c>
-      <c r="F66" s="1" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>moiristorante</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H66" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I66" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr"/>
-      <c r="L66" s="1" t="inlineStr"/>
-      <c r="M66" s="1" t="inlineStr"/>
-      <c r="N66" s="1" t="inlineStr"/>
-      <c r="O66" s="1" t="inlineStr"/>
-      <c r="P66" s="1" t="inlineStr"/>
-      <c r="Q66" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R66" s="1" t="inlineStr">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, TheFork 9.5/10 con 892 recensioni, Michelin Guide attiva</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Sintesi</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Viale dei Castani, 17</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>06/45557597</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>www.ristorantesintesi.it</t>
         </is>
       </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>sintesiristorante</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>sintesi_ristorante</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H67" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr"/>
-      <c r="L67" s="1" t="inlineStr"/>
-      <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr"/>
-      <c r="P67" s="1" t="inlineStr"/>
-      <c r="Q67" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R67" s="1" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto (Ariccia), Michelin 1 stella 2026, sito attivo</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Specus</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Via Casilina, 315</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>06/89522332</t>
         </is>
       </c>
-      <c r="D68" s="1" t="inlineStr"/>
-      <c r="E68" s="1" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr"/>
-      <c r="L68" s="1" t="inlineStr"/>
-      <c r="M68" s="1" t="inlineStr"/>
-      <c r="N68" s="1" t="inlineStr"/>
-      <c r="O68" s="1" t="inlineStr"/>
-      <c r="P68" s="1" t="inlineStr"/>
-      <c r="Q68" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R68" s="1" t="inlineStr">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto (Valmontone), Michelin Guide 2025-2026 attiva, Tripadvisor attivo</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Stecca</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Viale Guglielmo Massaia, 28</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>06/01906053</t>
         </is>
       </c>
-      <c r="D69" s="1" t="inlineStr"/>
-      <c r="E69" s="1" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr"/>
-      <c r="L69" s="1" t="inlineStr"/>
-      <c r="M69" s="1" t="inlineStr"/>
-      <c r="N69" s="1" t="inlineStr"/>
-      <c r="O69" s="1" t="inlineStr"/>
-      <c r="P69" s="1" t="inlineStr"/>
-      <c r="Q69" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R69" s="1" t="inlineStr">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, articolo Linkiesta febbraio 2026, citato in nuove aperture aprile 2026</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Terramadre</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Via del Baluardo, 7</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>06/55135169</t>
         </is>
       </c>
-      <c r="D70" s="1" t="inlineStr"/>
-      <c r="E70" s="1" t="inlineStr"/>
-      <c r="F70" s="1" t="inlineStr"/>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr"/>
-      <c r="L70" s="1" t="inlineStr"/>
-      <c r="M70" s="1" t="inlineStr"/>
-      <c r="N70" s="1" t="inlineStr"/>
-      <c r="O70" s="1" t="inlineStr"/>
-      <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R70" s="1" t="inlineStr">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto (Nettuno), sito attivo, Michelin Guide attiva</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Tinello Bistrot</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Via Vigna di Corte, 6</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>06/24597135</t>
         </is>
       </c>
-      <c r="D71" s="1" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>www.tinellobistrot.it</t>
         </is>
       </c>
-      <c r="E71" s="1" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Tinellobistrot</t>
         </is>
       </c>
-      <c r="F71" s="1" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>tinello_bistrot</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H71" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I71" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr"/>
-      <c r="L71" s="1" t="inlineStr"/>
-      <c r="M71" s="1" t="inlineStr"/>
-      <c r="N71" s="1" t="inlineStr"/>
-      <c r="O71" s="1" t="inlineStr"/>
-      <c r="P71" s="1" t="inlineStr"/>
-      <c r="Q71" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R71" s="1" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto (Castel Gandolfo), Tripadvisor '2026 Reviews', Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Toma 52</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Via Cremona, 52/B</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>06/5126917</t>
         </is>
       </c>
-      <c r="D72" s="1" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>www.tomatrattoria.com</t>
         </is>
       </c>
-      <c r="E72" s="1" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>toma52TrattoriaGourmet</t>
         </is>
       </c>
-      <c r="F72" s="1" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>toma52trattoriagourmet</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H72" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I72" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr"/>
-      <c r="L72" s="1" t="inlineStr"/>
-      <c r="M72" s="1" t="inlineStr"/>
-      <c r="N72" s="1" t="inlineStr"/>
-      <c r="O72" s="1" t="inlineStr"/>
-      <c r="P72" s="1" t="inlineStr"/>
-      <c r="Q72" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R72" s="1" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Restaurant Guru 4.8/5 con 123 recensioni, sito attivo</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>UMA</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Via Girolamo Benzoni, 34</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>334/3855945</t>
         </is>
       </c>
-      <c r="D73" s="1" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>www.umaroma.com</t>
         </is>
       </c>
-      <c r="E73" s="1" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>ristoranteumaroma</t>
         </is>
       </c>
-      <c r="F73" s="1" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>umaroma_restaurant</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H73" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr"/>
-      <c r="L73" s="1" t="inlineStr"/>
-      <c r="M73" s="1" t="inlineStr"/>
-      <c r="N73" s="1" t="inlineStr"/>
-      <c r="O73" s="1" t="inlineStr"/>
-      <c r="P73" s="1" t="inlineStr"/>
-      <c r="Q73" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R73" s="1" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Tripadvisor '2026 Reviews', sito attivo</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>100C Vino e Pesce</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>Viale delle Orchidee, 100</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>349/2422046</t>
         </is>
       </c>
-      <c r="D74" s="1" t="inlineStr"/>
-      <c r="E74" s="1" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr"/>
-      <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr"/>
-      <c r="L74" s="1" t="inlineStr"/>
-      <c r="M74" s="1" t="inlineStr"/>
-      <c r="N74" s="1" t="inlineStr"/>
-      <c r="O74" s="1" t="inlineStr"/>
-      <c r="P74" s="1" t="inlineStr"/>
-      <c r="Q74" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R74" s="1" t="inlineStr">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, apertura 2/1/2026, articolo Foodzilla 4/2/2026, Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>266 La Barraca</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Lungomare delle Meduse, 266</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>06/85386554</t>
         </is>
       </c>
-      <c r="D75" s="1" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>www.266labarraca.it</t>
         </is>
       </c>
-      <c r="E75" s="1" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>266LaBarraca</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>266labarraca</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H75" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I75" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr"/>
-      <c r="L75" s="1" t="inlineStr"/>
-      <c r="M75" s="1" t="inlineStr"/>
-      <c r="N75" s="1" t="inlineStr"/>
-      <c r="O75" s="1" t="inlineStr"/>
-      <c r="P75" s="1" t="inlineStr"/>
-      <c r="Q75" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R75" s="1" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto (Torvaianica), Tripadvisor recensioni recenti attive, articoli attivi</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Acqua Pazza</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Via Dietro la Chiesa, 3/4</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>0771/80643</t>
         </is>
       </c>
-      <c r="D76" s="1" t="inlineStr"/>
-      <c r="E76" s="1" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr"/>
-      <c r="L76" s="1" t="inlineStr"/>
-      <c r="M76" s="1" t="inlineStr"/>
-      <c r="N76" s="1" t="inlineStr"/>
-      <c r="O76" s="1" t="inlineStr"/>
-      <c r="P76" s="1" t="inlineStr"/>
-      <c r="Q76" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R76" s="1" t="inlineStr">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto (Ponza), Michelin Guide attiva, stagionale marzo-ottobre quindi attiva</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -5201,152 +5138,136 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Alla Magnatora</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Via Volubro, 4</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>0775/1626000</t>
         </is>
       </c>
-      <c r="D79" s="1" t="inlineStr"/>
-      <c r="E79" s="1" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr"/>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
-      <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" s="1" t="inlineStr"/>
-      <c r="Q79" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R79" s="1" t="inlineStr">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto (Piglio), Google 4.5/5 con 314 recensioni, Facebook attivo</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Angelino "ai Fori" dal 1947</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Largo Corrado Ricci, 40</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>06/6791121</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr"/>
-      <c r="L80" s="1" t="inlineStr"/>
-      <c r="M80" s="1" t="inlineStr"/>
-      <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr"/>
-      <c r="P80" s="1" t="inlineStr"/>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated April 2026' con 157 recensioni</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Arcangelo Vino &amp; Cucina</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Via G.G. Belli, 59/61</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>06/3210992</t>
         </is>
       </c>
-      <c r="D81" s="1" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>www.larcangelo.com</t>
         </is>
       </c>
-      <c r="E81" s="1" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>RistoranteArcangelo</t>
         </is>
       </c>
-      <c r="F81" s="1" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>arcangelodandini</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H81" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I81" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr"/>
-      <c r="L81" s="1" t="inlineStr"/>
-      <c r="M81" s="1" t="inlineStr"/>
-      <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr"/>
-      <c r="P81" s="1" t="inlineStr"/>
-      <c r="Q81" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R81" s="1" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated April 2026', sito attivo con info vacanza gennaio 2026</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -5410,64 +5331,62 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Aventina</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Viale della Piramide Cestia, 9</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>06/66594151</t>
         </is>
       </c>
-      <c r="D83" s="1" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>www.aventinaroma.com</t>
         </is>
       </c>
-      <c r="E83" s="1" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>aventina.roma</t>
         </is>
       </c>
-      <c r="F83" s="1" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>aventina.roma</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I83" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr"/>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
-      <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R83" s="1" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, sito aventinaroma.com attivo, Facebook attivo</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -5533,7 +5452,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5504,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5564,7 @@
       </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5628,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5692,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5813,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5873,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6018,7 +5937,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6001,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6065,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6121,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6185,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6245,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6309,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6430,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6474,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6538,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6598,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6662,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6722,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6786,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6830,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7032,7 +6951,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7015,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7152,7 +7071,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7135,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7252,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7316,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7380,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7436,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7500,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7621,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7681,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7745,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7805,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7865,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7909,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8034,7 +7953,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8017,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8081,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8145,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8209,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8354,7 +8273,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8317,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8361,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8421,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8530,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8594,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8646,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8710,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8855,7 +8774,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8838,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8902,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9047,7 +8966,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9091,7 +9010,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9054,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9199,7 +9118,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9182,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9242,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9306,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9350,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9414,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9458,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9502,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9566,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9630,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9775,7 +9694,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9738,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9802,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9866,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10007,7 +9926,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10059,7 +9978,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10038,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10102,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10166,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10226,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10290,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10334,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10398,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10442,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10506,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10570,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10634,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10698,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10823,7 +10742,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10802,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10846,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10991,7 +10910,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11051,7 +10970,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11034,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11078,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11194,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11238,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11383,7 +11302,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11358,7 @@
       </c>
       <c r="R185" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11483,7 +11402,7 @@
       </c>
       <c r="R186" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11466,7 @@
       </c>
       <c r="R187" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11587,7 @@
       </c>
       <c r="R189" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11631,7 @@
       </c>
       <c r="R190" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11695,7 @@
       </c>
       <c r="R191" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11836,7 +11755,7 @@
       </c>
       <c r="R192" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11819,7 @@
       </c>
       <c r="R193" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -11964,7 +11883,7 @@
       </c>
       <c r="R194" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12028,7 +11947,7 @@
       </c>
       <c r="R195" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12092,7 +12011,7 @@
       </c>
       <c r="R196" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12067,7 @@
       </c>
       <c r="R197" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12131,7 @@
       </c>
       <c r="R198" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12195,7 @@
       </c>
       <c r="R199" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12239,7 @@
       </c>
       <c r="R200" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12303,7 @@
       </c>
       <c r="R201" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12448,7 +12367,7 @@
       </c>
       <c r="R202" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12512,7 +12431,7 @@
       </c>
       <c r="R203" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12495,7 @@
       </c>
       <c r="R204" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12559,7 @@
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12611,7 @@
       </c>
       <c r="R206" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12675,7 @@
       </c>
       <c r="R207" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12820,7 +12739,7 @@
       </c>
       <c r="R208" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12783,7 @@
       </c>
       <c r="R209" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12827,7 @@
       </c>
       <c r="R210" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12891,7 @@
       </c>
       <c r="R211" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13036,7 +12955,7 @@
       </c>
       <c r="R212" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13100,7 +13019,7 @@
       </c>
       <c r="R213" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13083,7 @@
       </c>
       <c r="R214" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13228,7 +13147,7 @@
       </c>
       <c r="R215" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13207,7 @@
       </c>
       <c r="R216" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13271,7 @@
       </c>
       <c r="R217" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13494,7 @@
       </c>
       <c r="R220" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13619,7 +13538,7 @@
       </c>
       <c r="R221" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13602,7 @@
       </c>
       <c r="R222" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13747,7 +13666,7 @@
       </c>
       <c r="R223" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13730,7 @@
       </c>
       <c r="R224" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13875,7 +13794,7 @@
       </c>
       <c r="R225" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13939,7 +13858,7 @@
       </c>
       <c r="R226" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13902,7 @@
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14047,7 +13966,7 @@
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14010,7 @@
       </c>
       <c r="R229" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14074,7 @@
       </c>
       <c r="R230" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14118,7 @@
       </c>
       <c r="R231" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14259,7 +14178,7 @@
       </c>
       <c r="R232" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14242,7 @@
       </c>
       <c r="R233" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14387,7 +14306,7 @@
       </c>
       <c r="R234" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14370,7 @@
       </c>
       <c r="R235" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14414,7 @@
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14555,7 +14474,7 @@
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14534,7 @@
       </c>
       <c r="R238" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14598,7 @@
       </c>
       <c r="R239" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14662,7 @@
       </c>
       <c r="R240" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14807,7 +14726,7 @@
       </c>
       <c r="R241" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14871,7 +14790,7 @@
       </c>
       <c r="R242" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14935,7 +14854,7 @@
       </c>
       <c r="R243" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14918,7 @@
       </c>
       <c r="R244" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15063,7 +14982,7 @@
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15107,7 +15026,7 @@
       </c>
       <c r="R246" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15208,7 +15127,7 @@
       </c>
       <c r="R248" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15171,7 @@
       </c>
       <c r="R249" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15235,7 @@
       </c>
       <c r="R250" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15299,7 @@
       </c>
       <c r="R251" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15444,7 +15363,7 @@
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15504,7 +15423,7 @@
       </c>
       <c r="R253" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15568,7 +15487,7 @@
       </c>
       <c r="R254" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15551,7 @@
       </c>
       <c r="R255" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15696,7 +15615,7 @@
       </c>
       <c r="R256" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15760,7 +15679,7 @@
       </c>
       <c r="R257" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15824,7 +15743,7 @@
       </c>
       <c r="R258" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15945,7 +15864,7 @@
       </c>
       <c r="R260" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -15997,7 +15916,7 @@
       </c>
       <c r="R261" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16057,7 +15976,7 @@
       </c>
       <c r="R262" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16040,7 @@
       </c>
       <c r="R263" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16104,7 @@
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16249,7 +16168,7 @@
       </c>
       <c r="R265" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16228,7 @@
       </c>
       <c r="R266" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16365,7 +16284,7 @@
       </c>
       <c r="R267" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16409,7 +16328,7 @@
       </c>
       <c r="R268" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16469,7 +16388,7 @@
       </c>
       <c r="R269" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16525,7 +16444,7 @@
       </c>
       <c r="R270" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16488,7 @@
       </c>
       <c r="R271" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16532,7 @@
       </c>
       <c r="R272" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16596,7 @@
       </c>
       <c r="R273" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16656,7 @@
       </c>
       <c r="R274" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16801,7 +16720,7 @@
       </c>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16784,7 @@
       </c>
       <c r="R276" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16897,7 @@
       </c>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17042,7 +16961,7 @@
       </c>
       <c r="R279" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17001,11 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H280" s="1" t="inlineStr"/>
+      <c r="H280" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I280" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17102,7 +17025,7 @@
       </c>
       <c r="R280" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17053,11 @@
         </is>
       </c>
       <c r="G281" s="1" t="inlineStr"/>
-      <c r="H281" s="1" t="inlineStr"/>
+      <c r="H281" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I281" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17150,7 +17077,7 @@
       </c>
       <c r="R281" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17185,8 +17112,16 @@
           <t>Rosciolicaffe</t>
         </is>
       </c>
-      <c r="G282" s="1" t="inlineStr"/>
-      <c r="H282" s="1" t="inlineStr"/>
+      <c r="G282" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H282" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I282" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17206,7 +17141,7 @@
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17241,8 +17176,16 @@
           <t>santisebastianoevalentino</t>
         </is>
       </c>
-      <c r="G283" s="1" t="inlineStr"/>
-      <c r="H283" s="1" t="inlineStr"/>
+      <c r="G283" s="1" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="H283" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I283" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17262,59 +17205,59 @@
       </c>
       <c r="R283" s="1" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Sensorio Coffee Lab</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Via Flaminia, 67</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>06/3231436</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Sensorio-Coffee-Lab-100094733526832</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>sensorio_coffee_lab</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="1" t="inlineStr">
-        <is>
-          <t>Sensorio Coffee Lab</t>
-        </is>
-      </c>
-      <c r="B284" s="1" t="inlineStr">
-        <is>
-          <t>Via Flaminia, 67</t>
-        </is>
-      </c>
-      <c r="C284" s="1" t="inlineStr">
-        <is>
-          <t>06/3231436</t>
-        </is>
-      </c>
-      <c r="D284" s="1" t="inlineStr"/>
-      <c r="E284" s="1" t="inlineStr">
-        <is>
-          <t>Sensorio-Coffee-Lab-100094733526832</t>
-        </is>
-      </c>
-      <c r="F284" s="1" t="inlineStr">
-        <is>
-          <t>sensorio_coffee_lab</t>
-        </is>
-      </c>
-      <c r="G284" s="1" t="inlineStr"/>
-      <c r="H284" s="1" t="inlineStr"/>
-      <c r="I284" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J284" s="1" t="inlineStr"/>
-      <c r="K284" s="1" t="inlineStr"/>
-      <c r="L284" s="1" t="inlineStr"/>
-      <c r="M284" s="1" t="inlineStr"/>
-      <c r="N284" s="1" t="inlineStr"/>
-      <c r="O284" s="1" t="inlineStr"/>
-      <c r="P284" s="1" t="inlineStr"/>
-      <c r="Q284" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R284" s="1" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 27/04/2026</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17354,7 +17297,7 @@
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17389,8 +17332,16 @@
           <t>pasticceria_sordoni</t>
         </is>
       </c>
-      <c r="G286" s="1" t="inlineStr"/>
-      <c r="H286" s="1" t="inlineStr"/>
+      <c r="G286" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H286" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I286" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17410,7 +17361,7 @@
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17393,11 @@
         </is>
       </c>
       <c r="G287" s="1" t="inlineStr"/>
-      <c r="H287" s="1" t="inlineStr"/>
+      <c r="H287" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I287" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17462,7 +17417,7 @@
       </c>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17493,8 +17448,16 @@
           <t>aqla_streetfood</t>
         </is>
       </c>
-      <c r="G288" s="1" t="inlineStr"/>
-      <c r="H288" s="1" t="inlineStr"/>
+      <c r="G288" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H288" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I288" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17514,7 +17477,7 @@
       </c>
       <c r="R288" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17549,8 +17512,16 @@
           <t>aromaticus_</t>
         </is>
       </c>
-      <c r="G289" s="1" t="inlineStr"/>
-      <c r="H289" s="1" t="inlineStr"/>
+      <c r="G289" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H289" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I289" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17570,7 +17541,7 @@
       </c>
       <c r="R289" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17602,7 +17573,11 @@
         </is>
       </c>
       <c r="G290" s="1" t="inlineStr"/>
-      <c r="H290" s="1" t="inlineStr"/>
+      <c r="H290" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I290" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17622,7 +17597,7 @@
       </c>
       <c r="R290" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17666,7 +17641,7 @@
       </c>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17710,7 +17685,7 @@
       </c>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17745,8 +17720,16 @@
           <t>ciaochecca</t>
         </is>
       </c>
-      <c r="G293" s="1" t="inlineStr"/>
-      <c r="H293" s="1" t="inlineStr"/>
+      <c r="G293" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H293" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I293" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17766,7 +17749,7 @@
       </c>
       <c r="R293" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17797,8 +17780,16 @@
           <t>cuscusroma</t>
         </is>
       </c>
-      <c r="G294" s="1" t="inlineStr"/>
-      <c r="H294" s="1" t="inlineStr"/>
+      <c r="G294" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H294" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I294" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17818,7 +17809,7 @@
       </c>
       <c r="R294" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17862,7 +17853,7 @@
       </c>
       <c r="R295" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17897,8 +17888,16 @@
           <t>drogheriedelmare_</t>
         </is>
       </c>
-      <c r="G296" s="1" t="inlineStr"/>
-      <c r="H296" s="1" t="inlineStr"/>
+      <c r="G296" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H296" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I296" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17918,7 +17917,7 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -17953,8 +17952,16 @@
           <t>il_maritozzo_rosso</t>
         </is>
       </c>
-      <c r="G297" s="1" t="inlineStr"/>
-      <c r="H297" s="1" t="inlineStr"/>
+      <c r="G297" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H297" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I297" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -17974,7 +17981,7 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18005,8 +18012,16 @@
           <t>jiamolab</t>
         </is>
       </c>
-      <c r="G298" s="1" t="inlineStr"/>
-      <c r="H298" s="1" t="inlineStr"/>
+      <c r="G298" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H298" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I298" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18026,7 +18041,7 @@
       </c>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18057,8 +18072,16 @@
           <t>ladifferenza.roma</t>
         </is>
       </c>
-      <c r="G299" s="1" t="inlineStr"/>
-      <c r="H299" s="1" t="inlineStr"/>
+      <c r="G299" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H299" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I299" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18078,63 +18101,64 @@
       </c>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="inlineStr">
+      <c r="A300" t="inlineStr">
         <is>
           <t>Luna</t>
         </is>
       </c>
-      <c r="B300" s="1" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>Via delle Quattro Fontane, 175</t>
         </is>
       </c>
-      <c r="C300" s="1" t="inlineStr">
+      <c r="C300" t="inlineStr">
         <is>
           <t>06/45595900</t>
         </is>
       </c>
-      <c r="D300" s="1" t="inlineStr">
+      <c r="D300" t="inlineStr">
         <is>
           <t>www.lunabyfaro.com</t>
         </is>
       </c>
-      <c r="E300" s="1" t="inlineStr">
+      <c r="E300" t="inlineStr">
         <is>
           <t>profile.php?id=61575006555305</t>
         </is>
       </c>
-      <c r="F300" s="1" t="inlineStr">
+      <c r="F300" t="inlineStr">
         <is>
           <t>luna.rome_</t>
         </is>
       </c>
-      <c r="G300" s="1" t="inlineStr"/>
-      <c r="H300" s="1" t="inlineStr"/>
-      <c r="I300" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J300" s="1" t="inlineStr"/>
-      <c r="K300" s="1" t="inlineStr"/>
-      <c r="L300" s="1" t="inlineStr"/>
-      <c r="M300" s="1" t="inlineStr"/>
-      <c r="N300" s="1" t="inlineStr"/>
-      <c r="O300" s="1" t="inlineStr"/>
-      <c r="P300" s="1" t="inlineStr"/>
-      <c r="Q300" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R300" s="1" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 24/03/2026</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18202,7 @@
       </c>
       <c r="R301" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18205,7 +18229,11 @@
         </is>
       </c>
       <c r="F302" s="1" t="inlineStr"/>
-      <c r="G302" s="1" t="inlineStr"/>
+      <c r="G302" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H302" s="1" t="inlineStr"/>
       <c r="I302" s="1" t="inlineStr">
         <is>
@@ -18226,7 +18254,7 @@
       </c>
       <c r="R302" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18261,8 +18289,16 @@
           <t>mordi.roma</t>
         </is>
       </c>
-      <c r="G303" s="1" t="inlineStr"/>
-      <c r="H303" s="1" t="inlineStr"/>
+      <c r="G303" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H303" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I303" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18282,7 +18318,7 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18317,8 +18353,16 @@
           <t>RadiciRoma</t>
         </is>
       </c>
-      <c r="G304" s="1" t="inlineStr"/>
-      <c r="H304" s="1" t="inlineStr"/>
+      <c r="G304" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H304" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I304" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18338,7 +18382,7 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18366,7 +18410,11 @@
         </is>
       </c>
       <c r="G305" s="1" t="inlineStr"/>
-      <c r="H305" s="1" t="inlineStr"/>
+      <c r="H305" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I305" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18386,7 +18434,7 @@
       </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18421,8 +18469,16 @@
           <t>tulipane.roma</t>
         </is>
       </c>
-      <c r="G306" s="1" t="inlineStr"/>
-      <c r="H306" s="1" t="inlineStr"/>
+      <c r="G306" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H306" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I306" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18442,7 +18498,7 @@
       </c>
       <c r="R306" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18477,8 +18533,16 @@
           <t>babingtonstearoom</t>
         </is>
       </c>
-      <c r="G307" s="1" t="inlineStr"/>
-      <c r="H307" s="1" t="inlineStr"/>
+      <c r="G307" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H307" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I307" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18498,7 +18562,7 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18533,8 +18597,16 @@
           <t>caffedoria</t>
         </is>
       </c>
-      <c r="G308" s="1" t="inlineStr"/>
-      <c r="H308" s="1" t="inlineStr"/>
+      <c r="G308" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H308" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I308" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18554,7 +18626,7 @@
       </c>
       <c r="R308" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18589,8 +18661,16 @@
           <t>charlotte_pasticceria</t>
         </is>
       </c>
-      <c r="G309" s="1" t="inlineStr"/>
-      <c r="H309" s="1" t="inlineStr"/>
+      <c r="G309" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H309" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I309" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18610,63 +18690,64 @@
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="inlineStr">
+      <c r="A310" t="inlineStr">
         <is>
           <t>Fabrica</t>
         </is>
       </c>
-      <c r="B310" s="1" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>Via Girolamo Savonarola, 8</t>
         </is>
       </c>
-      <c r="C310" s="1" t="inlineStr">
+      <c r="C310" t="inlineStr">
         <is>
           <t>06/3972 5514</t>
         </is>
       </c>
-      <c r="D310" s="1" t="inlineStr">
+      <c r="D310" t="inlineStr">
         <is>
           <t>www.fabricadicalisto.com</t>
         </is>
       </c>
-      <c r="E310" s="1" t="inlineStr">
+      <c r="E310" t="inlineStr">
         <is>
           <t>Fabricaid1923</t>
         </is>
       </c>
-      <c r="F310" s="1" t="inlineStr">
+      <c r="F310" t="inlineStr">
         <is>
           <t>fabrica_id_1923</t>
         </is>
       </c>
-      <c r="G310" s="1" t="inlineStr"/>
-      <c r="H310" s="1" t="inlineStr"/>
-      <c r="I310" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J310" s="1" t="inlineStr"/>
-      <c r="K310" s="1" t="inlineStr"/>
-      <c r="L310" s="1" t="inlineStr"/>
-      <c r="M310" s="1" t="inlineStr"/>
-      <c r="N310" s="1" t="inlineStr"/>
-      <c r="O310" s="1" t="inlineStr"/>
-      <c r="P310" s="1" t="inlineStr"/>
-      <c r="Q310" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R310" s="1" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 26/04/2026</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18701,8 +18782,16 @@
           <t>hoteldericci</t>
         </is>
       </c>
-      <c r="G311" s="1" t="inlineStr"/>
-      <c r="H311" s="1" t="inlineStr"/>
+      <c r="G311" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H311" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I311" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18722,7 +18811,7 @@
       </c>
       <c r="R311" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18757,8 +18846,16 @@
           <t>hotelvilon</t>
         </is>
       </c>
-      <c r="G312" s="1" t="inlineStr"/>
-      <c r="H312" s="1" t="inlineStr"/>
+      <c r="G312" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H312" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I312" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18778,7 +18875,7 @@
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18809,8 +18906,16 @@
           <t>liberapasticceriacaffetteria</t>
         </is>
       </c>
-      <c r="G313" s="1" t="inlineStr"/>
-      <c r="H313" s="1" t="inlineStr"/>
+      <c r="G313" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H313" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I313" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18830,7 +18935,7 @@
       </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18865,8 +18970,16 @@
           <t>madeleineroma</t>
         </is>
       </c>
-      <c r="G314" s="1" t="inlineStr"/>
-      <c r="H314" s="1" t="inlineStr"/>
+      <c r="G314" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H314" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I314" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18886,7 +18999,7 @@
       </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18921,8 +19034,16 @@
           <t>saiddal1923</t>
         </is>
       </c>
-      <c r="G315" s="1" t="inlineStr"/>
-      <c r="H315" s="1" t="inlineStr"/>
+      <c r="G315" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H315" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I315" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18942,7 +19063,7 @@
       </c>
       <c r="R315" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -18977,8 +19098,16 @@
           <t>shell_libreria_bistrot</t>
         </is>
       </c>
-      <c r="G316" s="1" t="inlineStr"/>
-      <c r="H316" s="1" t="inlineStr"/>
+      <c r="G316" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H316" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I316" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -18998,7 +19127,7 @@
       </c>
       <c r="R316" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19033,8 +19162,16 @@
           <t>velopasticceria</t>
         </is>
       </c>
-      <c r="G317" s="1" t="inlineStr"/>
-      <c r="H317" s="1" t="inlineStr"/>
+      <c r="G317" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H317" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I317" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19054,7 +19191,7 @@
       </c>
       <c r="R317" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19098,7 +19235,7 @@
       </c>
       <c r="R318" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19142,7 +19279,7 @@
       </c>
       <c r="R319" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19186,7 +19323,7 @@
       </c>
       <c r="R320" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19221,8 +19358,16 @@
           <t>enotecalantidoto</t>
         </is>
       </c>
-      <c r="G321" s="1" t="inlineStr"/>
-      <c r="H321" s="1" t="inlineStr"/>
+      <c r="G321" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H321" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I321" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19242,7 +19387,7 @@
       </c>
       <c r="R321" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19277,8 +19422,16 @@
           <t>Ilgoccetto</t>
         </is>
       </c>
-      <c r="G322" s="1" t="inlineStr"/>
-      <c r="H322" s="1" t="inlineStr"/>
+      <c r="G322" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H322" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I322" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19298,7 +19451,7 @@
       </c>
       <c r="R322" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19333,8 +19486,16 @@
           <t>latta_roma</t>
         </is>
       </c>
-      <c r="G323" s="1" t="inlineStr"/>
-      <c r="H323" s="1" t="inlineStr"/>
+      <c r="G323" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H323" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I323" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19354,7 +19515,7 @@
       </c>
       <c r="R323" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19385,8 +19546,16 @@
           <t>meta_roma</t>
         </is>
       </c>
-      <c r="G324" s="1" t="inlineStr"/>
-      <c r="H324" s="1" t="inlineStr"/>
+      <c r="G324" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H324" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I324" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19406,7 +19575,7 @@
       </c>
       <c r="R324" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19441,8 +19610,16 @@
           <t>minefleming</t>
         </is>
       </c>
-      <c r="G325" s="1" t="inlineStr"/>
-      <c r="H325" s="1" t="inlineStr"/>
+      <c r="G325" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H325" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I325" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19462,7 +19639,7 @@
       </c>
       <c r="R325" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19497,8 +19674,16 @@
           <t>enotecamosto</t>
         </is>
       </c>
-      <c r="G326" s="1" t="inlineStr"/>
-      <c r="H326" s="1" t="inlineStr"/>
+      <c r="G326" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H326" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I326" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19518,7 +19703,7 @@
       </c>
       <c r="R326" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19747,7 @@
       </c>
       <c r="R327" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19597,8 +19782,16 @@
           <t>pianoc_circolodelvino</t>
         </is>
       </c>
-      <c r="G328" s="1" t="inlineStr"/>
-      <c r="H328" s="1" t="inlineStr"/>
+      <c r="G328" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H328" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I328" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19618,7 +19811,7 @@
       </c>
       <c r="R328" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19653,8 +19846,16 @@
           <t>aipianisottobanco</t>
         </is>
       </c>
-      <c r="G329" s="1" t="inlineStr"/>
-      <c r="H329" s="1" t="inlineStr"/>
+      <c r="G329" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H329" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I329" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19674,7 +19875,7 @@
       </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19709,8 +19910,16 @@
           <t>_spacciogrosso</t>
         </is>
       </c>
-      <c r="G330" s="1" t="inlineStr"/>
-      <c r="H330" s="1" t="inlineStr"/>
+      <c r="G330" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H330" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I330" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19730,7 +19939,7 @@
       </c>
       <c r="R330" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19758,7 +19967,11 @@
         </is>
       </c>
       <c r="G331" s="1" t="inlineStr"/>
-      <c r="H331" s="1" t="inlineStr"/>
+      <c r="H331" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I331" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19778,7 +19991,7 @@
       </c>
       <c r="R331" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -19813,6 +20026,16 @@
           <t>duecentogradi</t>
         </is>
       </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I332" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -19895,6 +20118,16 @@
           <t>53.untitled.restaurant</t>
         </is>
       </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I333" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -19977,8 +20210,16 @@
           <t>aromaticus_</t>
         </is>
       </c>
-      <c r="G334" s="1" t="inlineStr"/>
-      <c r="H334" s="1" t="inlineStr"/>
+      <c r="G334" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H334" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I334" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -19998,7 +20239,7 @@
       </c>
       <c r="R334" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20033,8 +20274,16 @@
           <t>avanveraroma</t>
         </is>
       </c>
-      <c r="G335" s="1" t="inlineStr"/>
-      <c r="H335" s="1" t="inlineStr"/>
+      <c r="G335" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H335" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I335" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20054,7 +20303,7 @@
       </c>
       <c r="R335" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20085,8 +20334,16 @@
           <t>ciaparat_enoteca</t>
         </is>
       </c>
-      <c r="G336" s="1" t="inlineStr"/>
-      <c r="H336" s="1" t="inlineStr"/>
+      <c r="G336" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H336" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I336" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20106,7 +20363,7 @@
       </c>
       <c r="R336" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20150,7 +20407,7 @@
       </c>
       <c r="R337" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20185,8 +20442,16 @@
           <t>dumplingbarroma</t>
         </is>
       </c>
-      <c r="G338" s="1" t="inlineStr"/>
-      <c r="H338" s="1" t="inlineStr"/>
+      <c r="G338" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H338" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I338" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20206,7 +20471,7 @@
       </c>
       <c r="R338" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20237,8 +20502,16 @@
           <t>enofficina_roma</t>
         </is>
       </c>
-      <c r="G339" s="1" t="inlineStr"/>
-      <c r="H339" s="1" t="inlineStr"/>
+      <c r="G339" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H339" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I339" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20258,7 +20531,7 @@
       </c>
       <c r="R339" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20293,8 +20566,16 @@
           <t>enotecalamescita</t>
         </is>
       </c>
-      <c r="G340" s="1" t="inlineStr"/>
-      <c r="H340" s="1" t="inlineStr"/>
+      <c r="G340" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H340" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I340" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20314,7 +20595,7 @@
       </c>
       <c r="R340" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20358,7 +20639,7 @@
       </c>
       <c r="R341" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20402,7 +20683,7 @@
       </c>
       <c r="R342" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20710,11 @@
         </is>
       </c>
       <c r="F343" s="1" t="inlineStr"/>
-      <c r="G343" s="1" t="inlineStr"/>
+      <c r="G343" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H343" s="1" t="inlineStr"/>
       <c r="I343" s="1" t="inlineStr">
         <is>
@@ -20450,63 +20735,64 @@
       </c>
       <c r="R343" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="inlineStr">
+      <c r="A344" t="inlineStr">
         <is>
           <t>Koû Koû</t>
         </is>
       </c>
-      <c r="B344" s="1" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>Via Monte Pertica, 41</t>
         </is>
       </c>
-      <c r="C344" s="1" t="inlineStr">
+      <c r="C344" t="inlineStr">
         <is>
           <t>351/3100815</t>
         </is>
       </c>
-      <c r="D344" s="1" t="inlineStr">
+      <c r="D344" t="inlineStr">
         <is>
           <t>www.koukou.it</t>
         </is>
       </c>
-      <c r="E344" s="1" t="inlineStr">
+      <c r="E344" t="inlineStr">
         <is>
           <t>profile.php?id=61560266815819</t>
         </is>
       </c>
-      <c r="F344" s="1" t="inlineStr">
+      <c r="F344" t="inlineStr">
         <is>
           <t>kou.kouroma</t>
         </is>
       </c>
-      <c r="G344" s="1" t="inlineStr"/>
-      <c r="H344" s="1" t="inlineStr"/>
-      <c r="I344" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J344" s="1" t="inlineStr"/>
-      <c r="K344" s="1" t="inlineStr"/>
-      <c r="L344" s="1" t="inlineStr"/>
-      <c r="M344" s="1" t="inlineStr"/>
-      <c r="N344" s="1" t="inlineStr"/>
-      <c r="O344" s="1" t="inlineStr"/>
-      <c r="P344" s="1" t="inlineStr"/>
-      <c r="Q344" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R344" s="1" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 29/04/2026</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20534,7 +20820,11 @@
         </is>
       </c>
       <c r="G345" s="1" t="inlineStr"/>
-      <c r="H345" s="1" t="inlineStr"/>
+      <c r="H345" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I345" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20554,7 +20844,7 @@
       </c>
       <c r="R345" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20598,7 +20888,7 @@
       </c>
       <c r="R346" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20633,8 +20923,16 @@
           <t>openbaladinroma</t>
         </is>
       </c>
-      <c r="G347" s="1" t="inlineStr"/>
-      <c r="H347" s="1" t="inlineStr"/>
+      <c r="G347" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H347" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I347" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20654,7 +20952,7 @@
       </c>
       <c r="R347" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20685,8 +20983,16 @@
           <t>santi_tradizionecontadina</t>
         </is>
       </c>
-      <c r="G348" s="1" t="inlineStr"/>
-      <c r="H348" s="1" t="inlineStr"/>
+      <c r="G348" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H348" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I348" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20706,7 +21012,7 @@
       </c>
       <c r="R348" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20737,8 +21043,16 @@
           <t>scima_roma</t>
         </is>
       </c>
-      <c r="G349" s="1" t="inlineStr"/>
-      <c r="H349" s="1" t="inlineStr"/>
+      <c r="G349" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H349" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I349" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20758,7 +21072,7 @@
       </c>
       <c r="R349" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20793,8 +21107,16 @@
           <t>tapsroma</t>
         </is>
       </c>
-      <c r="G350" s="1" t="inlineStr"/>
-      <c r="H350" s="1" t="inlineStr"/>
+      <c r="G350" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H350" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I350" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20814,7 +21136,7 @@
       </c>
       <c r="R350" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20858,7 +21180,7 @@
       </c>
       <c r="R351" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20893,8 +21215,16 @@
           <t>vinificio_roma</t>
         </is>
       </c>
-      <c r="G352" s="1" t="inlineStr"/>
-      <c r="H352" s="1" t="inlineStr"/>
+      <c r="G352" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H352" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I352" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20914,7 +21244,7 @@
       </c>
       <c r="R352" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -20945,8 +21275,16 @@
           <t>da.brando</t>
         </is>
       </c>
-      <c r="G353" s="1" t="inlineStr"/>
-      <c r="H353" s="1" t="inlineStr"/>
+      <c r="G353" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H353" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I353" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -20966,7 +21304,7 @@
       </c>
       <c r="R353" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21001,8 +21339,16 @@
           <t>drinkkongbar</t>
         </is>
       </c>
-      <c r="G354" s="1" t="inlineStr"/>
-      <c r="H354" s="1" t="inlineStr"/>
+      <c r="G354" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H354" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I354" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21022,7 +21368,7 @@
       </c>
       <c r="R354" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21057,8 +21403,16 @@
           <t>jerrythomasproject_rome</t>
         </is>
       </c>
-      <c r="G355" s="1" t="inlineStr"/>
-      <c r="H355" s="1" t="inlineStr"/>
+      <c r="G355" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H355" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I355" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21078,7 +21432,7 @@
       </c>
       <c r="R355" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21113,8 +21467,16 @@
           <t>metropolita.roma</t>
         </is>
       </c>
-      <c r="G356" s="1" t="inlineStr"/>
-      <c r="H356" s="1" t="inlineStr"/>
+      <c r="G356" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H356" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I356" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21134,7 +21496,7 @@
       </c>
       <c r="R356" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21169,8 +21531,16 @@
           <t>nodoroma</t>
         </is>
       </c>
-      <c r="G357" s="1" t="inlineStr"/>
-      <c r="H357" s="1" t="inlineStr"/>
+      <c r="G357" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H357" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I357" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21190,7 +21560,7 @@
       </c>
       <c r="R357" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21222,7 +21592,11 @@
         </is>
       </c>
       <c r="G358" s="1" t="inlineStr"/>
-      <c r="H358" s="1" t="inlineStr"/>
+      <c r="H358" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I358" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21242,7 +21616,7 @@
       </c>
       <c r="R358" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21277,8 +21651,16 @@
           <t>porknrollpub</t>
         </is>
       </c>
-      <c r="G359" s="1" t="inlineStr"/>
-      <c r="H359" s="1" t="inlineStr"/>
+      <c r="G359" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H359" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I359" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21298,7 +21680,7 @@
       </c>
       <c r="R359" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21333,6 +21715,16 @@
           <t>agostinopizzeriacorsotrieste</t>
         </is>
       </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I360" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -21415,6 +21807,16 @@
           <t>alsettimogelo_roma</t>
         </is>
       </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I361" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -21493,8 +21895,16 @@
           <t>pizzamaranto</t>
         </is>
       </c>
-      <c r="G362" s="1" t="inlineStr"/>
-      <c r="H362" s="1" t="inlineStr"/>
+      <c r="G362" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H362" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I362" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21514,7 +21924,7 @@
       </c>
       <c r="R362" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21549,8 +21959,16 @@
           <t>amerina_lapizzetta</t>
         </is>
       </c>
-      <c r="G363" s="1" t="inlineStr"/>
-      <c r="H363" s="1" t="inlineStr"/>
+      <c r="G363" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H363" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I363" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21570,7 +21988,7 @@
       </c>
       <c r="R363" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21605,8 +22023,16 @@
           <t>anticofornoroscioli</t>
         </is>
       </c>
-      <c r="G364" s="1" t="inlineStr"/>
-      <c r="H364" s="1" t="inlineStr"/>
+      <c r="G364" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H364" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I364" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21626,7 +22052,7 @@
       </c>
       <c r="R364" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21657,8 +22083,16 @@
           <t>artebianca_digabriele</t>
         </is>
       </c>
-      <c r="G365" s="1" t="inlineStr"/>
-      <c r="H365" s="1" t="inlineStr"/>
+      <c r="G365" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H365" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I365" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21678,7 +22112,7 @@
       </c>
       <c r="R365" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21706,7 +22140,11 @@
         </is>
       </c>
       <c r="G366" s="1" t="inlineStr"/>
-      <c r="H366" s="1" t="inlineStr"/>
+      <c r="H366" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I366" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21726,7 +22164,7 @@
       </c>
       <c r="R366" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21761,8 +22199,16 @@
           <t>gelateria_torce</t>
         </is>
       </c>
-      <c r="G367" s="1" t="inlineStr"/>
-      <c r="H367" s="1" t="inlineStr"/>
+      <c r="G367" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H367" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I367" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21782,7 +22228,7 @@
       </c>
       <c r="R367" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21817,8 +22263,16 @@
           <t>comeillatte</t>
         </is>
       </c>
-      <c r="G368" s="1" t="inlineStr"/>
-      <c r="H368" s="1" t="inlineStr"/>
+      <c r="G368" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H368" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I368" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21838,7 +22292,7 @@
       </c>
       <c r="R368" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21873,8 +22327,16 @@
           <t>cremeriaalpi</t>
         </is>
       </c>
-      <c r="G369" s="1" t="inlineStr"/>
-      <c r="H369" s="1" t="inlineStr"/>
+      <c r="G369" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H369" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I369" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21894,7 +22356,7 @@
       </c>
       <c r="R369" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21925,8 +22387,16 @@
           <t>cremeriaaurelia</t>
         </is>
       </c>
-      <c r="G370" s="1" t="inlineStr"/>
-      <c r="H370" s="1" t="inlineStr"/>
+      <c r="G370" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H370" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I370" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -21946,7 +22416,7 @@
       </c>
       <c r="R370" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -21981,8 +22451,16 @@
           <t>criollo_gelato</t>
         </is>
       </c>
-      <c r="G371" s="1" t="inlineStr"/>
-      <c r="H371" s="1" t="inlineStr"/>
+      <c r="G371" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H371" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I371" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22002,7 +22480,7 @@
       </c>
       <c r="R371" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22046,7 +22524,7 @@
       </c>
       <c r="R372" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22081,8 +22559,16 @@
           <t>tulliopizza</t>
         </is>
       </c>
-      <c r="G373" s="1" t="inlineStr"/>
-      <c r="H373" s="1" t="inlineStr"/>
+      <c r="G373" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H373" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I373" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22102,7 +22588,7 @@
       </c>
       <c r="R373" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22137,8 +22623,16 @@
           <t>donchoc</t>
         </is>
       </c>
-      <c r="G374" s="1" t="inlineStr"/>
-      <c r="H374" s="1" t="inlineStr"/>
+      <c r="G374" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H374" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I374" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22158,7 +22652,7 @@
       </c>
       <c r="R374" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22193,8 +22687,16 @@
           <t>elmaiz.roma</t>
         </is>
       </c>
-      <c r="G375" s="1" t="inlineStr"/>
-      <c r="H375" s="1" t="inlineStr"/>
+      <c r="G375" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H375" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I375" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22214,63 +22716,64 @@
       </c>
       <c r="R375" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="inlineStr">
+      <c r="A376" t="inlineStr">
         <is>
           <t>Elettroforno Frontoni</t>
         </is>
       </c>
-      <c r="B376" s="1" t="inlineStr">
+      <c r="B376" t="inlineStr">
         <is>
           <t>Via Ostiense, 387</t>
         </is>
       </c>
-      <c r="C376" s="1" t="inlineStr">
+      <c r="C376" t="inlineStr">
         <is>
           <t>06/45619534</t>
         </is>
       </c>
-      <c r="D376" s="1" t="inlineStr">
+      <c r="D376" t="inlineStr">
         <is>
           <t>www.elettroforno.it</t>
         </is>
       </c>
-      <c r="E376" s="1" t="inlineStr">
+      <c r="E376" t="inlineStr">
         <is>
           <t>elettroforno</t>
         </is>
       </c>
-      <c r="F376" s="1" t="inlineStr">
+      <c r="F376" t="inlineStr">
         <is>
           <t>elettrofornofrontoni</t>
         </is>
       </c>
-      <c r="G376" s="1" t="inlineStr"/>
-      <c r="H376" s="1" t="inlineStr"/>
-      <c r="I376" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J376" s="1" t="inlineStr"/>
-      <c r="K376" s="1" t="inlineStr"/>
-      <c r="L376" s="1" t="inlineStr"/>
-      <c r="M376" s="1" t="inlineStr"/>
-      <c r="N376" s="1" t="inlineStr"/>
-      <c r="O376" s="1" t="inlineStr"/>
-      <c r="P376" s="1" t="inlineStr"/>
-      <c r="Q376" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R376" s="1" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 29/04/2026</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22305,8 +22808,16 @@
           <t>gelateriafatamorgana</t>
         </is>
       </c>
-      <c r="G377" s="1" t="inlineStr"/>
-      <c r="H377" s="1" t="inlineStr"/>
+      <c r="G377" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H377" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I377" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22326,7 +22837,7 @@
       </c>
       <c r="R377" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22357,8 +22868,16 @@
           <t>gelateria_fiordiluna</t>
         </is>
       </c>
-      <c r="G378" s="1" t="inlineStr"/>
-      <c r="H378" s="1" t="inlineStr"/>
+      <c r="G378" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H378" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I378" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22378,7 +22897,7 @@
       </c>
       <c r="R378" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22422,63 +22941,64 @@
       </c>
       <c r="R379" s="1" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Forno Ottavi 1921</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Via dei Dalmati, 3</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>06/65498083</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>www.ottavi1921.it</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>ottavi1921</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>ottavi1921</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="1" t="inlineStr">
-        <is>
-          <t>Forno Ottavi 1921</t>
-        </is>
-      </c>
-      <c r="B380" s="1" t="inlineStr">
-        <is>
-          <t>Via dei Dalmati, 3</t>
-        </is>
-      </c>
-      <c r="C380" s="1" t="inlineStr">
-        <is>
-          <t>06/65498083</t>
-        </is>
-      </c>
-      <c r="D380" s="1" t="inlineStr">
-        <is>
-          <t>www.ottavi1921.it</t>
-        </is>
-      </c>
-      <c r="E380" s="1" t="inlineStr">
-        <is>
-          <t>ottavi1921</t>
-        </is>
-      </c>
-      <c r="F380" s="1" t="inlineStr">
-        <is>
-          <t>ottavi1921</t>
-        </is>
-      </c>
-      <c r="G380" s="1" t="inlineStr"/>
-      <c r="H380" s="1" t="inlineStr"/>
-      <c r="I380" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J380" s="1" t="inlineStr"/>
-      <c r="K380" s="1" t="inlineStr"/>
-      <c r="L380" s="1" t="inlineStr"/>
-      <c r="M380" s="1" t="inlineStr"/>
-      <c r="N380" s="1" t="inlineStr"/>
-      <c r="O380" s="1" t="inlineStr"/>
-      <c r="P380" s="1" t="inlineStr"/>
-      <c r="Q380" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R380" s="1" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 27/04/2026</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22509,8 +23029,16 @@
           <t>frumentario_</t>
         </is>
       </c>
-      <c r="G381" s="1" t="inlineStr"/>
-      <c r="H381" s="1" t="inlineStr"/>
+      <c r="G381" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H381" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I381" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22530,63 +23058,64 @@
       </c>
       <c r="R381" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="inlineStr">
+      <c r="A382" t="inlineStr">
         <is>
           <t>Futura</t>
         </is>
       </c>
-      <c r="B382" s="1" t="inlineStr">
+      <c r="B382" t="inlineStr">
         <is>
           <t>Piazza di Santa Maria Liberatrice, 31</t>
         </is>
       </c>
-      <c r="C382" s="1" t="inlineStr">
+      <c r="C382" t="inlineStr">
         <is>
           <t>375/6342191</t>
         </is>
       </c>
-      <c r="D382" s="1" t="inlineStr">
+      <c r="D382" t="inlineStr">
         <is>
           <t>www.ristorantefutura.com</t>
         </is>
       </c>
-      <c r="E382" s="1" t="inlineStr">
+      <c r="E382" t="inlineStr">
         <is>
           <t>profile.php?id=61572356416768</t>
         </is>
       </c>
-      <c r="F382" s="1" t="inlineStr">
+      <c r="F382" t="inlineStr">
         <is>
           <t>futura_ristorante</t>
         </is>
       </c>
-      <c r="G382" s="1" t="inlineStr"/>
-      <c r="H382" s="1" t="inlineStr"/>
-      <c r="I382" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J382" s="1" t="inlineStr"/>
-      <c r="K382" s="1" t="inlineStr"/>
-      <c r="L382" s="1" t="inlineStr"/>
-      <c r="M382" s="1" t="inlineStr"/>
-      <c r="N382" s="1" t="inlineStr"/>
-      <c r="O382" s="1" t="inlineStr"/>
-      <c r="P382" s="1" t="inlineStr"/>
-      <c r="Q382" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R382" s="1" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 28/04/2026</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22618,7 +23147,11 @@
         </is>
       </c>
       <c r="G383" s="1" t="inlineStr"/>
-      <c r="H383" s="1" t="inlineStr"/>
+      <c r="H383" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I383" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22638,7 +23171,7 @@
       </c>
       <c r="R383" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22669,8 +23202,16 @@
           <t>gelasio.oltreilgelato</t>
         </is>
       </c>
-      <c r="G384" s="1" t="inlineStr"/>
-      <c r="H384" s="1" t="inlineStr"/>
+      <c r="G384" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H384" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I384" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22690,63 +23231,64 @@
       </c>
       <c r="R384" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="inlineStr">
+      <c r="A385" t="inlineStr">
         <is>
           <t>Gelateria daRe</t>
         </is>
       </c>
-      <c r="B385" s="1" t="inlineStr">
+      <c r="B385" t="inlineStr">
         <is>
           <t>Via Bisagno, 19</t>
         </is>
       </c>
-      <c r="C385" s="1" t="inlineStr">
+      <c r="C385" t="inlineStr">
         <is>
           <t>06/64012423</t>
         </is>
       </c>
-      <c r="D385" s="1" t="inlineStr">
+      <c r="D385" t="inlineStr">
         <is>
           <t>www.gelateriadare.com</t>
         </is>
       </c>
-      <c r="E385" s="1" t="inlineStr">
+      <c r="E385" t="inlineStr">
         <is>
           <t>GelateriadaRe</t>
         </is>
       </c>
-      <c r="F385" s="1" t="inlineStr">
+      <c r="F385" t="inlineStr">
         <is>
           <t>gelateriadare</t>
         </is>
       </c>
-      <c r="G385" s="1" t="inlineStr"/>
-      <c r="H385" s="1" t="inlineStr"/>
-      <c r="I385" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J385" s="1" t="inlineStr"/>
-      <c r="K385" s="1" t="inlineStr"/>
-      <c r="L385" s="1" t="inlineStr"/>
-      <c r="M385" s="1" t="inlineStr"/>
-      <c r="N385" s="1" t="inlineStr"/>
-      <c r="O385" s="1" t="inlineStr"/>
-      <c r="P385" s="1" t="inlineStr"/>
-      <c r="Q385" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R385" s="1" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 04/04/2026</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22781,8 +23323,16 @@
           <t>gelateriadeigracchi</t>
         </is>
       </c>
-      <c r="G386" s="1" t="inlineStr"/>
-      <c r="H386" s="1" t="inlineStr"/>
+      <c r="G386" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H386" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I386" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22802,7 +23352,7 @@
       </c>
       <c r="R386" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22833,8 +23383,16 @@
           <t>igemelligelateria</t>
         </is>
       </c>
-      <c r="G387" s="1" t="inlineStr"/>
-      <c r="H387" s="1" t="inlineStr"/>
+      <c r="G387" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H387" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I387" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22854,7 +23412,7 @@
       </c>
       <c r="R387" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22889,8 +23447,16 @@
           <t>gelateriaimannari</t>
         </is>
       </c>
-      <c r="G388" s="1" t="inlineStr"/>
-      <c r="H388" s="1" t="inlineStr"/>
+      <c r="G388" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H388" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I388" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22910,7 +23476,7 @@
       </c>
       <c r="R388" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22945,8 +23511,16 @@
           <t>gelatodessai</t>
         </is>
       </c>
-      <c r="G389" s="1" t="inlineStr"/>
-      <c r="H389" s="1" t="inlineStr"/>
+      <c r="G389" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H389" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I389" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -22966,7 +23540,7 @@
       </c>
       <c r="R389" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -22998,7 +23572,11 @@
         </is>
       </c>
       <c r="G390" s="1" t="inlineStr"/>
-      <c r="H390" s="1" t="inlineStr"/>
+      <c r="H390" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I390" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23018,7 +23596,7 @@
       </c>
       <c r="R390" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23062,7 +23640,7 @@
       </c>
       <c r="R391" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23097,8 +23675,16 @@
           <t>gorigelato</t>
         </is>
       </c>
-      <c r="G392" s="1" t="inlineStr"/>
-      <c r="H392" s="1" t="inlineStr"/>
+      <c r="G392" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H392" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I392" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23118,7 +23704,7 @@
       </c>
       <c r="R392" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23153,8 +23739,16 @@
           <t>gunthergelatoroma</t>
         </is>
       </c>
-      <c r="G393" s="1" t="inlineStr"/>
-      <c r="H393" s="1" t="inlineStr"/>
+      <c r="G393" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H393" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I393" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23174,7 +23768,7 @@
       </c>
       <c r="R393" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23206,7 +23800,11 @@
         </is>
       </c>
       <c r="G394" s="1" t="inlineStr"/>
-      <c r="H394" s="1" t="inlineStr"/>
+      <c r="H394" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I394" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23226,7 +23824,7 @@
       </c>
       <c r="R394" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23261,8 +23859,16 @@
           <t>la_casa_del_cremolato</t>
         </is>
       </c>
-      <c r="G395" s="1" t="inlineStr"/>
-      <c r="H395" s="1" t="inlineStr"/>
+      <c r="G395" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H395" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I395" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23282,7 +23888,7 @@
       </c>
       <c r="R395" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23313,7 +23919,11 @@
         </is>
       </c>
       <c r="F396" s="1" t="inlineStr"/>
-      <c r="G396" s="1" t="inlineStr"/>
+      <c r="G396" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H396" s="1" t="inlineStr"/>
       <c r="I396" s="1" t="inlineStr">
         <is>
@@ -23334,7 +23944,7 @@
       </c>
       <c r="R396" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23365,8 +23975,16 @@
           <t>lievitopizzapane</t>
         </is>
       </c>
-      <c r="G397" s="1" t="inlineStr"/>
-      <c r="H397" s="1" t="inlineStr"/>
+      <c r="G397" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H397" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I397" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23386,7 +24004,7 @@
       </c>
       <c r="R397" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23421,8 +24039,16 @@
           <t>linapizza_vs</t>
         </is>
       </c>
-      <c r="G398" s="1" t="inlineStr"/>
-      <c r="H398" s="1" t="inlineStr"/>
+      <c r="G398" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H398" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I398" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23442,7 +24068,7 @@
       </c>
       <c r="R398" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23474,7 +24100,11 @@
         </is>
       </c>
       <c r="G399" s="1" t="inlineStr"/>
-      <c r="H399" s="1" t="inlineStr"/>
+      <c r="H399" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I399" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23494,7 +24124,7 @@
       </c>
       <c r="R399" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23529,8 +24159,16 @@
           <t>nevedilattegelateria</t>
         </is>
       </c>
-      <c r="G400" s="1" t="inlineStr"/>
-      <c r="H400" s="1" t="inlineStr"/>
+      <c r="G400" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H400" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I400" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23550,7 +24188,7 @@
       </c>
       <c r="R400" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23578,7 +24216,11 @@
         </is>
       </c>
       <c r="G401" s="1" t="inlineStr"/>
-      <c r="H401" s="1" t="inlineStr"/>
+      <c r="H401" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I401" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23598,7 +24240,7 @@
       </c>
       <c r="R401" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23629,7 +24271,11 @@
         </is>
       </c>
       <c r="F402" s="1" t="inlineStr"/>
-      <c r="G402" s="1" t="inlineStr"/>
+      <c r="G402" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H402" s="1" t="inlineStr"/>
       <c r="I402" s="1" t="inlineStr">
         <is>
@@ -23650,7 +24296,7 @@
       </c>
       <c r="R402" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23682,7 +24328,11 @@
         </is>
       </c>
       <c r="G403" s="1" t="inlineStr"/>
-      <c r="H403" s="1" t="inlineStr"/>
+      <c r="H403" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I403" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23702,7 +24352,7 @@
       </c>
       <c r="R403" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23737,8 +24387,16 @@
           <t>paneetempesta</t>
         </is>
       </c>
-      <c r="G404" s="1" t="inlineStr"/>
-      <c r="H404" s="1" t="inlineStr"/>
+      <c r="G404" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H404" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I404" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23758,7 +24416,7 @@
       </c>
       <c r="R404" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23793,8 +24451,16 @@
           <t>panificio_mare_prati</t>
         </is>
       </c>
-      <c r="G405" s="1" t="inlineStr"/>
-      <c r="H405" s="1" t="inlineStr"/>
+      <c r="G405" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H405" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I405" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23814,7 +24480,7 @@
       </c>
       <c r="R405" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23845,8 +24511,16 @@
           <t>pinseparole</t>
         </is>
       </c>
-      <c r="G406" s="1" t="inlineStr"/>
-      <c r="H406" s="1" t="inlineStr"/>
+      <c r="G406" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H406" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I406" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23866,7 +24540,7 @@
       </c>
       <c r="R406" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23906,7 +24580,7 @@
       </c>
       <c r="R407" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23937,8 +24611,16 @@
           <t>pizzachefroma</t>
         </is>
       </c>
-      <c r="G408" s="1" t="inlineStr"/>
-      <c r="H408" s="1" t="inlineStr"/>
+      <c r="G408" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H408" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I408" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -23958,7 +24640,7 @@
       </c>
       <c r="R408" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -23993,8 +24675,16 @@
           <t>pizzarium</t>
         </is>
       </c>
-      <c r="G409" s="1" t="inlineStr"/>
-      <c r="H409" s="1" t="inlineStr"/>
+      <c r="G409" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H409" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I409" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24014,7 +24704,7 @@
       </c>
       <c r="R409" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24045,8 +24735,16 @@
           <t>prelibatoroma</t>
         </is>
       </c>
-      <c r="G410" s="1" t="inlineStr"/>
-      <c r="H410" s="1" t="inlineStr"/>
+      <c r="G410" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H410" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I410" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24066,7 +24764,7 @@
       </c>
       <c r="R410" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24110,7 +24808,7 @@
       </c>
       <c r="R411" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24138,7 +24836,11 @@
         </is>
       </c>
       <c r="G412" s="1" t="inlineStr"/>
-      <c r="H412" s="1" t="inlineStr"/>
+      <c r="H412" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I412" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24158,59 +24860,59 @@
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="inlineStr">
+      <c r="A413" t="inlineStr">
         <is>
           <t>Salmoneria</t>
         </is>
       </c>
-      <c r="B413" s="1" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t>Via della Dogana Vecchia, 12/13</t>
         </is>
       </c>
-      <c r="C413" s="1" t="inlineStr">
+      <c r="C413" t="inlineStr">
         <is>
           <t>06/68803029</t>
         </is>
       </c>
-      <c r="D413" s="1" t="inlineStr"/>
-      <c r="E413" s="1" t="inlineStr">
+      <c r="E413" t="inlineStr">
         <is>
           <t>salmoneriaitalia</t>
         </is>
       </c>
-      <c r="F413" s="1" t="inlineStr">
+      <c r="F413" t="inlineStr">
         <is>
           <t>Salmoneria_Italia</t>
         </is>
       </c>
-      <c r="G413" s="1" t="inlineStr"/>
-      <c r="H413" s="1" t="inlineStr"/>
-      <c r="I413" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J413" s="1" t="inlineStr"/>
-      <c r="K413" s="1" t="inlineStr"/>
-      <c r="L413" s="1" t="inlineStr"/>
-      <c r="M413" s="1" t="inlineStr"/>
-      <c r="N413" s="1" t="inlineStr"/>
-      <c r="O413" s="1" t="inlineStr"/>
-      <c r="P413" s="1" t="inlineStr"/>
-      <c r="Q413" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R413" s="1" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 29/04/2026</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24245,8 +24947,16 @@
           <t>_san_biagio</t>
         </is>
       </c>
-      <c r="G414" s="1" t="inlineStr"/>
-      <c r="H414" s="1" t="inlineStr"/>
+      <c r="G414" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H414" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I414" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24266,7 +24976,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24301,8 +25011,16 @@
           <t>pizzeriasancho</t>
         </is>
       </c>
-      <c r="G415" s="1" t="inlineStr"/>
-      <c r="H415" s="1" t="inlineStr"/>
+      <c r="G415" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H415" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I415" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24322,7 +25040,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24357,8 +25075,16 @@
           <t>stefanoferraragelato</t>
         </is>
       </c>
-      <c r="G416" s="1" t="inlineStr"/>
-      <c r="H416" s="1" t="inlineStr"/>
+      <c r="G416" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H416" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I416" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24378,7 +25104,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24413,8 +25139,16 @@
           <t>terragelato</t>
         </is>
       </c>
-      <c r="G417" s="1" t="inlineStr"/>
-      <c r="H417" s="1" t="inlineStr"/>
+      <c r="G417" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H417" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I417" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24434,7 +25168,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24469,8 +25203,16 @@
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="G418" s="1" t="inlineStr"/>
-      <c r="H418" s="1" t="inlineStr"/>
+      <c r="G418" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H418" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I418" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24490,7 +25232,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24525,8 +25267,16 @@
           <t>zelato_roma</t>
         </is>
       </c>
-      <c r="G419" s="1" t="inlineStr"/>
-      <c r="H419" s="1" t="inlineStr"/>
+      <c r="G419" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H419" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I419" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24546,7 +25296,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24581,8 +25331,16 @@
           <t>ziarosetta</t>
         </is>
       </c>
-      <c r="G420" s="1" t="inlineStr"/>
-      <c r="H420" s="1" t="inlineStr"/>
+      <c r="G420" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H420" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I420" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -24602,7 +25360,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -2596,7 +2596,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="R185" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="R186" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="R187" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11587,7 @@
       </c>
       <c r="R189" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="R190" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="R191" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="R192" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="R193" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="R194" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="R195" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="R196" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="R197" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="R198" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="R199" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="R200" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="R201" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="R202" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="R203" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="R204" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="R206" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="R207" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="R208" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="R209" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="R210" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="R211" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="R212" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="R213" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="R214" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13147,7 @@
       </c>
       <c r="R215" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13207,7 +13207,7 @@
       </c>
       <c r="R216" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="R217" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="R220" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R221" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="R222" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="R223" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="R224" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="R225" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="R226" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="R229" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R230" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="R231" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="R232" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="R233" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="R234" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="R235" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="R238" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="R239" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="R240" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="R241" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="R242" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="R243" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="R244" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="R246" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="R248" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="R249" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="R250" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="R251" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="R253" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="R254" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="R255" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R256" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="R257" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15743,7 @@
       </c>
       <c r="R258" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15864,7 +15864,7 @@
       </c>
       <c r="R260" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="R261" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="R262" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="R263" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="R265" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="R266" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="R267" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="R268" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="R269" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="R270" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="R271" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="R272" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="R273" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="R274" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="R276" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16897,7 +16897,7 @@
       </c>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="R279" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="R280" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="R281" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17141,7 +17141,7 @@
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="R283" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="R288" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="R289" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17597,7 +17597,7 @@
       </c>
       <c r="R290" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17641,7 @@
       </c>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="R293" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="R294" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="R295" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17917,7 +17917,7 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18101,7 +18101,7 @@
       </c>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="R301" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="R302" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18382,7 +18382,7 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="R306" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18562,7 +18562,7 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="R308" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="R311" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18875,7 +18875,7 @@
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18999,7 @@
       </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="R315" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="R316" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="R317" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="R318" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="R319" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="R320" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19387,7 +19387,7 @@
       </c>
       <c r="R321" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="R322" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="R323" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="R324" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="R325" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19703,7 +19703,7 @@
       </c>
       <c r="R326" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="R327" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="R328" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="R330" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="R331" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="R334" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="R335" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="R336" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
       </c>
       <c r="R337" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="R338" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="R339" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="R340" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20639,7 +20639,7 @@
       </c>
       <c r="R341" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="R342" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="R343" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="R345" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="R346" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="R347" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="R348" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="R349" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21136,7 +21136,7 @@
       </c>
       <c r="R350" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="R351" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="R352" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="R353" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="R354" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21432,7 +21432,7 @@
       </c>
       <c r="R355" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="R356" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="R357" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="R358" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="R359" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="R362" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -21988,7 +21988,7 @@
       </c>
       <c r="R363" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22052,7 +22052,7 @@
       </c>
       <c r="R364" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="R365" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22164,7 +22164,7 @@
       </c>
       <c r="R366" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22228,7 +22228,7 @@
       </c>
       <c r="R367" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="R368" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="R369" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="R370" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="R371" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22524,7 @@
       </c>
       <c r="R372" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22588,7 +22588,7 @@
       </c>
       <c r="R373" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22652,7 +22652,7 @@
       </c>
       <c r="R374" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22716,7 +22716,7 @@
       </c>
       <c r="R375" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22837,7 +22837,7 @@
       </c>
       <c r="R377" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="R378" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -22941,7 +22941,7 @@
       </c>
       <c r="R379" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23058,7 +23058,7 @@
       </c>
       <c r="R381" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="R383" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23231,7 +23231,7 @@
       </c>
       <c r="R384" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="R386" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="R387" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23476,7 +23476,7 @@
       </c>
       <c r="R388" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="R389" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23596,7 +23596,7 @@
       </c>
       <c r="R390" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="R391" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23704,7 +23704,7 @@
       </c>
       <c r="R392" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23768,7 +23768,7 @@
       </c>
       <c r="R393" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23824,7 +23824,7 @@
       </c>
       <c r="R394" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23888,7 +23888,7 @@
       </c>
       <c r="R395" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="R396" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24004,7 +24004,7 @@
       </c>
       <c r="R397" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24068,7 +24068,7 @@
       </c>
       <c r="R398" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24124,7 +24124,7 @@
       </c>
       <c r="R399" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="R400" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="R401" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24296,7 +24296,7 @@
       </c>
       <c r="R402" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24352,7 +24352,7 @@
       </c>
       <c r="R403" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24416,7 +24416,7 @@
       </c>
       <c r="R404" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="R405" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="R406" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24580,7 +24580,7 @@
       </c>
       <c r="R407" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24640,7 +24640,7 @@
       </c>
       <c r="R408" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24704,7 @@
       </c>
       <c r="R409" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24764,7 +24764,7 @@
       </c>
       <c r="R410" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="R411" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24860,7 +24860,7 @@
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -25168,7 +25168,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -25232,7 +25232,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -25296,7 +25296,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -2596,7 +2596,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="R185" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="R186" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="R187" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11587,7 @@
       </c>
       <c r="R189" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="R190" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="R191" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="R192" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="R193" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="R194" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="R195" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="R196" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="R197" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="R198" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="R199" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="R200" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="R201" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="R202" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="R203" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="R204" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="R206" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="R207" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="R208" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="R209" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="R210" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="R211" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="R212" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="R213" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="R214" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13147,7 @@
       </c>
       <c r="R215" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13207,7 +13207,7 @@
       </c>
       <c r="R216" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="R217" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="R220" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R221" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="R222" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="R223" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="R224" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="R225" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="R226" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="R229" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R230" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="R231" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="R232" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="R233" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="R234" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="R235" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="R238" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="R239" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="R240" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="R241" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="R242" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="R243" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="R244" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="R246" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="R248" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="R249" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="R250" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="R251" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="R253" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="R254" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="R255" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R256" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="R257" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15743,7 @@
       </c>
       <c r="R258" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15864,7 +15864,7 @@
       </c>
       <c r="R260" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="R261" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="R262" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="R263" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="R265" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="R266" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="R267" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="R268" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="R269" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="R270" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="R271" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="R272" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="R273" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="R274" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="R276" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16897,7 +16897,7 @@
       </c>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="R279" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="R280" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="R281" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17141,7 +17141,7 @@
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="R283" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="R288" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="R289" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17597,7 +17597,7 @@
       </c>
       <c r="R290" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17641,7 @@
       </c>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="R293" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="R294" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="R295" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17917,7 +17917,7 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18101,7 +18101,7 @@
       </c>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="R301" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="R302" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18382,7 +18382,7 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="R306" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18562,7 +18562,7 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="R308" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="R311" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18875,7 +18875,7 @@
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18999,7 @@
       </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="R315" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="R316" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="R317" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="R318" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="R319" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="R320" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19387,7 +19387,7 @@
       </c>
       <c r="R321" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="R322" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="R323" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="R324" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="R325" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19703,7 +19703,7 @@
       </c>
       <c r="R326" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="R327" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="R328" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="R330" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="R331" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="R334" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="R335" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="R336" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
       </c>
       <c r="R337" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="R338" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="R339" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="R340" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20639,7 +20639,7 @@
       </c>
       <c r="R341" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="R342" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="R343" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="R345" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="R346" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="R347" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="R348" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="R349" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21136,7 +21136,7 @@
       </c>
       <c r="R350" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="R351" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="R352" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="R353" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="R354" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21432,7 +21432,7 @@
       </c>
       <c r="R355" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="R356" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="R357" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="R358" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="R359" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="R362" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -21988,7 +21988,7 @@
       </c>
       <c r="R363" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22052,7 +22052,7 @@
       </c>
       <c r="R364" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="R365" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22164,7 +22164,7 @@
       </c>
       <c r="R366" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22228,7 +22228,7 @@
       </c>
       <c r="R367" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="R368" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="R369" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="R370" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="R371" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22524,7 @@
       </c>
       <c r="R372" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22588,7 +22588,7 @@
       </c>
       <c r="R373" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22652,7 +22652,7 @@
       </c>
       <c r="R374" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22716,7 +22716,7 @@
       </c>
       <c r="R375" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22837,7 +22837,7 @@
       </c>
       <c r="R377" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="R378" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -22941,7 +22941,7 @@
       </c>
       <c r="R379" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23058,7 +23058,7 @@
       </c>
       <c r="R381" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="R383" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23231,7 +23231,7 @@
       </c>
       <c r="R384" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="R386" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="R387" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23476,7 +23476,7 @@
       </c>
       <c r="R388" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="R389" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23596,7 +23596,7 @@
       </c>
       <c r="R390" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="R391" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23704,7 +23704,7 @@
       </c>
       <c r="R392" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23768,7 +23768,7 @@
       </c>
       <c r="R393" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23824,7 +23824,7 @@
       </c>
       <c r="R394" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23888,7 +23888,7 @@
       </c>
       <c r="R395" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="R396" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24004,7 +24004,7 @@
       </c>
       <c r="R397" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24068,7 +24068,7 @@
       </c>
       <c r="R398" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24124,7 +24124,7 @@
       </c>
       <c r="R399" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="R400" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="R401" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24296,7 +24296,7 @@
       </c>
       <c r="R402" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24352,7 +24352,7 @@
       </c>
       <c r="R403" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24416,7 +24416,7 @@
       </c>
       <c r="R404" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="R405" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="R406" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24580,7 +24580,7 @@
       </c>
       <c r="R407" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24640,7 +24640,7 @@
       </c>
       <c r="R408" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24704,7 @@
       </c>
       <c r="R409" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24764,7 +24764,7 @@
       </c>
       <c r="R410" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="R411" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24860,7 +24860,7 @@
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -25168,7 +25168,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -25232,7 +25232,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -25296,7 +25296,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -2596,7 +2596,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="R185" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="R186" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="R187" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11587,7 @@
       </c>
       <c r="R189" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="R190" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="R191" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="R192" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="R193" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="R194" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="R195" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="R196" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="R197" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="R198" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="R199" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="R200" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="R201" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="R202" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="R203" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="R204" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="R206" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="R207" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="R208" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="R209" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="R210" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="R211" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="R212" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="R213" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="R214" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13147,7 @@
       </c>
       <c r="R215" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13207,7 +13207,7 @@
       </c>
       <c r="R216" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="R217" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="R220" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R221" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="R222" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="R223" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="R224" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="R225" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="R226" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="R229" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R230" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="R231" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="R232" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="R233" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="R234" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="R235" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="R238" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="R239" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="R240" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="R241" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="R242" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="R243" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="R244" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="R246" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="R248" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="R249" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="R250" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="R251" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="R253" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="R254" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="R255" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R256" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="R257" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15743,7 @@
       </c>
       <c r="R258" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15864,7 +15864,7 @@
       </c>
       <c r="R260" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="R261" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="R262" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="R263" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="R265" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="R266" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="R267" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="R268" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="R269" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="R270" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="R271" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="R272" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="R273" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="R274" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="R276" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16897,7 +16897,7 @@
       </c>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="R279" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="R280" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="R281" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17141,7 +17141,7 @@
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="R283" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="R288" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="R289" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17597,7 +17597,7 @@
       </c>
       <c r="R290" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17641,7 @@
       </c>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="R293" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="R294" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="R295" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17917,7 +17917,7 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18101,7 +18101,7 @@
       </c>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="R301" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="R302" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18382,7 +18382,7 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="R306" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18562,7 +18562,7 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="R308" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="R311" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18875,7 +18875,7 @@
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18999,7 @@
       </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="R315" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="R316" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="R317" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="R318" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="R319" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="R320" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19387,7 +19387,7 @@
       </c>
       <c r="R321" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="R322" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="R323" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="R324" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="R325" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19703,7 +19703,7 @@
       </c>
       <c r="R326" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="R327" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="R328" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="R330" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="R331" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="R334" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="R335" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="R336" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
       </c>
       <c r="R337" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="R338" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="R339" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="R340" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20639,7 +20639,7 @@
       </c>
       <c r="R341" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="R342" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="R343" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="R345" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="R346" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="R347" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="R348" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="R349" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21136,7 +21136,7 @@
       </c>
       <c r="R350" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="R351" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="R352" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="R353" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="R354" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21432,7 +21432,7 @@
       </c>
       <c r="R355" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="R356" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="R357" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="R358" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="R359" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="R362" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -21988,7 +21988,7 @@
       </c>
       <c r="R363" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22052,7 +22052,7 @@
       </c>
       <c r="R364" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="R365" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22164,7 +22164,7 @@
       </c>
       <c r="R366" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22228,7 +22228,7 @@
       </c>
       <c r="R367" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="R368" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="R369" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="R370" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="R371" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22524,7 @@
       </c>
       <c r="R372" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22588,7 +22588,7 @@
       </c>
       <c r="R373" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22652,7 +22652,7 @@
       </c>
       <c r="R374" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22716,7 +22716,7 @@
       </c>
       <c r="R375" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22837,7 +22837,7 @@
       </c>
       <c r="R377" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="R378" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -22941,7 +22941,7 @@
       </c>
       <c r="R379" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23058,7 +23058,7 @@
       </c>
       <c r="R381" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="R383" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23231,7 +23231,7 @@
       </c>
       <c r="R384" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="R386" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="R387" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23476,7 +23476,7 @@
       </c>
       <c r="R388" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="R389" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23596,7 +23596,7 @@
       </c>
       <c r="R390" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="R391" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23704,7 +23704,7 @@
       </c>
       <c r="R392" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23768,7 +23768,7 @@
       </c>
       <c r="R393" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23824,7 +23824,7 @@
       </c>
       <c r="R394" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23888,7 +23888,7 @@
       </c>
       <c r="R395" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="R396" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24004,7 +24004,7 @@
       </c>
       <c r="R397" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24068,7 +24068,7 @@
       </c>
       <c r="R398" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24124,7 +24124,7 @@
       </c>
       <c r="R399" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="R400" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="R401" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24296,7 +24296,7 @@
       </c>
       <c r="R402" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24352,7 +24352,7 @@
       </c>
       <c r="R403" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24416,7 +24416,7 @@
       </c>
       <c r="R404" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="R405" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="R406" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24580,7 +24580,7 @@
       </c>
       <c r="R407" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24640,7 +24640,7 @@
       </c>
       <c r="R408" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24704,7 @@
       </c>
       <c r="R409" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24764,7 +24764,7 @@
       </c>
       <c r="R410" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="R411" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24860,7 +24860,7 @@
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -25168,7 +25168,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -25232,7 +25232,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -25296,7 +25296,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -2596,7 +2596,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="R103" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="R117" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="R144" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="R151" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="R182" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="R183" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="R185" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="R186" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="R187" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11587,7 @@
       </c>
       <c r="R189" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="R190" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="R191" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="R192" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="R193" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="R194" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="R195" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="R196" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="R197" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="R198" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="R199" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="R200" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="R201" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="R202" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="R203" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="R204" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="R206" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="R207" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="R208" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="R209" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="R210" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="R211" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="R212" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="R213" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="R214" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13147,7 @@
       </c>
       <c r="R215" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13207,7 +13207,7 @@
       </c>
       <c r="R216" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="R217" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="R220" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="R221" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="R222" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="R223" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="R224" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="R225" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="R226" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="R229" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R230" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="R231" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="R232" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="R233" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="R234" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="R235" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="R238" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="R239" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14662,7 @@
       </c>
       <c r="R240" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="R241" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="R242" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="R243" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="R244" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="R246" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="R248" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="R249" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="R250" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="R251" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="R253" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="R254" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="R255" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R256" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="R257" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15743,7 @@
       </c>
       <c r="R258" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15864,7 +15864,7 @@
       </c>
       <c r="R260" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="R261" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="R262" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="R263" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="R265" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="R266" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="R267" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="R268" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="R269" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="R270" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="R271" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="R272" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="R273" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="R274" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="R276" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16897,7 +16897,7 @@
       </c>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="R279" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="R280" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="R281" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17141,7 +17141,7 @@
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="R283" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="R288" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="R289" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17597,7 +17597,7 @@
       </c>
       <c r="R290" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17641,7 @@
       </c>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="R293" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="R294" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="R295" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17917,7 +17917,7 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18101,7 +18101,7 @@
       </c>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="R301" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="R302" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18382,7 +18382,7 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="R306" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18562,7 +18562,7 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="R308" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="R311" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18875,7 +18875,7 @@
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18999,7 @@
       </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="R315" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="R316" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="R317" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="R318" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="R319" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="R320" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19387,7 +19387,7 @@
       </c>
       <c r="R321" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="R322" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="R323" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="R324" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="R325" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19703,7 +19703,7 @@
       </c>
       <c r="R326" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="R327" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="R328" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="R330" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="R331" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="R334" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="R335" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="R336" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
       </c>
       <c r="R337" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="R338" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="R339" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="R340" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20639,7 +20639,7 @@
       </c>
       <c r="R341" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20683,7 +20683,7 @@
       </c>
       <c r="R342" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="R343" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="R345" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="R346" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
       </c>
       <c r="R347" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="R348" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="R349" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21136,7 +21136,7 @@
       </c>
       <c r="R350" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="R351" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="R352" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21304,7 +21304,7 @@
       </c>
       <c r="R353" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="R354" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21432,7 +21432,7 @@
       </c>
       <c r="R355" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="R356" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="R357" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="R358" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="R359" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="R362" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -21988,7 +21988,7 @@
       </c>
       <c r="R363" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22052,7 +22052,7 @@
       </c>
       <c r="R364" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="R365" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22164,7 +22164,7 @@
       </c>
       <c r="R366" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22228,7 +22228,7 @@
       </c>
       <c r="R367" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22292,7 +22292,7 @@
       </c>
       <c r="R368" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="R369" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="R370" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="R371" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22524,7 @@
       </c>
       <c r="R372" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22588,7 +22588,7 @@
       </c>
       <c r="R373" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22652,7 +22652,7 @@
       </c>
       <c r="R374" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22716,7 +22716,7 @@
       </c>
       <c r="R375" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22837,7 +22837,7 @@
       </c>
       <c r="R377" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="R378" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -22941,7 +22941,7 @@
       </c>
       <c r="R379" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23058,7 +23058,7 @@
       </c>
       <c r="R381" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23171,7 +23171,7 @@
       </c>
       <c r="R383" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23231,7 +23231,7 @@
       </c>
       <c r="R384" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="R386" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="R387" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23476,7 +23476,7 @@
       </c>
       <c r="R388" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="R389" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23596,7 +23596,7 @@
       </c>
       <c r="R390" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="R391" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23704,7 +23704,7 @@
       </c>
       <c r="R392" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23768,7 +23768,7 @@
       </c>
       <c r="R393" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23824,7 +23824,7 @@
       </c>
       <c r="R394" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23888,7 +23888,7 @@
       </c>
       <c r="R395" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="R396" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24004,7 +24004,7 @@
       </c>
       <c r="R397" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24068,7 +24068,7 @@
       </c>
       <c r="R398" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24124,7 +24124,7 @@
       </c>
       <c r="R399" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="R400" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="R401" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24296,7 +24296,7 @@
       </c>
       <c r="R402" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24352,7 +24352,7 @@
       </c>
       <c r="R403" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24416,7 +24416,7 @@
       </c>
       <c r="R404" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="R405" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="R406" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24580,7 +24580,7 @@
       </c>
       <c r="R407" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24640,7 +24640,7 @@
       </c>
       <c r="R408" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24704,7 +24704,7 @@
       </c>
       <c r="R409" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24764,7 +24764,7 @@
       </c>
       <c r="R410" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="R411" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24860,7 +24860,7 @@
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25104,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -25168,7 +25168,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -25232,7 +25232,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -25296,7 +25296,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -7017,48 +7017,72 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr"/>
-      <c r="E109" s="1" t="inlineStr"/>
-      <c r="F109" s="1" t="inlineStr"/>
-      <c r="G109" s="1" t="inlineStr"/>
-      <c r="H109" s="1" t="inlineStr"/>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="K109" s="1" t="inlineStr"/>
-      <c r="L109" s="1" t="inlineStr"/>
-      <c r="M109" s="1" t="inlineStr"/>
-      <c r="N109" s="1" t="inlineStr"/>
-      <c r="O109" s="1" t="inlineStr"/>
-      <c r="P109" s="1" t="inlineStr"/>
-      <c r="Q109" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R109" s="1" t="inlineStr">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Baccano</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Via delle Muratte, 23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>06/69941166</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>www.baccanoroma.com</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RistoranteBaccano</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>baccanoroma</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '00'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: trovato (RistoranteBaccano) | IG: trovato (baccanoroma)</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
@@ -7067,37 +7091,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Baccano</t>
+          <t>Borgo San Giorgio</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Via delle Muratte, 23</t>
+          <t>Via dei Pastori, 30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>06/69941166</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>www.baccanoroma.com</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RistoranteBaccano</t>
+          <t>06/59603683</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>baccanoroma</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>borgosangiorgiomaccarese</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7117,7 +7126,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12', 'closes': '00'}, 'martedì': {'opens': '12', 'closes':</t>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -7127,7 +7136,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: trovato (RistoranteBaccano) | IG: trovato (baccanoroma)</t>
+          <t>Rating Google: 5.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (borgosangiorgiomaccarese)</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -7139,22 +7148,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Borgo San Giorgio</t>
+          <t>Buccia</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Via dei Pastori, 30</t>
+          <t>Via Litoranea, Km 20,600</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>06/59603683</t>
+          <t>366/4990849</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>bucciatrattoria</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>borgosangiorgiomaccarese</t>
+          <t>buccia_trattoria</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7174,7 +7193,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
+          <t>{'lunedì': {'opens': '12:30', 'closes': '14:30'}, 'martedì': {'opens': 'Chiuso'}</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -7184,7 +7203,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Rating Google: 5.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (borgosangiorgiomaccarese)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (bucciatrattoria) | IG: trovato (buccia_trattoria)</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -7196,27 +7215,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Buccia</t>
+          <t>Casale Verdeluna</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Via Litoranea, Km 20,600</t>
+          <t>Località Civitella, 3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>366/4990849</t>
+          <t>0775/503051</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>www.casaleverdeluna.it</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>bucciatrattoria</t>
+          <t>CasaleVerdeluna</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>buccia_trattoria</t>
+          <t>casaleverdeluna</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7234,16 +7258,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12:30', 'closes': '14:30'}, 'martedì': {'opens': 'Chiuso'}</t>
-        </is>
-      </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7251,7 +7265,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (bucciatrattoria) | IG: trovato (buccia_trattoria)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (CasaleVerdeluna) | IG: trovato (casaleverdeluna)</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -7263,32 +7277,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Casale Verdeluna</t>
+          <t>Chalet del Lago</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Località Civitella, 3</t>
+          <t>Via Reginaldo Belloni, 28/29</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>0775/503051</t>
+          <t>06/9968229</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>www.casaleverdeluna.it</t>
+          <t>www.chaletdellago.com</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CasaleVerdeluna</t>
+          <t>chaletdellagoanguillara</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>casaleverdeluna</t>
+          <t>chaletdellago</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7306,6 +7320,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30', 'closes': '16'}, '</t>
+        </is>
+      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7313,7 +7337,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (CasaleVerdeluna) | IG: trovato (casaleverdeluna)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (chaletdellagoanguillara) | IG: trovato (chaletdellago)</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -7325,32 +7349,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Chalet del Lago</t>
+          <t>Contrada Rapello</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Via Reginaldo Belloni, 28/29</t>
+          <t>Contrada Rapello, 13</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>06/9968229</t>
+          <t>0774/034382</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>www.chaletdellago.com</t>
+          <t>www.contradarapello.it</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>chaletdellagoanguillara</t>
+          <t>contradarapello</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>chaletdellago</t>
+          <t>contradarapello</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7373,11 +7397,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30', 'closes': '16'}, '</t>
-        </is>
-      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7385,7 +7404,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (chaletdellagoanguillara) | IG: trovato (chaletdellago)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (contradarapello) | IG: trovato (contradarapello)</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -7397,32 +7416,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Contrada Rapello</t>
+          <t>Contrasto</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Contrada Rapello, 13</t>
+          <t>Via Cardinal Pietro La Fontaine, 21</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>0774/034382</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>www.contradarapello.it</t>
+          <t>0761/973117</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>contradarapello</t>
+          <t>contrasto.viterbo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>contradarapello</t>
+          <t>contrasto_viterbo</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7440,11 +7454,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7452,7 +7461,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (contradarapello) | IG: trovato (contradarapello)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (contrasto.viterbo) | IG: trovato (contrasto_viterbo)</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -7464,27 +7473,32 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Contrasto</t>
+          <t>Da Fausto</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Via Cardinal Pietro La Fontaine, 21</t>
+          <t>Piazza Cesare Beccaria, 6</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0761/973117</t>
+          <t>0771/531268</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>www.dafausto.it</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>contrasto.viterbo</t>
+          <t>fausto.ristorantedafausto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>contrasto_viterbo</t>
+          <t>fausto_ferrante_</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7502,6 +7516,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
+        </is>
+      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7509,7 +7533,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (contrasto.viterbo) | IG: trovato (contrasto_viterbo)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (fausto.ristorantedafausto) | IG: trovato (fausto_ferrante_)</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -7521,32 +7545,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Da Fausto</t>
+          <t>Da Michele</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Piazza Cesare Beccaria, 6</t>
+          <t>Via Tiberio Imperatore, 95/97</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>0771/531268</t>
+          <t>06/5404352</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>www.dafausto.it</t>
+          <t>www.ristorantedamicheleroma.it</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>fausto.ristorantedafausto</t>
+          <t>ristorantedamicheleroma</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>fausto_ferrante_</t>
+          <t>ristorantedamicheleroma</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7564,16 +7588,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
-        </is>
-      </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7581,7 +7595,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (fausto.ristorantedafausto) | IG: trovato (fausto_ferrante_)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ristorantedamicheleroma) | IG: trovato (ristorantedamicheleroma)</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -7593,32 +7607,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Da Michele</t>
+          <t>De Novo e D'Antico</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Via Tiberio Imperatore, 95/97</t>
+          <t>Via Santa Margherita, 1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>06/5404352</t>
+          <t>06/9678949</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>www.ristorantedamicheleroma.it</t>
+          <t>www.denovoedantico.it</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ristorantedamicheleroma</t>
+          <t>denovoedantico</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ristorantedamicheleroma</t>
+          <t>denovo_e_dantico_lalocanda</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7636,6 +7650,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '22'}, 'martedì': {'opens': '19:30', 'cl</t>
+        </is>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7643,7 +7667,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ristorantedamicheleroma) | IG: trovato (ristorantedamicheleroma)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (denovoedantico) | IG: trovato (denovo_e_dantico_lalocanda)</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -7655,32 +7679,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>De Novo e D'Antico</t>
+          <t>Divina Giulia</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Via Santa Margherita, 1</t>
+          <t>Via Giovanni Amendola 1/B</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>06/9678949</t>
+          <t>340/8244624</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>www.denovoedantico.it</t>
+          <t>www.ristorantedivinagiulia.it</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>denovoedantico</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>denovo_e_dantico_lalocanda</t>
+          <t>ristorantedivinagiulia.it</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7688,11 +7707,6 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I119" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -7705,7 +7719,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '19:30', 'closes': '22'}, 'martedì': {'opens': '19:30', 'cl</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '13, 20', 'closes': '15, 22</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -7715,7 +7729,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (denovoedantico) | IG: trovato (denovo_e_dantico_lalocanda)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (ristorantedivinagiulia.it) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -7727,31 +7741,41 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Divina Giulia</t>
+          <t>Friccico Mangia&amp;Bevi</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Via Giovanni Amendola 1/B</t>
+          <t>Viale dei Colli Portuensi, 169</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>340/8244624</t>
+          <t>366/8171293</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>www.ristorantedivinagiulia.it</t>
+          <t>www.friccicomangiaebevi.it</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ristorantedivinagiulia.it</t>
+          <t>friccicoroma</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>friccico_roma</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
@@ -7767,7 +7791,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '13, 20', 'closes': '15, 22</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '23:30'}</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -7777,7 +7801,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (ristorantedivinagiulia.it) | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (friccicoroma) | IG: trovato (friccico_roma)</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -7789,37 +7813,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Friccico Mangia&amp;Bevi</t>
+          <t>Gallo Ristorante di Pesce</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Viale dei Colli Portuensi, 169</t>
+          <t>Via di Santa Croce in Gerusalemme, 29</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>366/8171293</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>www.friccicomangiaebevi.it</t>
+          <t>06/69350147</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>friccicoroma</t>
+          <t>profile.php?id=61557992211281</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>friccico_roma</t>
+          <t>gallo_ristorante</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7839,7 +7858,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '23:30'}</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '22:30'}</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -7849,7 +7868,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (friccicoroma) | IG: trovato (friccico_roma)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=61557992211281) | IG: trovato (gallo_ristorante)</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -7861,27 +7880,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Gallo Ristorante di Pesce</t>
+          <t>Garibaldi dal 1970</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Via di Santa Croce in Gerusalemme, 29</t>
+          <t>Via Tiberina, 62</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>06/69350147</t>
+          <t>06/33611962</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>www.garibaldidal1970.com</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>profile.php?id=61557992211281</t>
+          <t>Garibaldidal1970</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>gallo_ristorante</t>
+          <t>ristorante_garibaldidal1970</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7906,7 +7930,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '22:30'}</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 20', 'closes': '15,</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -7916,7 +7940,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=61557992211281) | IG: trovato (gallo_ristorante)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (Garibaldidal1970) | IG: trovato (ristorante_garibaldidal1970)</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -7928,32 +7952,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Garibaldi dal 1970</t>
+          <t>Il Casaletto</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Via Tiberina, 62</t>
+          <t>Strada Grottana, 9</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>06/33611962</t>
+          <t>0761/367077</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>www.garibaldidal1970.com</t>
+          <t>www.ilcasaletto.it</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Garibaldidal1970</t>
+          <t>AgriristoranteilCasaletto</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ristorante_garibaldidal1970</t>
+          <t>Agristorante_ilcasaletto</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7971,16 +7995,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 20', 'closes': '15,</t>
-        </is>
-      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>Si</t>
@@ -7988,7 +8002,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (Garibaldidal1970) | IG: trovato (ristorante_garibaldidal1970)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (AgriristoranteilCasaletto) | IG: trovato (Agristorante_ilcasaletto)</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -8000,42 +8014,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Il Casaletto</t>
+          <t>Il Giardino</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Strada Grottana, 9</t>
+          <t>Via degli Ulivi, 43</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>0761/367077</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>www.ilcasaletto.it</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AgriristoranteilCasaletto</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Agristorante_ilcasaletto</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>0771/85020</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8043,14 +8032,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (AgriristoranteilCasaletto) | IG: trovato (Agristorante_ilcasaletto)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -8062,17 +8051,42 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Il Giardino</t>
+          <t>Il Grecale</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Via degli Ulivi, 43</t>
+          <t>Riviera Zanardelli, 57</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>0771/85020</t>
+          <t>06/9846822</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>www.ristoranteilgrecale.it</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ristoranteilgrecale</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ristoranteilgrecale</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8085,9 +8099,19 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15:30, 22', 'break': '15:30–19:3</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (ristoranteilgrecale) | IG: trovato (ristoranteilgrecale)</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -8099,32 +8123,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Il Grecale</t>
+          <t>Il Pacchero Solitario</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Riviera Zanardelli, 57</t>
+          <t>Via Giuseppe Verdi, 29</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>06/9846822</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>www.ristoranteilgrecale.it</t>
+          <t>06/92062042</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ristoranteilgrecale</t>
+          <t>ristoranteilpaccherosolitario</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ristoranteilgrecale</t>
+          <t>ilpacchero.solitario</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8147,11 +8166,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15:30, 22', 'break': '15:30–19:3</t>
-        </is>
-      </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8159,7 +8173,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (ristoranteilgrecale) | IG: trovato (ristoranteilgrecale)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (ristoranteilpaccherosolitario) | IG: trovato (ilpacchero.solitario)</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -8171,27 +8185,32 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Il Pacchero Solitario</t>
+          <t>Il Torchio</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Via Giuseppe Verdi, 29</t>
+          <t>Via Goffredo Mameli, 3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>06/92062042</t>
+          <t>06/9425520</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>www.torchioristorante.com</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ristoranteilpaccherosolitario</t>
+          <t>iltorchiofrascati</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ilpacchero.solitario</t>
+          <t>iltorchiofrascati</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8209,11 +8228,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="O127" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8221,7 +8235,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (ristoranteilpaccherosolitario) | IG: trovato (ilpacchero.solitario)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (iltorchiofrascati) | IG: trovato (iltorchiofrascati)</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -8233,32 +8247,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Il Torchio</t>
+          <t>Iodio</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Via Goffredo Mameli, 3</t>
+          <t>Via Tor de' Schiavi, 55/d</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>06/9425520</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>www.torchioristorante.com</t>
+          <t>06/89619556</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>iltorchiofrascati</t>
+          <t>iodioroma</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>iltorchiofrascati</t>
+          <t>iodio_roma</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8276,6 +8285,11 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8283,7 +8297,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (iltorchiofrascati) | IG: trovato (iltorchiofrascati)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (iodioroma) | IG: trovato (iodio_roma)</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -8295,27 +8309,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Iodio</t>
+          <t>La Baia</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Via Tor de' Schiavi, 55/d</t>
+          <t>Via Silvi Marina, 1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>06/89619556</t>
+          <t>06/66561647</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>www.labaiadifregene.it</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>iodioroma</t>
+          <t>labaiadifregene</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>iodio_roma</t>
+          <t>la_baia_fregene_</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8333,11 +8352,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="O129" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8345,7 +8359,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (iodioroma) | IG: trovato (iodio_roma)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (labaiadifregene) | IG: trovato (la_baia_fregene_)</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -8357,42 +8371,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>La Baia</t>
+          <t>La Bottega delle tre Sorelle</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Via Silvi Marina, 1</t>
+          <t>Via Giovanni XXIII, snc</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>06/66561647</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>www.labaiadifregene.it</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>labaiadifregene</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>la_baia_fregene_</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>353/4196130</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8400,14 +8389,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (labaiadifregene) | IG: trovato (la_baia_fregene_)</t>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -8419,17 +8408,42 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>La Bottega delle tre Sorelle</t>
+          <t>La Lampara</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Via Giovanni XXIII, snc</t>
+          <t>Via Carbonia, 35</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>353/4196130</t>
+          <t>06/6672038</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>www.lalamparabeach.it</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>lalamparabeach</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>lalampara_passoscuro</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8442,9 +8456,19 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11:30', 'closes': '23'}, 'martedì': {'opens': '11:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (lalamparabeach) | IG: trovato (lalampara_passoscuro)</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -8456,32 +8480,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>La Lampara</t>
+          <t>La Locanda del Bere</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Via Carbonia, 35</t>
+          <t>Via Foro Appio, 64 - Loc. Borgo Faiti</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>06/6672038</t>
+          <t>0773/258620</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>www.lalamparabeach.it</t>
+          <t>www.enotecalocandadelbere.it</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>lalamparabeach</t>
+          <t>locandadelbere</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>lalampara_passoscuro</t>
+          <t>locandadelbere</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8506,7 +8530,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '11:30', 'closes': '23'}, 'martedì': {'opens': '11:30', 'cl</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '09', 'closes': '00'}, 'mer</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -8516,7 +8540,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (lalamparabeach) | IG: trovato (lalampara_passoscuro)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (locandadelbere) | IG: trovato (locandadelbere)</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -8528,32 +8552,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>La Locanda del Bere</t>
+          <t>La Locanda della Chiocciola</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Via Foro Appio, 64 - Loc. Borgo Faiti</t>
+          <t>Localita Seripola</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0773/258620</t>
+          <t>0761/402734</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>www.enotecalocandadelbere.it</t>
+          <t>www.lachiocciola.net</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>locandadelbere</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>locandadelbere</t>
+          <t>La-Locanda-della-Chiocciola-Relais-Benessere/139722916120593</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8561,11 +8580,6 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -8576,19 +8590,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '09', 'closes': '00'}, 'mer</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (locandadelbere) | IG: trovato (locandadelbere)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: non trovato (La-Locanda-della-Chiocciola-Relais-Benessere/139722916120593) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -8600,27 +8604,32 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>La Locanda della Chiocciola</t>
+          <t>La Palazzina</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Localita Seripola</t>
+          <t>Via del Carzolese, 1 ang. Via Casilina</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0761/402734</t>
+          <t>351/7164206</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>www.lachiocciola.net</t>
+          <t>www.ristorantelapalazzina.it</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>La-Locanda-della-Chiocciola-Relais-Benessere/139722916120593</t>
+          <t>LaPalazzinaRistorante</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>la_palazzina_ristorante</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8628,6 +8637,11 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -8638,9 +8652,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: non trovato (La-Locanda-della-Chiocciola-Relais-Benessere/139722916120593) | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (LaPalazzinaRistorante) | IG: trovato (la_palazzina_ristorante)</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -8652,32 +8671,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>La Palazzina</t>
+          <t>La Taverna dei Corsari</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Via del Carzolese, 1 ang. Via Casilina</t>
+          <t>Piazza Vittorio Veneto, 10</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>351/7164206</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>www.ristorantelapalazzina.it</t>
+          <t>0765/279279</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LaPalazzinaRistorante</t>
+          <t>LaTavernaDeiCorsari</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>la_palazzina_ristorante</t>
+          <t>la_tavernadeicorsari</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8707,7 +8721,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (LaPalazzinaRistorante) | IG: trovato (la_palazzina_ristorante)</t>
+          <t>TF: non trovato | FB: trovato (LaTavernaDeiCorsari) | IG: trovato (la_tavernadeicorsari)</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -8719,27 +8733,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>La Taverna dei Corsari</t>
+          <t>La Villetta</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Piazza Vittorio Veneto, 10</t>
+          <t>Via del Porticciolo Romano, snc</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>0765/279279</t>
+          <t>0771/723113</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>www.ristorantelavilletta.it</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LaTavernaDeiCorsari</t>
+          <t>RistoranteLaVillettaDaMario</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>la_tavernadeicorsari</t>
+          <t>ristorantelavillettaformia</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8757,11 +8776,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="O136" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8769,7 +8783,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (LaTavernaDeiCorsari) | IG: trovato (la_tavernadeicorsari)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (RistoranteLaVillettaDaMario) | IG: trovato (ristorantelavillettaformia)</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -8781,32 +8795,32 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>La Villetta</t>
+          <t>Li Somari</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Via del Porticciolo Romano, snc</t>
+          <t>Piazza Rivarola, 21</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0771/723113</t>
+          <t>0774/282499</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>www.ristorantelavilletta.it</t>
+          <t>www.lisomari.com</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RistoranteLaVillettaDaMario</t>
+          <t>LiSomariTivoli</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ristorantelavillettaformia</t>
+          <t>lisomariofficial</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8824,6 +8838,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12, 18', 'closes': '14:30, 23', 'break': '14:30–18'}, 'mar</t>
+        </is>
+      </c>
       <c r="O137" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8831,7 +8855,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (RistoranteLaVillettaDaMario) | IG: trovato (ristorantelavillettaformia)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (LiSomariTivoli) | IG: trovato (lisomariofficial)</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -8843,32 +8867,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Li Somari</t>
+          <t>Lo Stuzzichino</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Piazza Rivarola, 21</t>
+          <t>Contrada Taverna</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>0774/282499</t>
+          <t>0771/598099</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>www.lisomari.com</t>
+          <t>www.ristorantelostuzzichino.com</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LiSomariTivoli</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>lisomariofficial</t>
+          <t>Ristorante-Lo-Stuzzichino-167579323279043</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8876,11 +8895,6 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I138" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -8891,11 +8905,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12, 18', 'closes': '14:30, 23', 'break': '14:30–18'}, 'mar</t>
-        </is>
-      </c>
       <c r="O138" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8903,7 +8912,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (LiSomariTivoli) | IG: trovato (lisomariofficial)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (Ristorante-Lo-Stuzzichino-167579323279043) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -8915,27 +8924,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Lo Stuzzichino</t>
+          <t>Locanda Dorica</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Contrada Taverna</t>
+          <t>Vicolo Giorgi, 15</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>0771/598099</t>
+          <t>06/5590376</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>www.ristorantelostuzzichino.com</t>
+          <t>www.locandadorica.it</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ristorante-Lo-Stuzzichino-167579323279043</t>
+          <t>locandadorica</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>locanda.dorica</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8943,6 +8957,11 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -8953,6 +8972,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '23:30'}, 'martedì': {'opens': 'Chiuso'}, '</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>Si</t>
@@ -8960,7 +8984,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (Ristorante-Lo-Stuzzichino-167579323279043) | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (locandadorica) | IG: trovato (locanda.dorica)</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -8972,32 +8996,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Locanda Dorica</t>
+          <t>Locanda Ruggieri</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vicolo Giorgi, 15</t>
+          <t>Via del Rio, 10</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>06/5590376</t>
+          <t>333/4758507</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>www.locandadorica.it</t>
+          <t>www.ristorantelocandaruggieriterracina.it</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>locandadorica</t>
+          <t>locandaruggieri</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>locanda.dorica</t>
+          <t>locandaruggieri</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9022,7 +9046,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '23:30'}, 'martedì': {'opens': 'Chiuso'}, '</t>
+          <t>{'lunedì': {'opens': '12, 20', 'closes': '14:30, 23', 'break': '14:30–20'}, 'mar</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -9032,7 +9056,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (locandadorica) | IG: trovato (locanda.dorica)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (locandaruggieri) | IG: trovato (locandaruggieri)</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -9044,32 +9068,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Locanda Ruggieri</t>
+          <t>L'Osteria di Ianus</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Via del Rio, 10</t>
+          <t>Via Amiterno, 70</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>333/4758507</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>www.ristorantelocandaruggieriterracina.it</t>
+          <t>335/6151823</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>locandaruggieri</t>
+          <t>losteriadiianus</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>locandaruggieri</t>
+          <t>losteria_di_ianus</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -9094,7 +9113,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12, 20', 'closes': '14:30, 23', 'break': '14:30–20'}, 'mar</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -9104,7 +9123,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (locandaruggieri) | IG: trovato (locandaruggieri)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (losteriadiianus) | IG: trovato (losteria_di_ianus)</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -9114,297 +9133,298 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>L'Osteria di Ianus</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Via Amiterno, 70</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>335/6151823</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>losteriadiianus</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>losteria_di_ianus</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>Bless</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>Via dell’Indipendenza, 208</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>0771/030188</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="inlineStr"/>
+      <c r="E142" s="1" t="inlineStr"/>
+      <c r="F142" s="1" t="inlineStr"/>
+      <c r="G142" s="1" t="inlineStr"/>
+      <c r="H142" s="1" t="inlineStr"/>
+      <c r="I142" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J142" s="1" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="K142" s="1" t="inlineStr"/>
+      <c r="L142" s="1" t="inlineStr"/>
+      <c r="M142" s="1" t="inlineStr"/>
+      <c r="N142" s="1" t="inlineStr"/>
+      <c r="O142" s="1" t="inlineStr"/>
+      <c r="P142" s="1" t="inlineStr"/>
+      <c r="Q142" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R142" s="1" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Maksymovych</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Via della Portella, 31</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>06/5576474</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>www.maksymovychristorante.it</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>maksymovych.ristorante</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>maksymovych_ristorante</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr">
+      <c r="O143" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (losteriadiianus) | IG: trovato (losteria_di_ianus)</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (maksymovych.ristorante) | IG: trovato (maksymovych_ristorante)</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="1" t="inlineStr">
-        <is>
-          <t>Maksymovych</t>
-        </is>
-      </c>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t>Via della Portella, 31</t>
-        </is>
-      </c>
-      <c r="C143" s="1" t="inlineStr">
-        <is>
-          <t>06/5576474</t>
-        </is>
-      </c>
-      <c r="D143" s="1" t="inlineStr">
-        <is>
-          <t>www.maksymovychristorante.it</t>
-        </is>
-      </c>
-      <c r="E143" s="1" t="inlineStr">
-        <is>
-          <t>maksymovych.ristorante</t>
-        </is>
-      </c>
-      <c r="F143" s="1" t="inlineStr">
-        <is>
-          <t>maksymovych_ristorante</t>
-        </is>
-      </c>
-      <c r="G143" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H143" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I143" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J143" s="1" t="inlineStr"/>
-      <c r="K143" s="1" t="inlineStr"/>
-      <c r="L143" s="1" t="inlineStr"/>
-      <c r="M143" s="1" t="inlineStr"/>
-      <c r="N143" s="1" t="inlineStr"/>
-      <c r="O143" s="1" t="inlineStr"/>
-      <c r="P143" s="1" t="inlineStr"/>
-      <c r="Q143" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R143" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
     <row r="144">
-      <c r="A144" s="1" t="inlineStr">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Mamma Angelina</t>
         </is>
       </c>
-      <c r="B144" s="1" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Viale Arrigo Boito, 65</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>06/8608928</t>
         </is>
       </c>
-      <c r="D144" s="1" t="inlineStr"/>
-      <c r="E144" s="1" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>Mamma-Angelina-163636110315582</t>
         </is>
       </c>
-      <c r="F144" s="1" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Mamma-Angelina</t>
         </is>
       </c>
-      <c r="G144" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H144" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I144" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J144" s="1" t="inlineStr"/>
-      <c r="K144" s="1" t="inlineStr"/>
-      <c r="L144" s="1" t="inlineStr"/>
-      <c r="M144" s="1" t="inlineStr"/>
-      <c r="N144" s="1" t="inlineStr"/>
-      <c r="O144" s="1" t="inlineStr"/>
-      <c r="P144" s="1" t="inlineStr"/>
-      <c r="Q144" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R144" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (Mamma-Angelina-163636110315582) | IG: trovato (Mamma-Angelina)</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="inlineStr">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Mamma Orso</t>
         </is>
       </c>
-      <c r="B145" s="1" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Via Arezzo, 17</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>06/97277922</t>
         </is>
       </c>
-      <c r="D145" s="1" t="inlineStr"/>
-      <c r="E145" s="1" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>mammaorsoroma</t>
         </is>
       </c>
-      <c r="F145" s="1" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>ristorantemammaorso</t>
         </is>
       </c>
-      <c r="G145" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H145" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I145" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J145" s="1" t="inlineStr"/>
-      <c r="K145" s="1" t="inlineStr"/>
-      <c r="L145" s="1" t="inlineStr"/>
-      <c r="M145" s="1" t="inlineStr"/>
-      <c r="N145" s="1" t="inlineStr"/>
-      <c r="O145" s="1" t="inlineStr"/>
-      <c r="P145" s="1" t="inlineStr"/>
-      <c r="Q145" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R145" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '19', 'closes': '23:30'}, 'martedì': {'opens': '19', 'close</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (mammaorsoroma) | IG: trovato (ristorantemammaorso)</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="inlineStr">
+      <c r="A146" t="inlineStr">
         <is>
           <t>Mangiafuoco</t>
         </is>
       </c>
-      <c r="B146" s="1" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Via Cicerone, 40</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>06/9411904</t>
         </is>
       </c>
-      <c r="D146" s="1" t="inlineStr"/>
-      <c r="E146" s="1" t="inlineStr"/>
-      <c r="F146" s="1" t="inlineStr"/>
-      <c r="G146" s="1" t="inlineStr"/>
-      <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J146" s="1" t="inlineStr"/>
-      <c r="K146" s="1" t="inlineStr"/>
-      <c r="L146" s="1" t="inlineStr"/>
-      <c r="M146" s="1" t="inlineStr"/>
-      <c r="N146" s="1" t="inlineStr"/>
-      <c r="O146" s="1" t="inlineStr"/>
-      <c r="P146" s="1" t="inlineStr"/>
-      <c r="Q146" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R146" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15, 00', 'break': '15–19:30'}, '</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -9434,7 +9454,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J147" s="1" t="inlineStr"/>
+      <c r="J147" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K147" s="1" t="inlineStr"/>
       <c r="L147" s="1" t="inlineStr"/>
       <c r="M147" s="1" t="inlineStr"/>
@@ -9443,1460 +9467,1547 @@
       <c r="P147" s="1" t="inlineStr"/>
       <c r="Q147" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>Mazzo</t>
         </is>
       </c>
-      <c r="B148" s="1" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Via degli Equi, 62</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>06/69420455</t>
         </is>
       </c>
-      <c r="D148" s="1" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>www.mazzoroma.it</t>
         </is>
       </c>
-      <c r="E148" s="1" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>MAZZO.ROMA</t>
         </is>
       </c>
-      <c r="F148" s="1" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>mazzo_roma</t>
         </is>
       </c>
-      <c r="G148" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H148" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I148" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J148" s="1" t="inlineStr"/>
-      <c r="K148" s="1" t="inlineStr"/>
-      <c r="L148" s="1" t="inlineStr"/>
-      <c r="M148" s="1" t="inlineStr"/>
-      <c r="N148" s="1" t="inlineStr"/>
-      <c r="O148" s="1" t="inlineStr"/>
-      <c r="P148" s="1" t="inlineStr"/>
-      <c r="Q148" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R148" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (MAZZO.ROMA) | IG: trovato (mazzo_roma)</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="inlineStr">
+      <c r="A149" t="inlineStr">
         <is>
           <t>Menabó Vino e Cucina</t>
         </is>
       </c>
-      <c r="B149" s="1" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Via delle Palme, 44/D-E</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>06/86937299</t>
         </is>
       </c>
-      <c r="D149" s="1" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>www.menabovinoecucina.it</t>
         </is>
       </c>
-      <c r="E149" s="1" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>menabovinoecucina</t>
         </is>
       </c>
-      <c r="F149" s="1" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>menabo_vino_e_cucina</t>
         </is>
       </c>
-      <c r="G149" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H149" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I149" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J149" s="1" t="inlineStr"/>
-      <c r="K149" s="1" t="inlineStr"/>
-      <c r="L149" s="1" t="inlineStr"/>
-      <c r="M149" s="1" t="inlineStr"/>
-      <c r="N149" s="1" t="inlineStr"/>
-      <c r="O149" s="1" t="inlineStr"/>
-      <c r="P149" s="1" t="inlineStr"/>
-      <c r="Q149" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R149" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '00'}, '</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (menabovinoecucina) | IG: trovato (menabo_vino_e_cucina)</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="inlineStr">
+      <c r="A150" t="inlineStr">
         <is>
           <t>Michele Chinappi</t>
         </is>
       </c>
-      <c r="B150" s="1" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>Via Abate Tosti, 101</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>0771/279917</t>
         </is>
       </c>
-      <c r="D150" s="1" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>www.michelechinappi.it</t>
         </is>
       </c>
-      <c r="E150" s="1" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>RistoranteMicheleChinappi</t>
         </is>
       </c>
-      <c r="F150" s="1" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>istorantemichelechinappi</t>
         </is>
       </c>
-      <c r="G150" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H150" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I150" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J150" s="1" t="inlineStr"/>
-      <c r="K150" s="1" t="inlineStr"/>
-      <c r="L150" s="1" t="inlineStr"/>
-      <c r="M150" s="1" t="inlineStr"/>
-      <c r="N150" s="1" t="inlineStr"/>
-      <c r="O150" s="1" t="inlineStr"/>
-      <c r="P150" s="1" t="inlineStr"/>
-      <c r="Q150" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R150" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (RistoranteMicheleChinappi) | IG: trovato (istorantemichelechinappi)</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="inlineStr">
+      <c r="A151" t="inlineStr">
         <is>
           <t>Mile</t>
         </is>
       </c>
-      <c r="B151" s="1" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Via Pesaro, 8</t>
         </is>
       </c>
-      <c r="C151" s="1" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>327/5878046</t>
         </is>
       </c>
-      <c r="D151" s="1" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>mile-ristorante-roma.eatbu.com</t>
         </is>
       </c>
-      <c r="E151" s="1" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>mileristorante</t>
         </is>
       </c>
-      <c r="F151" s="1" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>mile_pigneto</t>
         </is>
       </c>
-      <c r="G151" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H151" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I151" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J151" s="1" t="inlineStr"/>
-      <c r="K151" s="1" t="inlineStr"/>
-      <c r="L151" s="1" t="inlineStr"/>
-      <c r="M151" s="1" t="inlineStr"/>
-      <c r="N151" s="1" t="inlineStr"/>
-      <c r="O151" s="1" t="inlineStr"/>
-      <c r="P151" s="1" t="inlineStr"/>
-      <c r="Q151" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R151" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '23'}, 'martedì': {'opens': '19:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (mileristorante) | IG: trovato (mile_pigneto)</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="inlineStr">
+      <c r="A152" t="inlineStr">
         <is>
           <t>Molo 21</t>
         </is>
       </c>
-      <c r="B152" s="1" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Lungomare Guglielmo Marconi, 21</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>0766/1894210</t>
         </is>
       </c>
-      <c r="D152" s="1" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>www.molo21.com</t>
         </is>
       </c>
-      <c r="E152" s="1" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>moloventuno</t>
         </is>
       </c>
-      <c r="F152" s="1" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>_molo21</t>
         </is>
       </c>
-      <c r="G152" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H152" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I152" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J152" s="1" t="inlineStr"/>
-      <c r="K152" s="1" t="inlineStr"/>
-      <c r="L152" s="1" t="inlineStr"/>
-      <c r="M152" s="1" t="inlineStr"/>
-      <c r="N152" s="1" t="inlineStr"/>
-      <c r="O152" s="1" t="inlineStr"/>
-      <c r="P152" s="1" t="inlineStr"/>
-      <c r="Q152" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R152" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10:30', 'closes': '17'}, 'martedì': {'opens': '10:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Rating Google: 3.9 ( rec.) | TF: non trovato | FB: trovato (moloventuno) | IG: trovato (_molo21)</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="inlineStr">
+      <c r="A153" t="inlineStr">
         <is>
           <t>Molo 29</t>
         </is>
       </c>
-      <c r="B153" s="1" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>Via Mario Musco, 29/31</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>06/59600651</t>
         </is>
       </c>
-      <c r="D153" s="1" t="inlineStr"/>
-      <c r="E153" s="1" t="inlineStr"/>
-      <c r="F153" s="1" t="inlineStr"/>
-      <c r="G153" s="1" t="inlineStr"/>
-      <c r="H153" s="1" t="inlineStr"/>
-      <c r="I153" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J153" s="1" t="inlineStr"/>
-      <c r="K153" s="1" t="inlineStr"/>
-      <c r="L153" s="1" t="inlineStr"/>
-      <c r="M153" s="1" t="inlineStr"/>
-      <c r="N153" s="1" t="inlineStr"/>
-      <c r="O153" s="1" t="inlineStr"/>
-      <c r="P153" s="1" t="inlineStr"/>
-      <c r="Q153" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R153" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="inlineStr">
+      <c r="A154" t="inlineStr">
         <is>
           <t>Mr. Meat Kitchen and Grill</t>
         </is>
       </c>
-      <c r="B154" s="1" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Via di Salone, 248</t>
         </is>
       </c>
-      <c r="C154" s="1" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>345/1764800</t>
         </is>
       </c>
-      <c r="D154" s="1" t="inlineStr"/>
-      <c r="E154" s="1" t="inlineStr"/>
-      <c r="F154" s="1" t="inlineStr"/>
-      <c r="G154" s="1" t="inlineStr"/>
-      <c r="H154" s="1" t="inlineStr"/>
-      <c r="I154" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J154" s="1" t="inlineStr"/>
-      <c r="K154" s="1" t="inlineStr"/>
-      <c r="L154" s="1" t="inlineStr"/>
-      <c r="M154" s="1" t="inlineStr"/>
-      <c r="N154" s="1" t="inlineStr"/>
-      <c r="O154" s="1" t="inlineStr"/>
-      <c r="P154" s="1" t="inlineStr"/>
-      <c r="Q154" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R154" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '15'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="inlineStr">
+      <c r="A155" t="inlineStr">
         <is>
           <t>Mudejar Spiriti e Cucina</t>
         </is>
       </c>
-      <c r="B155" s="1" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Corso San Leone, 3/A</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>338/6839418</t>
         </is>
       </c>
-      <c r="D155" s="1" t="inlineStr"/>
-      <c r="E155" s="1" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>mudejarspiritiecucina</t>
         </is>
       </c>
-      <c r="F155" s="1" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>mudejar_spiriti_e_cucina</t>
         </is>
       </c>
-      <c r="G155" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H155" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I155" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J155" s="1" t="inlineStr"/>
-      <c r="K155" s="1" t="inlineStr"/>
-      <c r="L155" s="1" t="inlineStr"/>
-      <c r="M155" s="1" t="inlineStr"/>
-      <c r="N155" s="1" t="inlineStr"/>
-      <c r="O155" s="1" t="inlineStr"/>
-      <c r="P155" s="1" t="inlineStr"/>
-      <c r="Q155" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R155" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11:30, 18', 'closes': '15:30, 23:30', 'break': '15:30–18'}</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Rating Google: 3.6 ( rec.) | TF: non trovato | FB: trovato (mudejarspiritiecucina) | IG: trovato (mudejar_spiriti_e_cucina)</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="inlineStr">
+      <c r="A156" t="inlineStr">
         <is>
           <t>Nena Mercato&amp;Cucina</t>
         </is>
       </c>
-      <c r="B156" s="1" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>Via dei Sabelli, 193</t>
         </is>
       </c>
-      <c r="C156" s="1" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>06/83434951</t>
         </is>
       </c>
-      <c r="D156" s="1" t="inlineStr"/>
-      <c r="E156" s="1" t="inlineStr"/>
-      <c r="F156" s="1" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>nena.mercatocucina</t>
         </is>
       </c>
-      <c r="G156" s="1" t="inlineStr"/>
-      <c r="H156" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I156" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J156" s="1" t="inlineStr"/>
-      <c r="K156" s="1" t="inlineStr"/>
-      <c r="L156" s="1" t="inlineStr"/>
-      <c r="M156" s="1" t="inlineStr"/>
-      <c r="N156" s="1" t="inlineStr"/>
-      <c r="O156" s="1" t="inlineStr"/>
-      <c r="P156" s="1" t="inlineStr"/>
-      <c r="Q156" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R156" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '00'}, '</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (nena.mercatocucina)</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="inlineStr">
+      <c r="A157" t="inlineStr">
         <is>
           <t>NuAN</t>
         </is>
       </c>
-      <c r="B157" s="1" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>Via Siria, 3</t>
         </is>
       </c>
-      <c r="C157" s="1" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>06/69401880</t>
         </is>
       </c>
-      <c r="D157" s="1" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>www.nuancucina.icalu.com</t>
         </is>
       </c>
-      <c r="E157" s="1" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>nuancucina</t>
         </is>
       </c>
-      <c r="F157" s="1" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>nuancucina</t>
         </is>
       </c>
-      <c r="G157" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H157" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I157" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J157" s="1" t="inlineStr"/>
-      <c r="K157" s="1" t="inlineStr"/>
-      <c r="L157" s="1" t="inlineStr"/>
-      <c r="M157" s="1" t="inlineStr"/>
-      <c r="N157" s="1" t="inlineStr"/>
-      <c r="O157" s="1" t="inlineStr"/>
-      <c r="P157" s="1" t="inlineStr"/>
-      <c r="Q157" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R157" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (nuancucina) | IG: trovato (nuancucina)</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="inlineStr">
+      <c r="A158" t="inlineStr">
         <is>
           <t>Osteria “Il Bersagliere”</t>
         </is>
       </c>
-      <c r="B158" s="1" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Via Casilina, km 25,000</t>
         </is>
       </c>
-      <c r="C158" s="1" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>320/6851104</t>
         </is>
       </c>
-      <c r="D158" s="1" t="inlineStr"/>
-      <c r="E158" s="1" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>colonna.roma.fuoriporta</t>
         </is>
       </c>
-      <c r="F158" s="1" t="inlineStr"/>
-      <c r="G158" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H158" s="1" t="inlineStr"/>
-      <c r="I158" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J158" s="1" t="inlineStr"/>
-      <c r="K158" s="1" t="inlineStr"/>
-      <c r="L158" s="1" t="inlineStr"/>
-      <c r="M158" s="1" t="inlineStr"/>
-      <c r="N158" s="1" t="inlineStr"/>
-      <c r="O158" s="1" t="inlineStr"/>
-      <c r="P158" s="1" t="inlineStr"/>
-      <c r="Q158" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R158" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12, 19:30', 'closes': '15,</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (colonna.roma.fuoriporta) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="inlineStr">
+      <c r="A159" t="inlineStr">
         <is>
           <t>Osteria Anna</t>
         </is>
       </c>
-      <c r="B159" s="1" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>S.R. 630 Cassino Formia km. 15</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>0776/952596</t>
         </is>
       </c>
-      <c r="D159" s="1" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>www.osteriaanna.com</t>
         </is>
       </c>
-      <c r="E159" s="1" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>osteriaanna</t>
         </is>
       </c>
-      <c r="F159" s="1" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>osteria_anna</t>
         </is>
       </c>
-      <c r="G159" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H159" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I159" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J159" s="1" t="inlineStr"/>
-      <c r="K159" s="1" t="inlineStr"/>
-      <c r="L159" s="1" t="inlineStr"/>
-      <c r="M159" s="1" t="inlineStr"/>
-      <c r="N159" s="1" t="inlineStr"/>
-      <c r="O159" s="1" t="inlineStr"/>
-      <c r="P159" s="1" t="inlineStr"/>
-      <c r="Q159" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R159" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (osteriaanna) | IG: trovato (osteria_anna)</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="inlineStr">
+      <c r="A160" t="inlineStr">
         <is>
           <t>Osteria del Borgo</t>
         </is>
       </c>
-      <c r="B160" s="1" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Via Borgo di Sopra, 21/23</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>06/30430023</t>
         </is>
       </c>
-      <c r="D160" s="1" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>www.osteriadelborgocesano.com</t>
         </is>
       </c>
-      <c r="E160" s="1" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>osteria.delborgo.50</t>
         </is>
       </c>
-      <c r="F160" s="1" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>osteriadelborgocesano</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H160" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I160" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J160" s="1" t="inlineStr"/>
-      <c r="K160" s="1" t="inlineStr"/>
-      <c r="L160" s="1" t="inlineStr"/>
-      <c r="M160" s="1" t="inlineStr"/>
-      <c r="N160" s="1" t="inlineStr"/>
-      <c r="O160" s="1" t="inlineStr"/>
-      <c r="P160" s="1" t="inlineStr"/>
-      <c r="Q160" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R160" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (osteria.delborgo.50) | IG: non trovato (osteriadelborgocesano)</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="inlineStr">
+      <c r="A161" t="inlineStr">
         <is>
           <t>Osteria del Tempo Perso</t>
         </is>
       </c>
-      <c r="B161" s="1" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Piazza San Rocco, 13</t>
         </is>
       </c>
-      <c r="C161" s="1" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>0776/638039</t>
         </is>
       </c>
-      <c r="D161" s="1" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>www.osteriadeltempoperso.info</t>
         </is>
       </c>
-      <c r="E161" s="1" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>ostempoperso</t>
         </is>
       </c>
-      <c r="F161" s="1" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>osteria_del_tempoperso</t>
         </is>
       </c>
-      <c r="G161" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H161" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I161" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J161" s="1" t="inlineStr"/>
-      <c r="K161" s="1" t="inlineStr"/>
-      <c r="L161" s="1" t="inlineStr"/>
-      <c r="M161" s="1" t="inlineStr"/>
-      <c r="N161" s="1" t="inlineStr"/>
-      <c r="O161" s="1" t="inlineStr"/>
-      <c r="P161" s="1" t="inlineStr"/>
-      <c r="Q161" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R161" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ostempoperso) | IG: non trovato (osteria_del_tempoperso)</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="inlineStr">
+      <c r="A162" t="inlineStr">
         <is>
           <t>Osteria di Maccarese</t>
         </is>
       </c>
-      <c r="B162" s="1" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Via dei Pastori, 26-A/28</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>06/30328324</t>
         </is>
       </c>
-      <c r="D162" s="1" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>www.osteria-di-maccarese.eatbu.com</t>
         </is>
       </c>
-      <c r="E162" s="1" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>osteriadimaccarese</t>
         </is>
       </c>
-      <c r="F162" s="1" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>osteriadimaccarese</t>
         </is>
       </c>
-      <c r="G162" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H162" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I162" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J162" s="1" t="inlineStr"/>
-      <c r="K162" s="1" t="inlineStr"/>
-      <c r="L162" s="1" t="inlineStr"/>
-      <c r="M162" s="1" t="inlineStr"/>
-      <c r="N162" s="1" t="inlineStr"/>
-      <c r="O162" s="1" t="inlineStr"/>
-      <c r="P162" s="1" t="inlineStr"/>
-      <c r="Q162" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R162" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (osteriadimaccarese) | IG: non trovato (osteriadimaccarese)</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="inlineStr">
+      <c r="A163" t="inlineStr">
         <is>
           <t>Osteria La Briciola</t>
         </is>
       </c>
-      <c r="B163" s="1" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>Via Scuole Rurali, 1</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>0774/418421</t>
         </is>
       </c>
-      <c r="D163" s="1" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>www.osterialabriciola.it</t>
         </is>
       </c>
-      <c r="E163" s="1" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>osteria.labriciola</t>
         </is>
       </c>
-      <c r="F163" s="1" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>osterialabriciola</t>
         </is>
       </c>
-      <c r="G163" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H163" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I163" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J163" s="1" t="inlineStr"/>
-      <c r="K163" s="1" t="inlineStr"/>
-      <c r="L163" s="1" t="inlineStr"/>
-      <c r="M163" s="1" t="inlineStr"/>
-      <c r="N163" s="1" t="inlineStr"/>
-      <c r="O163" s="1" t="inlineStr"/>
-      <c r="P163" s="1" t="inlineStr"/>
-      <c r="Q163" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R163" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (osteria.labriciola) | IG: non trovato (osterialabriciola)</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="inlineStr">
+      <c r="A164" t="inlineStr">
         <is>
           <t>Osteria La Massaia</t>
         </is>
       </c>
-      <c r="B164" s="1" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Via della Seta, 1</t>
         </is>
       </c>
-      <c r="C164" s="1" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>06/52205140</t>
         </is>
       </c>
-      <c r="D164" s="1" t="inlineStr"/>
-      <c r="E164" s="1" t="inlineStr"/>
-      <c r="F164" s="1" t="inlineStr"/>
-      <c r="G164" s="1" t="inlineStr"/>
-      <c r="H164" s="1" t="inlineStr"/>
-      <c r="I164" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J164" s="1" t="inlineStr"/>
-      <c r="K164" s="1" t="inlineStr"/>
-      <c r="L164" s="1" t="inlineStr"/>
-      <c r="M164" s="1" t="inlineStr"/>
-      <c r="N164" s="1" t="inlineStr"/>
-      <c r="O164" s="1" t="inlineStr"/>
-      <c r="P164" s="1" t="inlineStr"/>
-      <c r="Q164" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R164" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15, 23:30', 'break': '15–19:30'}</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="inlineStr">
+      <c r="A165" t="inlineStr">
         <is>
           <t>Osteria Santa Lucia</t>
         </is>
       </c>
-      <c r="B165" s="1" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Corso della Repubblica, 26</t>
         </is>
       </c>
-      <c r="C165" s="1" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>0775/211863</t>
         </is>
       </c>
-      <c r="D165" s="1" t="inlineStr"/>
-      <c r="E165" s="1" t="inlineStr"/>
-      <c r="F165" s="1" t="inlineStr"/>
-      <c r="G165" s="1" t="inlineStr"/>
-      <c r="H165" s="1" t="inlineStr"/>
-      <c r="I165" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J165" s="1" t="inlineStr"/>
-      <c r="K165" s="1" t="inlineStr"/>
-      <c r="L165" s="1" t="inlineStr"/>
-      <c r="M165" s="1" t="inlineStr"/>
-      <c r="N165" s="1" t="inlineStr"/>
-      <c r="O165" s="1" t="inlineStr"/>
-      <c r="P165" s="1" t="inlineStr"/>
-      <c r="Q165" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R165" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12, 19', 'closes': '15, 23', 'break': '15–19'}, 'martedì':</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="inlineStr">
+      <c r="A166" t="inlineStr">
         <is>
           <t>Pastorie</t>
         </is>
       </c>
-      <c r="B166" s="1" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>Via Pesaro, 40</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>393/9558235</t>
         </is>
       </c>
-      <c r="D166" s="1" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>www.pastorie.it</t>
         </is>
       </c>
-      <c r="E166" s="1" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>pastorie</t>
         </is>
       </c>
-      <c r="F166" s="1" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>ristorantepastorieroma</t>
         </is>
       </c>
-      <c r="G166" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H166" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I166" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J166" s="1" t="inlineStr"/>
-      <c r="K166" s="1" t="inlineStr"/>
-      <c r="L166" s="1" t="inlineStr"/>
-      <c r="M166" s="1" t="inlineStr"/>
-      <c r="N166" s="1" t="inlineStr"/>
-      <c r="O166" s="1" t="inlineStr"/>
-      <c r="P166" s="1" t="inlineStr"/>
-      <c r="Q166" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R166" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '23'}, '</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (pastorie) | IG: non trovato (ristorantepastorieroma)</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="inlineStr">
+      <c r="A167" t="inlineStr">
         <is>
           <t>Popina Trattoria</t>
         </is>
       </c>
-      <c r="B167" s="1" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>Via Giovanni Verga, 42</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>06/72499997</t>
         </is>
       </c>
-      <c r="D167" s="1" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>www.trattoriapopina.it</t>
         </is>
       </c>
-      <c r="E167" s="1" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>trattoriapopina</t>
         </is>
       </c>
-      <c r="F167" s="1" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>trattoriapopina</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H167" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I167" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J167" s="1" t="inlineStr"/>
-      <c r="K167" s="1" t="inlineStr"/>
-      <c r="L167" s="1" t="inlineStr"/>
-      <c r="M167" s="1" t="inlineStr"/>
-      <c r="N167" s="1" t="inlineStr"/>
-      <c r="O167" s="1" t="inlineStr"/>
-      <c r="P167" s="1" t="inlineStr"/>
-      <c r="Q167" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R167" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15, 22:30', 'break': '15–19:30'}</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (trattoriapopina) | IG: non trovato (trattoriapopina)</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="inlineStr">
+      <c r="A168" t="inlineStr">
         <is>
           <t>Porto Quadro</t>
         </is>
       </c>
-      <c r="B168" s="1" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Piazza Ippolito Nievo, 13/14</t>
         </is>
       </c>
-      <c r="C168" s="1" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>340/8640569</t>
         </is>
       </c>
-      <c r="D168" s="1" t="inlineStr"/>
-      <c r="E168" s="1" t="inlineStr">
+      <c r="E168" t="inlineStr">
         <is>
           <t>PortoQuadroristorante</t>
         </is>
       </c>
-      <c r="F168" s="1" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>portoquadro_ristorante</t>
         </is>
       </c>
-      <c r="G168" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H168" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I168" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J168" s="1" t="inlineStr"/>
-      <c r="K168" s="1" t="inlineStr"/>
-      <c r="L168" s="1" t="inlineStr"/>
-      <c r="M168" s="1" t="inlineStr"/>
-      <c r="N168" s="1" t="inlineStr"/>
-      <c r="O168" s="1" t="inlineStr"/>
-      <c r="P168" s="1" t="inlineStr"/>
-      <c r="Q168" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R168" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '22:30'}, 'martedì': {'opens': '19:30',</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (PortoQuadroristorante) | IG: non trovato (portoquadro_ristorante)</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="inlineStr">
+      <c r="A169" t="inlineStr">
         <is>
           <t>Prato di Sopra</t>
         </is>
       </c>
-      <c r="B169" s="1" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Via Principe Amedeo, 7</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>06/94315464</t>
         </is>
       </c>
-      <c r="D169" s="1" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>www.pratodisopra.it</t>
         </is>
       </c>
-      <c r="E169" s="1" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>profile.php?id=100045448885045</t>
         </is>
       </c>
-      <c r="F169" s="1" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>pratodisopra</t>
         </is>
       </c>
-      <c r="G169" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H169" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I169" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J169" s="1" t="inlineStr"/>
-      <c r="K169" s="1" t="inlineStr"/>
-      <c r="L169" s="1" t="inlineStr"/>
-      <c r="M169" s="1" t="inlineStr"/>
-      <c r="N169" s="1" t="inlineStr"/>
-      <c r="O169" s="1" t="inlineStr"/>
-      <c r="P169" s="1" t="inlineStr"/>
-      <c r="Q169" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R169" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '00'}, '</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100045448885045) | IG: non trovato (pratodisopra)</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="inlineStr">
+      <c r="A170" t="inlineStr">
         <is>
           <t>Ristorante Belvedere dal 1933</t>
         </is>
       </c>
-      <c r="B170" s="1" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>Via Regina Margherita, 29</t>
         </is>
       </c>
-      <c r="C170" s="1" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>06/9419004</t>
         </is>
       </c>
-      <c r="D170" s="1" t="inlineStr"/>
-      <c r="E170" s="1" t="inlineStr"/>
-      <c r="F170" s="1" t="inlineStr"/>
-      <c r="G170" s="1" t="inlineStr"/>
-      <c r="H170" s="1" t="inlineStr"/>
-      <c r="I170" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J170" s="1" t="inlineStr"/>
-      <c r="K170" s="1" t="inlineStr"/>
-      <c r="L170" s="1" t="inlineStr"/>
-      <c r="M170" s="1" t="inlineStr"/>
-      <c r="N170" s="1" t="inlineStr"/>
-      <c r="O170" s="1" t="inlineStr"/>
-      <c r="P170" s="1" t="inlineStr"/>
-      <c r="Q170" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R170" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '22:30'}, 'martedì': {'opens': '19:30',</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>Ristorante degli Angeli</t>
         </is>
       </c>
-      <c r="B171" s="1" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Località Madonna degli Angeli</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>0744/91377</t>
         </is>
       </c>
-      <c r="D171" s="1" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>www.ristorantedegliangeli.it</t>
         </is>
       </c>
-      <c r="E171" s="1" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>angelimagliano</t>
         </is>
       </c>
-      <c r="F171" s="1" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>gli_angeli_gourmet</t>
         </is>
       </c>
-      <c r="G171" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H171" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I171" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J171" s="1" t="inlineStr"/>
-      <c r="K171" s="1" t="inlineStr"/>
-      <c r="L171" s="1" t="inlineStr"/>
-      <c r="M171" s="1" t="inlineStr"/>
-      <c r="N171" s="1" t="inlineStr"/>
-      <c r="O171" s="1" t="inlineStr"/>
-      <c r="P171" s="1" t="inlineStr"/>
-      <c r="Q171" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R171" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '23'}, 'martedì': {'opens': '19:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (angelimagliano) | IG: non trovato (gli_angeli_gourmet)</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="inlineStr">
+      <c r="A172" t="inlineStr">
         <is>
           <t>Santuccio ai Colli</t>
         </is>
       </c>
-      <c r="B172" s="1" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Via Santi Sebastiano e Rocco, 95</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>0773/888573</t>
         </is>
       </c>
-      <c r="D172" s="1" t="inlineStr"/>
-      <c r="E172" s="1" t="inlineStr"/>
-      <c r="F172" s="1" t="inlineStr"/>
-      <c r="G172" s="1" t="inlineStr"/>
-      <c r="H172" s="1" t="inlineStr"/>
-      <c r="I172" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J172" s="1" t="inlineStr"/>
-      <c r="K172" s="1" t="inlineStr"/>
-      <c r="L172" s="1" t="inlineStr"/>
-      <c r="M172" s="1" t="inlineStr"/>
-      <c r="N172" s="1" t="inlineStr"/>
-      <c r="O172" s="1" t="inlineStr"/>
-      <c r="P172" s="1" t="inlineStr"/>
-      <c r="Q172" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R172" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '13, 20', 'closes': '14:30, 22:30', 'break': '14:30–20'}, '</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -10935,204 +11046,223 @@
       <c r="P173" s="1" t="inlineStr"/>
       <c r="Q173" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>Scottadito</t>
         </is>
       </c>
-      <c r="B174" s="1" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Via Veglia, 14</t>
         </is>
       </c>
-      <c r="C174" s="1" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>06/97162153</t>
         </is>
       </c>
-      <c r="D174" s="1" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>www.scottaditoristorante.it</t>
         </is>
       </c>
-      <c r="E174" s="1" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>Scottaditotalenti</t>
         </is>
       </c>
-      <c r="F174" s="1" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>scottadito_ristorante</t>
         </is>
       </c>
-      <c r="G174" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H174" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I174" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J174" s="1" t="inlineStr"/>
-      <c r="K174" s="1" t="inlineStr"/>
-      <c r="L174" s="1" t="inlineStr"/>
-      <c r="M174" s="1" t="inlineStr"/>
-      <c r="N174" s="1" t="inlineStr"/>
-      <c r="O174" s="1" t="inlineStr"/>
-      <c r="P174" s="1" t="inlineStr"/>
-      <c r="Q174" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R174" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Scottaditotalenti) | IG: non trovato (scottadito_ristorante)</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="inlineStr">
+      <c r="A175" t="inlineStr">
         <is>
           <t>Sora Maria e Arcangelo</t>
         </is>
       </c>
-      <c r="B175" s="1" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Via Roma, 45</t>
         </is>
       </c>
-      <c r="C175" s="1" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>06/9564043</t>
         </is>
       </c>
-      <c r="D175" s="1" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>www.soramariaearcangelo.com</t>
         </is>
       </c>
-      <c r="E175" s="1" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>SoraMariaArcangelo</t>
         </is>
       </c>
-      <c r="F175" s="1" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>soramariaarcangelo</t>
         </is>
       </c>
-      <c r="G175" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H175" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I175" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J175" s="1" t="inlineStr"/>
-      <c r="K175" s="1" t="inlineStr"/>
-      <c r="L175" s="1" t="inlineStr"/>
-      <c r="M175" s="1" t="inlineStr"/>
-      <c r="N175" s="1" t="inlineStr"/>
-      <c r="O175" s="1" t="inlineStr"/>
-      <c r="P175" s="1" t="inlineStr"/>
-      <c r="Q175" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R175" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30', 'closes': '14:30'}</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (SoraMariaArcangelo) | IG: non trovato (soramariaarcangelo)</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="inlineStr">
+      <c r="A176" t="inlineStr">
         <is>
           <t>Tram Tram</t>
         </is>
       </c>
-      <c r="B176" s="1" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Via dei Reti, 44/46</t>
         </is>
       </c>
-      <c r="C176" s="1" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>06/490416</t>
         </is>
       </c>
-      <c r="D176" s="1" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>www.tramtram.it</t>
         </is>
       </c>
-      <c r="E176" s="1" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>TramTramOsteria</t>
         </is>
       </c>
-      <c r="F176" s="1" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>fabiolissimasultram</t>
         </is>
       </c>
-      <c r="G176" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H176" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I176" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J176" s="1" t="inlineStr"/>
-      <c r="K176" s="1" t="inlineStr"/>
-      <c r="L176" s="1" t="inlineStr"/>
-      <c r="M176" s="1" t="inlineStr"/>
-      <c r="N176" s="1" t="inlineStr"/>
-      <c r="O176" s="1" t="inlineStr"/>
-      <c r="P176" s="1" t="inlineStr"/>
-      <c r="Q176" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R176" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (TramTramOsteria) | IG: non trovato (fabiolissimasultram)</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
